--- a/research/traditional_assets/database/data/denmark/denmark_transportation.xlsx
+++ b/research/traditional_assets/database/data/denmark/denmark_transportation.xlsx
@@ -353,7 +353,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ3"/>
+  <dimension ref="A1:AQ6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -581,7 +581,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.134</v>
+        <v>0.2095</v>
       </c>
       <c r="E2">
         <v>0.208</v>
@@ -599,40 +599,40 @@
         <v>0.128</v>
       </c>
       <c r="G2">
-        <v>0.116448137631535</v>
+        <v>0.1162498227940992</v>
       </c>
       <c r="H2">
-        <v>0.116448137631535</v>
+        <v>0.1162095449352469</v>
       </c>
       <c r="I2">
-        <v>0.10028812426925</v>
+        <v>0.09985866379734459</v>
       </c>
       <c r="J2">
-        <v>0.07592837343544884</v>
+        <v>0.09379480482494806</v>
       </c>
       <c r="K2">
-        <v>1616.5</v>
+        <v>1602.177</v>
       </c>
       <c r="L2">
-        <v>0.06750041757140471</v>
+        <v>0.06680358081006028</v>
       </c>
       <c r="M2">
         <v>1112.2</v>
       </c>
       <c r="N2">
-        <v>0.02233777397514767</v>
+        <v>0.02231039573771544</v>
       </c>
       <c r="O2">
-        <v>0.6880296937828643</v>
+        <v>0.6941804806834702</v>
       </c>
       <c r="P2">
         <v>229.3</v>
       </c>
       <c r="Q2">
-        <v>0.004605333188726273</v>
+        <v>0.004599688673492313</v>
       </c>
       <c r="R2">
-        <v>0.1418496752242499</v>
+        <v>0.1431177703836717</v>
       </c>
       <c r="S2">
         <v>882.9000000000001</v>
@@ -641,73 +641,73 @@
         <v>0.7938320445962956</v>
       </c>
       <c r="U2">
-        <v>1277.4</v>
+        <v>1286.25</v>
       </c>
       <c r="V2">
-        <v>0.02565570263968139</v>
+        <v>0.02580178611547967</v>
       </c>
       <c r="W2">
-        <v>0.1623970263210769</v>
+        <v>-0.2634469696969697</v>
       </c>
       <c r="X2">
-        <v>0.08510370976008728</v>
+        <v>0.08986105455404342</v>
       </c>
       <c r="Y2">
-        <v>0.07729331656098966</v>
+        <v>-0.3533080242510132</v>
       </c>
       <c r="Z2">
-        <v>1.66096781129275</v>
+        <v>1.657485602601747</v>
       </c>
       <c r="AA2">
-        <v>0.1261145842400961</v>
+        <v>-0.08628892688763011</v>
       </c>
       <c r="AB2">
-        <v>0.08006372801944187</v>
+        <v>0.07928419066219769</v>
       </c>
       <c r="AC2">
-        <v>0.04605085622065419</v>
+        <v>-0.1662021223516058</v>
       </c>
       <c r="AD2">
-        <v>6795.1</v>
+        <v>6828.08</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>0.8186134138260381</v>
       </c>
       <c r="AF2">
-        <v>6795.1</v>
+        <v>6828.898613413827</v>
       </c>
       <c r="AG2">
-        <v>5517.700000000001</v>
+        <v>5542.648613413827</v>
       </c>
       <c r="AH2">
-        <v>0.1200861709422252</v>
+        <v>0.1204814172958709</v>
       </c>
       <c r="AI2">
-        <v>0.3860852272727273</v>
+        <v>0.386982109817379</v>
       </c>
       <c r="AJ2">
-        <v>0.09976350532836237</v>
+        <v>0.100058919034408</v>
       </c>
       <c r="AK2">
-        <v>0.3380405082523618</v>
+        <v>0.3387865187784166</v>
       </c>
       <c r="AL2">
-        <v>271.3</v>
+        <v>274.5</v>
       </c>
       <c r="AM2">
-        <v>224.3</v>
+        <v>227.385</v>
       </c>
       <c r="AN2">
-        <v>2.59563008518278</v>
+        <v>2.607462035102566</v>
       </c>
       <c r="AO2">
-        <v>8.85256173977147</v>
+        <v>8.724885245901639</v>
       </c>
       <c r="AP2">
-        <v>2.10768172963062</v>
+        <v>2.116589997977532</v>
       </c>
       <c r="AQ2">
-        <v>10.70753455193937</v>
+        <v>10.53271323965961</v>
       </c>
     </row>
     <row r="3">
@@ -787,10 +787,10 @@
         <v>0.1623970263210769</v>
       </c>
       <c r="X3">
-        <v>0.08510370976008728</v>
+        <v>0.08507844096922526</v>
       </c>
       <c r="Y3">
-        <v>0.07729331656098966</v>
+        <v>0.07731858535185168</v>
       </c>
       <c r="Z3">
         <v>1.66096781129275</v>
@@ -799,10 +799,10 @@
         <v>0.1261145842400961</v>
       </c>
       <c r="AB3">
-        <v>0.08006372801944187</v>
+        <v>0.08004149366091881</v>
       </c>
       <c r="AC3">
-        <v>0.04605085622065419</v>
+        <v>0.04607309057917724</v>
       </c>
       <c r="AD3">
         <v>6795.1</v>
@@ -845,6 +845,360 @@
       </c>
       <c r="AQ3">
         <v>10.70753455193937</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Denmark</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>DonkeyRepublic Holding A/S (CPSE:DONKEY)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Transportation</t>
+        </is>
+      </c>
+      <c r="G4">
+        <v>0.05796791443850268</v>
+      </c>
+      <c r="H4">
+        <v>0.01390374331550802</v>
+      </c>
+      <c r="I4">
+        <v>-0.0781135124473373</v>
+      </c>
+      <c r="J4">
+        <v>-0.0781135124473373</v>
+      </c>
+      <c r="K4">
+        <v>-3.45</v>
+      </c>
+      <c r="L4">
+        <v>-0.1844919786096257</v>
+      </c>
+      <c r="M4">
+        <v>-0</v>
+      </c>
+      <c r="N4">
+        <v>-0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>-0</v>
+      </c>
+      <c r="Q4">
+        <v>-0</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>5.68</v>
+      </c>
+      <c r="V4">
+        <v>0.2558558558558559</v>
+      </c>
+      <c r="W4">
+        <v>-0.4791666666666667</v>
+      </c>
+      <c r="X4">
+        <v>0.09464366813886159</v>
+      </c>
+      <c r="Y4">
+        <v>-0.5738103348055282</v>
+      </c>
+      <c r="Z4">
+        <v>1.091103436927655</v>
+      </c>
+      <c r="AA4">
+        <v>-0.08522992190178089</v>
+      </c>
+      <c r="AB4">
+        <v>0.07852688766347657</v>
+      </c>
+      <c r="AC4">
+        <v>-0.1637568095652575</v>
+      </c>
+      <c r="AD4">
+        <v>9.880000000000001</v>
+      </c>
+      <c r="AE4">
+        <v>0.8186134138260381</v>
+      </c>
+      <c r="AF4">
+        <v>10.69861341382604</v>
+      </c>
+      <c r="AG4">
+        <v>5.018613413826039</v>
+      </c>
+      <c r="AH4">
+        <v>0.3251995237382806</v>
+      </c>
+      <c r="AI4">
+        <v>0.5294085840895159</v>
+      </c>
+      <c r="AJ4">
+        <v>0.1843816706429568</v>
+      </c>
+      <c r="AK4">
+        <v>0.3454296202175849</v>
+      </c>
+      <c r="AL4">
+        <v>1.57</v>
+      </c>
+      <c r="AM4">
+        <v>1.556</v>
+      </c>
+      <c r="AN4">
+        <v>17.6114081996435</v>
+      </c>
+      <c r="AO4">
+        <v>-0.9108280254777069</v>
+      </c>
+      <c r="AP4">
+        <v>8.945834962256754</v>
+      </c>
+      <c r="AQ4">
+        <v>-0.9190231362467866</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Denmark</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Det Østasiatiske Kompagni A/S (CPSE:OKEAC)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Transportation</t>
+        </is>
+      </c>
+      <c r="K5">
+        <v>-0.273</v>
+      </c>
+      <c r="M5">
+        <v>-0</v>
+      </c>
+      <c r="N5">
+        <v>-0</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>-0</v>
+      </c>
+      <c r="Q5">
+        <v>-0</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>1.45</v>
+      </c>
+      <c r="V5">
+        <v>0.1028368794326241</v>
+      </c>
+      <c r="W5">
+        <v>-0.04772727272727274</v>
+      </c>
+      <c r="X5">
+        <v>0.08129950326447477</v>
+      </c>
+      <c r="Y5">
+        <v>-0.1290267759917475</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+      <c r="AA5">
+        <v>-0.08734793187347933</v>
+      </c>
+      <c r="AB5">
+        <v>0.08129950326447477</v>
+      </c>
+      <c r="AC5">
+        <v>-0.1686474351379541</v>
+      </c>
+      <c r="AD5">
+        <v>0</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>0</v>
+      </c>
+      <c r="AG5">
+        <v>-1.45</v>
+      </c>
+      <c r="AH5">
+        <v>0</v>
+      </c>
+      <c r="AI5">
+        <v>0</v>
+      </c>
+      <c r="AJ5">
+        <v>-0.1146245059288537</v>
+      </c>
+      <c r="AK5">
+        <v>-0.3795811518324608</v>
+      </c>
+      <c r="AL5">
+        <v>0</v>
+      </c>
+      <c r="AM5">
+        <v>-0.101</v>
+      </c>
+      <c r="AQ5">
+        <v>3.554455445544554</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Denmark</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>GreenMobility A/S (CPSE:GREENM)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Transportation</t>
+        </is>
+      </c>
+      <c r="D6">
+        <v>0.285</v>
+      </c>
+      <c r="G6">
+        <v>-0.102874251497006</v>
+      </c>
+      <c r="H6">
+        <v>-0.1113772455089821</v>
+      </c>
+      <c r="I6">
+        <v>-0.2952095808383233</v>
+      </c>
+      <c r="J6">
+        <v>-0.2952095808383233</v>
+      </c>
+      <c r="K6">
+        <v>-10.6</v>
+      </c>
+      <c r="L6">
+        <v>-0.6347305389221557</v>
+      </c>
+      <c r="M6">
+        <v>-0</v>
+      </c>
+      <c r="N6">
+        <v>-0</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>-0</v>
+      </c>
+      <c r="Q6">
+        <v>-0</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>1.72</v>
+      </c>
+      <c r="V6">
+        <v>0.06935483870967742</v>
+      </c>
+      <c r="W6">
+        <v>-1.830742659758204</v>
+      </c>
+      <c r="X6">
+        <v>0.1070910375313823</v>
+      </c>
+      <c r="Y6">
+        <v>-1.937833697289586</v>
+      </c>
+      <c r="Z6">
+        <v>0.5493421052631579</v>
+      </c>
+      <c r="AA6">
+        <v>-0.1621710526315789</v>
+      </c>
+      <c r="AB6">
+        <v>0.07624745575737539</v>
+      </c>
+      <c r="AC6">
+        <v>-0.2384185083889543</v>
+      </c>
+      <c r="AD6">
+        <v>23.1</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6">
+        <v>23.1</v>
+      </c>
+      <c r="AG6">
+        <v>21.38</v>
+      </c>
+      <c r="AH6">
+        <v>0.4822546972860125</v>
+      </c>
+      <c r="AI6">
+        <v>1.096345514950166</v>
+      </c>
+      <c r="AJ6">
+        <v>0.4629709831095712</v>
+      </c>
+      <c r="AK6">
+        <v>1.104909560723514</v>
+      </c>
+      <c r="AL6">
+        <v>1.63</v>
+      </c>
+      <c r="AM6">
+        <v>1.63</v>
+      </c>
+      <c r="AN6">
+        <v>111.0576923076923</v>
+      </c>
+      <c r="AO6">
+        <v>-3.024539877300613</v>
+      </c>
+      <c r="AP6">
+        <v>102.7884615384616</v>
+      </c>
+      <c r="AQ6">
+        <v>-3.024539877300613</v>
       </c>
     </row>
   </sheetData>
@@ -1139,7 +1493,7 @@
         <v>6.56726870622927</v>
       </c>
       <c r="F2">
-        <v>3.02120820809334</v>
+        <v>3.16325416362757</v>
       </c>
       <c r="G2">
         <v>2.59563008518278</v>
@@ -1157,13 +1511,13 @@
         <v>49790.1</v>
       </c>
       <c r="L2">
-        <v>46807.5083914644</v>
+        <v>47383.109959066</v>
       </c>
       <c r="M2">
         <v>55307.8</v>
       </c>
       <c r="N2">
-        <v>55715.4443914644</v>
+        <v>56291.045959066</v>
       </c>
       <c r="O2">
         <v>6795.1</v>
@@ -1172,16 +1526,16 @@
         <v>10185.336</v>
       </c>
       <c r="Q2">
-        <v>0.08006372801944189</v>
+        <v>0.0800414936609188</v>
       </c>
       <c r="R2">
-        <v>0.07980081626894139</v>
+        <v>0.0794138429352016</v>
       </c>
       <c r="S2">
         <v>0.043134</v>
       </c>
       <c r="T2">
-        <v>0.045162</v>
+        <v>0.043134</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -1194,10 +1548,10 @@
         </is>
       </c>
       <c r="W2">
-        <v>0.0851037097600873</v>
+        <v>0.0850784409692253</v>
       </c>
       <c r="X2">
-        <v>0.0874044588645627</v>
+        <v>0.0873777108965873</v>
       </c>
       <c r="Y2">
         <v>0.907123348019059</v>
@@ -1236,7 +1590,7 @@
         <v>49790.1</v>
       </c>
       <c r="AK2">
-        <v>0.043327855959079</v>
+        <v>0.0433</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -1424,13 +1778,13 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.08132234097140918</v>
+        <v>0.08129950326447477</v>
       </c>
       <c r="C2">
-        <v>54713.55585345018</v>
+        <v>54714.38551556835</v>
       </c>
       <c r="D2">
-        <v>53436.15585345018</v>
+        <v>53436.98551556835</v>
       </c>
       <c r="E2">
         <v>-6795.1</v>
@@ -1475,19 +1829,19 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0.08132234097140918</v>
+        <v>0.08129950326447477</v>
       </c>
       <c r="T2">
         <v>0.8198499599185859</v>
       </c>
       <c r="U2">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V2">
         <v>0.22</v>
       </c>
       <c r="W2">
-        <v>0.040326</v>
+        <v>0.039234</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1506,13 +1860,13 @@
         <v>0.01</v>
       </c>
       <c r="B3">
-        <v>0.08118945182127207</v>
+        <v>0.08115574435729292</v>
       </c>
       <c r="C3">
-        <v>54339.31640285394</v>
+        <v>54355.89069389385</v>
       </c>
       <c r="D3">
-        <v>53627.76840285394</v>
+        <v>53644.34269389384</v>
       </c>
       <c r="E3">
         <v>-6229.248000000001</v>
@@ -1539,37 +1893,37 @@
         <v>1781.7</v>
       </c>
       <c r="M3">
-        <v>29.2545484</v>
+        <v>28.4623556</v>
       </c>
       <c r="N3">
-        <v>1752.4454516</v>
+        <v>1753.2376444</v>
       </c>
       <c r="O3">
-        <v>385.537999352</v>
+        <v>385.712281768</v>
       </c>
       <c r="P3">
-        <v>1366.907452248</v>
+        <v>1367.525362632</v>
       </c>
       <c r="Q3">
-        <v>2203.107452248</v>
+        <v>2203.725362632</v>
       </c>
       <c r="R3">
         <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0.08160221396088088</v>
+        <v>0.0815791963204979</v>
       </c>
       <c r="T3">
         <v>0.8263093838452171</v>
       </c>
       <c r="U3">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V3">
         <v>0.22</v>
       </c>
       <c r="W3">
-        <v>0.040326</v>
+        <v>0.039234</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1577,7 +1931,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>60.90334998984294</v>
+        <v>62.59847305119047</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1588,13 +1942,13 @@
         <v>0.02</v>
       </c>
       <c r="B4">
-        <v>0.08105656267113499</v>
+        <v>0.08101198545011107</v>
       </c>
       <c r="C4">
-        <v>53966.45607457934</v>
+        <v>53999.01140104215</v>
       </c>
       <c r="D4">
-        <v>53820.76007457933</v>
+        <v>53853.31540104214</v>
       </c>
       <c r="E4">
         <v>-5663.396000000001</v>
@@ -1621,37 +1975,37 @@
         <v>1781.7</v>
       </c>
       <c r="M4">
-        <v>58.5090968</v>
+        <v>56.9247112</v>
       </c>
       <c r="N4">
-        <v>1723.1909032</v>
+        <v>1724.7752888</v>
       </c>
       <c r="O4">
-        <v>379.101998704</v>
+        <v>379.450563536</v>
       </c>
       <c r="P4">
-        <v>1344.088904496</v>
+        <v>1345.324725264</v>
       </c>
       <c r="Q4">
-        <v>2180.288904496</v>
+        <v>2181.524725264</v>
       </c>
       <c r="R4">
         <v>0.02040816326530612</v>
       </c>
       <c r="S4">
-        <v>0.0818877986440153</v>
+        <v>0.08186459739807253</v>
       </c>
       <c r="T4">
         <v>0.832900632749943</v>
       </c>
       <c r="U4">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V4">
         <v>0.22</v>
       </c>
       <c r="W4">
-        <v>0.040326</v>
+        <v>0.039234</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1659,7 +2013,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>30.45167499492148</v>
+        <v>31.29923652559523</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1670,13 +2024,13 @@
         <v>0.03</v>
       </c>
       <c r="B5">
-        <v>0.08092367352099789</v>
+        <v>0.08086822654292923</v>
       </c>
       <c r="C5">
-        <v>53594.98981165448</v>
+        <v>53643.76659083156</v>
       </c>
       <c r="D5">
-        <v>54015.14581165447</v>
+        <v>54063.92259083156</v>
       </c>
       <c r="E5">
         <v>-5097.544000000001</v>
@@ -1703,37 +2057,37 @@
         <v>1781.7</v>
       </c>
       <c r="M5">
-        <v>87.7636452</v>
+        <v>85.38706679999999</v>
       </c>
       <c r="N5">
-        <v>1693.9363548</v>
+        <v>1696.3129332</v>
       </c>
       <c r="O5">
-        <v>372.665998056</v>
+        <v>373.188845304</v>
       </c>
       <c r="P5">
-        <v>1321.270356744</v>
+        <v>1323.124087896</v>
       </c>
       <c r="Q5">
-        <v>2157.470356744</v>
+        <v>2159.324087896</v>
       </c>
       <c r="R5">
         <v>0.03092783505154639</v>
       </c>
       <c r="S5">
-        <v>0.08217927167113184</v>
+        <v>0.08215588303394766</v>
       </c>
       <c r="T5">
         <v>0.8396277836939414</v>
       </c>
       <c r="U5">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V5">
         <v>0.22</v>
       </c>
       <c r="W5">
-        <v>0.040326</v>
+        <v>0.039234</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1741,7 +2095,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>20.30111666328098</v>
+        <v>20.86615768373016</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1752,13 +2106,13 @@
         <v>0.04</v>
       </c>
       <c r="B6">
-        <v>0.08079078437086078</v>
+        <v>0.08072446763574739</v>
       </c>
       <c r="C6">
-        <v>53224.93277377028</v>
+        <v>53290.17551473955</v>
       </c>
       <c r="D6">
-        <v>54210.94077377029</v>
+        <v>54276.18351473955</v>
       </c>
       <c r="E6">
         <v>-4531.692000000001</v>
@@ -1785,37 +2139,37 @@
         <v>1781.7</v>
       </c>
       <c r="M6">
-        <v>117.0181936</v>
+        <v>113.8494224</v>
       </c>
       <c r="N6">
-        <v>1664.6818064</v>
+        <v>1667.8505776</v>
       </c>
       <c r="O6">
-        <v>366.229997408</v>
+        <v>366.927127072</v>
       </c>
       <c r="P6">
-        <v>1298.451808992</v>
+        <v>1300.923450528</v>
       </c>
       <c r="Q6">
-        <v>2134.651808992</v>
+        <v>2137.123450528</v>
       </c>
       <c r="R6">
         <v>0.04166666666666667</v>
       </c>
       <c r="S6">
-        <v>0.08247681705297999</v>
+        <v>0.08245323712057021</v>
       </c>
       <c r="T6">
         <v>0.8464950836159399</v>
       </c>
       <c r="U6">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V6">
         <v>0.22</v>
       </c>
       <c r="W6">
-        <v>0.040326</v>
+        <v>0.039234</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1823,7 +2177,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>15.22583749746074</v>
+        <v>15.64961826279762</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1834,13 +2188,13 @@
         <v>0.05</v>
       </c>
       <c r="B7">
-        <v>0.08065789522072367</v>
+        <v>0.08058070872856554</v>
       </c>
       <c r="C7">
-        <v>52856.30034122172</v>
+        <v>52938.25772776897</v>
       </c>
       <c r="D7">
-        <v>54408.16034122172</v>
+        <v>54490.11772776897</v>
       </c>
       <c r="E7">
         <v>-3965.84</v>
@@ -1867,37 +2221,37 @@
         <v>1781.7</v>
       </c>
       <c r="M7">
-        <v>146.272742</v>
+        <v>142.311778</v>
       </c>
       <c r="N7">
-        <v>1635.427258</v>
+        <v>1639.388222</v>
       </c>
       <c r="O7">
-        <v>359.79399676</v>
+        <v>360.66540884</v>
       </c>
       <c r="P7">
-        <v>1275.63326124</v>
+        <v>1278.72281316</v>
       </c>
       <c r="Q7">
-        <v>2111.83326124</v>
+        <v>2114.92281316</v>
       </c>
       <c r="R7">
         <v>0.05263157894736843</v>
       </c>
       <c r="S7">
-        <v>0.08278062654813019</v>
+        <v>0.08275685129322689</v>
       </c>
       <c r="T7">
         <v>0.8535069582731384</v>
       </c>
       <c r="U7">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V7">
         <v>0.22</v>
       </c>
       <c r="W7">
-        <v>0.040326</v>
+        <v>0.039234</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1905,7 +2259,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>12.18066999796859</v>
+        <v>12.51969461023809</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1916,13 +2270,13 @@
         <v>0.06</v>
       </c>
       <c r="B8">
-        <v>0.08052500607058657</v>
+        <v>0.08043694982138369</v>
       </c>
       <c r="C8">
-        <v>52489.10811893516</v>
+        <v>52588.0330944535</v>
       </c>
       <c r="D8">
-        <v>54606.82011893516</v>
+        <v>54705.7450944535</v>
       </c>
       <c r="E8">
         <v>-3399.988000000001</v>
@@ -1949,37 +2303,37 @@
         <v>1781.7</v>
       </c>
       <c r="M8">
-        <v>175.5272904</v>
+        <v>170.7741336</v>
       </c>
       <c r="N8">
-        <v>1606.1727096</v>
+        <v>1610.9258664</v>
       </c>
       <c r="O8">
-        <v>353.357996112</v>
+        <v>354.403690608</v>
       </c>
       <c r="P8">
-        <v>1252.814713488</v>
+        <v>1256.522175792</v>
       </c>
       <c r="Q8">
-        <v>2089.014713488</v>
+        <v>2092.722175792</v>
       </c>
       <c r="R8">
         <v>0.06382978723404255</v>
       </c>
       <c r="S8">
-        <v>0.08309090007509211</v>
+        <v>0.08306692534189755</v>
       </c>
       <c r="T8">
         <v>0.8606680217528303</v>
       </c>
       <c r="U8">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V8">
         <v>0.22</v>
       </c>
       <c r="W8">
-        <v>0.040326</v>
+        <v>0.039234</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1987,7 +2341,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>10.15055833164049</v>
+        <v>10.43307884186508</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1998,13 +2352,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B9">
-        <v>0.08039211692044948</v>
+        <v>0.08029319091420185</v>
       </c>
       <c r="C9">
-        <v>52123.37194058447</v>
+        <v>52239.52179500643</v>
       </c>
       <c r="D9">
-        <v>54806.93594058447</v>
+        <v>54923.08579500642</v>
       </c>
       <c r="E9">
         <v>-2834.136</v>
@@ -2031,37 +2385,37 @@
         <v>1781.7</v>
       </c>
       <c r="M9">
-        <v>204.7818388</v>
+        <v>199.2364892</v>
       </c>
       <c r="N9">
-        <v>1576.9181612</v>
+        <v>1582.4635108</v>
       </c>
       <c r="O9">
-        <v>346.921995464</v>
+        <v>348.141972376</v>
       </c>
       <c r="P9">
-        <v>1229.996165736</v>
+        <v>1234.321538424</v>
       </c>
       <c r="Q9">
-        <v>2066.196165736</v>
+        <v>2070.521538424</v>
       </c>
       <c r="R9">
         <v>0.07526881720430109</v>
       </c>
       <c r="S9">
-        <v>0.08340784615102095</v>
+        <v>0.08338366764967942</v>
       </c>
       <c r="T9">
         <v>0.8679830865976772</v>
       </c>
       <c r="U9">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V9">
         <v>0.22</v>
       </c>
       <c r="W9">
-        <v>0.040326</v>
+        <v>0.039234</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2069,7 +2423,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>8.700478569977562</v>
+        <v>8.942639007312923</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2080,13 +2434,13 @@
         <v>0.08</v>
       </c>
       <c r="B10">
-        <v>0.08032786777031238</v>
+        <v>0.08024303200702002</v>
       </c>
       <c r="C10">
-        <v>51654.79871417218</v>
+        <v>51749.90907538091</v>
       </c>
       <c r="D10">
-        <v>54904.21471417218</v>
+        <v>54999.3250753809</v>
       </c>
       <c r="E10">
         <v>-2268.284000000001</v>
@@ -2113,37 +2467,37 @@
         <v>1781.7</v>
       </c>
       <c r="M10">
-        <v>239.0158848</v>
+        <v>234.4890688</v>
       </c>
       <c r="N10">
-        <v>1542.6841152</v>
+        <v>1547.2109312</v>
       </c>
       <c r="O10">
-        <v>339.390505344</v>
+        <v>340.386404864</v>
       </c>
       <c r="P10">
-        <v>1203.293609856</v>
+        <v>1206.824526336</v>
       </c>
       <c r="Q10">
-        <v>2039.493609856</v>
+        <v>2043.024526336</v>
       </c>
       <c r="R10">
         <v>0.08695652173913043</v>
       </c>
       <c r="S10">
-        <v>0.08373168235903519</v>
+        <v>0.08370729565980436</v>
       </c>
       <c r="T10">
         <v>0.8754571745913248</v>
       </c>
       <c r="U10">
-        <v>0.0528</v>
+        <v>0.0518</v>
       </c>
       <c r="V10">
         <v>0.22</v>
       </c>
       <c r="W10">
-        <v>0.041184</v>
+        <v>0.040404</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2151,7 +2505,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>7.454316274798487</v>
+        <v>7.59822199438919</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2162,13 +2516,13 @@
         <v>0.09</v>
       </c>
       <c r="B11">
-        <v>0.08035799862017529</v>
+        <v>0.08011097309983817</v>
       </c>
       <c r="C11">
-        <v>51043.2830360216</v>
+        <v>51385.79657776284</v>
       </c>
       <c r="D11">
-        <v>54858.55103602159</v>
+        <v>55201.06457776284</v>
       </c>
       <c r="E11">
         <v>-1702.432000000001</v>
@@ -2195,45 +2549,45 @@
         <v>1781.7</v>
       </c>
       <c r="M11">
-        <v>280.09674</v>
+        <v>263.8002024</v>
       </c>
       <c r="N11">
-        <v>1501.60326</v>
+        <v>1517.8997976</v>
       </c>
       <c r="O11">
-        <v>330.3527172</v>
+        <v>333.937955472</v>
       </c>
       <c r="P11">
-        <v>1171.2505428</v>
+        <v>1183.961842128</v>
       </c>
       <c r="Q11">
-        <v>2007.4505428</v>
+        <v>2020.161842128</v>
       </c>
       <c r="R11">
         <v>0.0989010989010989</v>
       </c>
       <c r="S11">
-        <v>0.08406263584634646</v>
+        <v>0.08403803637344853</v>
       </c>
       <c r="T11">
         <v>0.8830955282551626</v>
       </c>
       <c r="U11">
-        <v>0.055</v>
+        <v>0.0518</v>
       </c>
       <c r="V11">
         <v>0.22</v>
       </c>
       <c r="W11">
-        <v>0.0429</v>
+        <v>0.040404</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y11">
-        <v>6.361016554494708</v>
+        <v>6.753975106123725</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2244,13 +2598,13 @@
         <v>0.1</v>
       </c>
       <c r="B12">
-        <v>0.08025084947003819</v>
+        <v>0.08011151419265632</v>
       </c>
       <c r="C12">
-        <v>50640.16315134984</v>
+        <v>50819.11495896857</v>
       </c>
       <c r="D12">
-        <v>55021.28315134984</v>
+        <v>55200.23495896856</v>
       </c>
       <c r="E12">
         <v>-1136.58</v>
@@ -2277,37 +2631,37 @@
         <v>1781.7</v>
       </c>
       <c r="M12">
-        <v>311.2186</v>
+        <v>302.73082</v>
       </c>
       <c r="N12">
-        <v>1470.4814</v>
+        <v>1478.96918</v>
       </c>
       <c r="O12">
-        <v>323.505908</v>
+        <v>325.3732196</v>
       </c>
       <c r="P12">
-        <v>1146.975492</v>
+        <v>1153.5959604</v>
       </c>
       <c r="Q12">
-        <v>1983.175492</v>
+        <v>1989.7959604</v>
       </c>
       <c r="R12">
         <v>0.1111111111111111</v>
       </c>
       <c r="S12">
-        <v>0.08440094385559799</v>
+        <v>0.08437612688072925</v>
       </c>
       <c r="T12">
         <v>0.89090362311153</v>
       </c>
       <c r="U12">
-        <v>0.055</v>
+        <v>0.0535</v>
       </c>
       <c r="V12">
         <v>0.22</v>
       </c>
       <c r="W12">
-        <v>0.0429</v>
+        <v>0.04173</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2315,7 +2669,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>5.724914899045237</v>
+        <v>5.885426531728749</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2326,13 +2680,13 @@
         <v>0.11</v>
       </c>
       <c r="B13">
-        <v>0.08027240031990109</v>
+        <v>0.08006135528547448</v>
       </c>
       <c r="C13">
-        <v>50041.50341345467</v>
+        <v>50330.27414709896</v>
       </c>
       <c r="D13">
-        <v>54988.47541345467</v>
+        <v>55277.24614709896</v>
       </c>
       <c r="E13">
         <v>-570.728000000001</v>
@@ -2359,37 +2713,37 @@
         <v>1781.7</v>
       </c>
       <c r="M13">
-        <v>351.677018</v>
+        <v>337.9833996</v>
       </c>
       <c r="N13">
-        <v>1430.022982</v>
+        <v>1443.7166004</v>
       </c>
       <c r="O13">
-        <v>314.60505604</v>
+        <v>317.617652088</v>
       </c>
       <c r="P13">
-        <v>1115.41792596</v>
+        <v>1126.098948312</v>
       </c>
       <c r="Q13">
-        <v>1951.61792596</v>
+        <v>1962.298948312</v>
       </c>
       <c r="R13">
         <v>0.1235955056179775</v>
       </c>
       <c r="S13">
-        <v>0.08474685429202369</v>
+        <v>0.08472181492749942</v>
       </c>
       <c r="T13">
         <v>0.8988871807736587</v>
       </c>
       <c r="U13">
-        <v>0.0565</v>
+        <v>0.0543</v>
       </c>
       <c r="V13">
         <v>0.22</v>
       </c>
       <c r="W13">
-        <v>0.04407000000000001</v>
+        <v>0.042354</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2397,7 +2751,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>5.066296370836493</v>
+        <v>5.271560680520476</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2408,13 +2762,13 @@
         <v>0.12</v>
       </c>
       <c r="B14">
-        <v>0.08017695116976399</v>
+        <v>0.07994879637829265</v>
       </c>
       <c r="C14">
-        <v>49621.255433055</v>
+        <v>49938.02341271554</v>
       </c>
       <c r="D14">
-        <v>55134.079433055</v>
+        <v>55450.84741271554</v>
       </c>
       <c r="E14">
         <v>-4.876000000001113</v>
@@ -2441,37 +2795,37 @@
         <v>1781.7</v>
       </c>
       <c r="M14">
-        <v>383.647656</v>
+        <v>368.7091632</v>
       </c>
       <c r="N14">
-        <v>1398.052344</v>
+        <v>1412.9908368</v>
       </c>
       <c r="O14">
-        <v>307.5715156800001</v>
+        <v>310.8579840960001</v>
       </c>
       <c r="P14">
-        <v>1090.48082832</v>
+        <v>1102.132852704</v>
       </c>
       <c r="Q14">
-        <v>1926.68082832</v>
+        <v>1938.332852704</v>
       </c>
       <c r="R14">
         <v>0.1363636363636364</v>
       </c>
       <c r="S14">
-        <v>0.08510062632927726</v>
+        <v>0.0850753595207871</v>
       </c>
       <c r="T14">
         <v>0.9070521829281083</v>
       </c>
       <c r="U14">
-        <v>0.0565</v>
+        <v>0.0543</v>
       </c>
       <c r="V14">
         <v>0.22</v>
       </c>
       <c r="W14">
-        <v>0.04407000000000001</v>
+        <v>0.042354</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2479,7 +2833,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>4.644105006600119</v>
+        <v>4.83226395714377</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2490,13 +2844,13 @@
         <v>0.13</v>
       </c>
       <c r="B15">
-        <v>0.08008150201962688</v>
+        <v>0.07983623747111079</v>
       </c>
       <c r="C15">
-        <v>49201.78058980098</v>
+        <v>49546.86652246857</v>
       </c>
       <c r="D15">
-        <v>55280.45658980098</v>
+        <v>55625.54252246857</v>
       </c>
       <c r="E15">
         <v>560.9759999999997</v>
@@ -2523,37 +2877,37 @@
         <v>1781.7</v>
       </c>
       <c r="M15">
-        <v>415.618294</v>
+        <v>399.4349268</v>
       </c>
       <c r="N15">
-        <v>1366.081706</v>
+        <v>1382.2650732</v>
       </c>
       <c r="O15">
-        <v>300.53797532</v>
+        <v>304.098316104</v>
       </c>
       <c r="P15">
-        <v>1065.54373068</v>
+        <v>1078.166757096</v>
       </c>
       <c r="Q15">
-        <v>1901.74373068</v>
+        <v>1914.366757096</v>
       </c>
       <c r="R15">
         <v>0.1494252873563219</v>
       </c>
       <c r="S15">
-        <v>0.08546253105704239</v>
+        <v>0.08543703157598942</v>
       </c>
       <c r="T15">
         <v>0.9154048862815107</v>
       </c>
       <c r="U15">
-        <v>0.0565</v>
+        <v>0.0543</v>
       </c>
       <c r="V15">
         <v>0.22</v>
       </c>
       <c r="W15">
-        <v>0.04407000000000001</v>
+        <v>0.042354</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2561,7 +2915,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>4.286866159938571</v>
+        <v>4.460551345055787</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2572,13 +2926,13 @@
         <v>0.14</v>
       </c>
       <c r="B16">
-        <v>0.08013893286948978</v>
+        <v>0.07983287856392896</v>
       </c>
       <c r="C16">
-        <v>48547.76185254273</v>
+        <v>48986.24457181655</v>
       </c>
       <c r="D16">
-        <v>55192.28985254273</v>
+        <v>55630.77257181655</v>
       </c>
       <c r="E16">
         <v>1126.828</v>
@@ -2605,37 +2959,37 @@
         <v>1781.7</v>
       </c>
       <c r="M16">
-        <v>458.6796312000001</v>
+        <v>438.0826184000001</v>
       </c>
       <c r="N16">
-        <v>1323.0203688</v>
+        <v>1343.6173816</v>
       </c>
       <c r="O16">
-        <v>291.064481136</v>
+        <v>295.595823952</v>
       </c>
       <c r="P16">
-        <v>1031.955887664</v>
+        <v>1048.021557648</v>
       </c>
       <c r="Q16">
-        <v>1868.155887664</v>
+        <v>1884.221557648</v>
       </c>
       <c r="R16">
         <v>0.1627906976744186</v>
       </c>
       <c r="S16">
-        <v>0.08583285217382533</v>
+        <v>0.08580711460921971</v>
       </c>
       <c r="T16">
         <v>0.9239518385501087</v>
       </c>
       <c r="U16">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V16">
         <v>0.22</v>
       </c>
       <c r="W16">
-        <v>0.045162</v>
+        <v>0.04313400000000001</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2643,7 +2997,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>3.884410553262867</v>
+        <v>4.067041067521158</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2654,13 +3008,13 @@
         <v>0.15</v>
       </c>
       <c r="B17">
-        <v>0.08005440371935267</v>
+        <v>0.0797281196567471</v>
       </c>
       <c r="C17">
-        <v>48111.77526484378</v>
+        <v>48584.0045043118</v>
       </c>
       <c r="D17">
-        <v>55322.15526484378</v>
+        <v>55794.3845043118</v>
       </c>
       <c r="E17">
         <v>1692.679999999998</v>
@@ -2687,37 +3041,37 @@
         <v>1781.7</v>
       </c>
       <c r="M17">
-        <v>491.4424619999999</v>
+        <v>469.3742339999999</v>
       </c>
       <c r="N17">
-        <v>1290.257538</v>
+        <v>1312.325766</v>
       </c>
       <c r="O17">
-        <v>283.85665836</v>
+        <v>288.71166852</v>
       </c>
       <c r="P17">
-        <v>1006.40087964</v>
+        <v>1023.61409748</v>
       </c>
       <c r="Q17">
-        <v>1842.60087964</v>
+        <v>1859.81409748</v>
       </c>
       <c r="R17">
         <v>0.1764705882352941</v>
       </c>
       <c r="S17">
-        <v>0.08621188672865021</v>
+        <v>0.086185905478526</v>
       </c>
       <c r="T17">
         <v>0.9326998955779677</v>
       </c>
       <c r="U17">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V17">
         <v>0.22</v>
       </c>
       <c r="W17">
-        <v>0.045162</v>
+        <v>0.04313400000000001</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2725,7 +3079,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>3.62544984971201</v>
+        <v>3.795904996353081</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2736,13 +3090,13 @@
         <v>0.16</v>
       </c>
       <c r="B18">
-        <v>0.07996987456921557</v>
+        <v>0.07962336074956525</v>
       </c>
       <c r="C18">
-        <v>47676.40125552231</v>
+        <v>48182.72965168901</v>
       </c>
       <c r="D18">
-        <v>55452.63325552231</v>
+        <v>55958.961651689</v>
       </c>
       <c r="E18">
         <v>2258.531999999999</v>
@@ -2769,37 +3123,37 @@
         <v>1781.7</v>
       </c>
       <c r="M18">
-        <v>524.2052927999999</v>
+        <v>500.6658496</v>
       </c>
       <c r="N18">
-        <v>1257.4947072</v>
+        <v>1281.0341504</v>
       </c>
       <c r="O18">
-        <v>276.648835584</v>
+        <v>281.827513088</v>
       </c>
       <c r="P18">
-        <v>980.8458716160001</v>
+        <v>999.2066373120001</v>
       </c>
       <c r="Q18">
-        <v>1817.045871616</v>
+        <v>1835.406637312</v>
       </c>
       <c r="R18">
         <v>0.1904761904761905</v>
       </c>
       <c r="S18">
-        <v>0.08659994591573283</v>
+        <v>0.08657371517805387</v>
       </c>
       <c r="T18">
         <v>0.9416562396779187</v>
       </c>
       <c r="U18">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V18">
         <v>0.22</v>
       </c>
       <c r="W18">
-        <v>0.045162</v>
+        <v>0.04313400000000001</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2807,7 +3161,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>3.398859234105009</v>
+        <v>3.558660934081013</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2818,13 +3172,13 @@
         <v>0.17</v>
       </c>
       <c r="B19">
-        <v>0.07988534541907846</v>
+        <v>0.07951860184238341</v>
       </c>
       <c r="C19">
-        <v>47241.64416914621</v>
+        <v>47782.42858052348</v>
       </c>
       <c r="D19">
-        <v>55583.7281691462</v>
+        <v>56124.51258052348</v>
       </c>
       <c r="E19">
         <v>2824.384</v>
@@ -2851,37 +3205,37 @@
         <v>1781.7</v>
       </c>
       <c r="M19">
-        <v>556.9681236</v>
+        <v>531.9574652</v>
       </c>
       <c r="N19">
-        <v>1224.7318764</v>
+        <v>1249.7425348</v>
       </c>
       <c r="O19">
-        <v>269.441012808</v>
+        <v>274.943357656</v>
       </c>
       <c r="P19">
-        <v>955.2908635920001</v>
+        <v>974.7991771440002</v>
       </c>
       <c r="Q19">
-        <v>1791.490863592</v>
+        <v>1810.999177144</v>
       </c>
       <c r="R19">
         <v>0.2048192771084338</v>
       </c>
       <c r="S19">
-        <v>0.08699735592660057</v>
+        <v>0.08697086968961856</v>
       </c>
       <c r="T19">
         <v>0.9508283992983504</v>
       </c>
       <c r="U19">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V19">
         <v>0.22</v>
       </c>
       <c r="W19">
-        <v>0.045162</v>
+        <v>0.04313400000000001</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2889,7 +3243,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>3.198926337981185</v>
+        <v>3.349327937958601</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2900,13 +3254,13 @@
         <v>0.18</v>
       </c>
       <c r="B20">
-        <v>0.07980081626894138</v>
+        <v>0.07941384293520157</v>
       </c>
       <c r="C20">
-        <v>46807.50839146439</v>
+        <v>47383.10995906603</v>
       </c>
       <c r="D20">
-        <v>55715.44439146439</v>
+        <v>56291.04595906602</v>
       </c>
       <c r="E20">
         <v>3390.235999999999</v>
@@ -2933,37 +3287,37 @@
         <v>1781.7</v>
       </c>
       <c r="M20">
-        <v>589.7309544</v>
+        <v>563.2490808</v>
       </c>
       <c r="N20">
-        <v>1191.9690456</v>
+        <v>1218.4509192</v>
       </c>
       <c r="O20">
-        <v>262.233190032</v>
+        <v>268.059202224</v>
       </c>
       <c r="P20">
-        <v>929.735855568</v>
+        <v>950.391716976</v>
       </c>
       <c r="Q20">
-        <v>1765.935855568</v>
+        <v>1786.591716976</v>
       </c>
       <c r="R20">
         <v>0.2195121951219512</v>
       </c>
       <c r="S20">
-        <v>0.08740445886456266</v>
+        <v>0.08737771089658727</v>
       </c>
       <c r="T20">
         <v>0.9602242701290364</v>
       </c>
       <c r="U20">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V20">
         <v>0.22</v>
       </c>
       <c r="W20">
-        <v>0.045162</v>
+        <v>0.04313400000000001</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2971,7 +3325,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>3.021208208093342</v>
+        <v>3.163254163627567</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2982,13 +3336,13 @@
         <v>0.19</v>
       </c>
       <c r="B21">
-        <v>0.08010160711880429</v>
+        <v>0.07967958402801972</v>
       </c>
       <c r="C21">
-        <v>45775.77160110358</v>
+        <v>46396.72587669203</v>
       </c>
       <c r="D21">
-        <v>55249.55960110358</v>
+        <v>55870.51387669204</v>
       </c>
       <c r="E21">
         <v>3956.088</v>
@@ -3015,37 +3369,37 @@
         <v>1781.7</v>
       </c>
       <c r="M21">
-        <v>650.446874</v>
+        <v>621.4186664</v>
       </c>
       <c r="N21">
-        <v>1131.253126</v>
+        <v>1160.2813336</v>
       </c>
       <c r="O21">
-        <v>248.87568772</v>
+        <v>255.261893392</v>
       </c>
       <c r="P21">
-        <v>882.3774382800001</v>
+        <v>905.0194402079999</v>
       </c>
       <c r="Q21">
-        <v>1718.57743828</v>
+        <v>1741.219440208</v>
       </c>
       <c r="R21">
         <v>0.2345679012345679</v>
       </c>
       <c r="S21">
-        <v>0.08782161372691887</v>
+        <v>0.08779459756545645</v>
       </c>
       <c r="T21">
         <v>0.9698521377703568</v>
       </c>
       <c r="U21">
-        <v>0.0605</v>
+        <v>0.0578</v>
       </c>
       <c r="V21">
         <v>0.22</v>
       </c>
       <c r="W21">
-        <v>0.04719</v>
+        <v>0.04508400000000001</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3053,7 +3407,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>2.739193731600592</v>
+        <v>2.867149148128647</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3064,13 +3418,13 @@
         <v>0.2</v>
       </c>
       <c r="B22">
-        <v>0.08003735796866719</v>
+        <v>0.07959432512083789</v>
       </c>
       <c r="C22">
-        <v>45308.77739339485</v>
+        <v>45965.1088603879</v>
       </c>
       <c r="D22">
-        <v>55348.41739339485</v>
+        <v>56004.7488603879</v>
       </c>
       <c r="E22">
         <v>4521.940000000001</v>
@@ -3097,37 +3451,37 @@
         <v>1781.7</v>
       </c>
       <c r="M22">
-        <v>684.68092</v>
+        <v>654.1249120000001</v>
       </c>
       <c r="N22">
-        <v>1097.01908</v>
+        <v>1127.575088</v>
       </c>
       <c r="O22">
-        <v>241.3441976</v>
+        <v>248.06651936</v>
       </c>
       <c r="P22">
-        <v>855.6748824</v>
+        <v>879.50856864</v>
       </c>
       <c r="Q22">
-        <v>1691.8748824</v>
+        <v>1715.70856864</v>
       </c>
       <c r="R22">
         <v>0.25</v>
       </c>
       <c r="S22">
-        <v>0.08824919746083398</v>
+        <v>0.08822190640104735</v>
       </c>
       <c r="T22">
         <v>0.9797207021027102</v>
       </c>
       <c r="U22">
-        <v>0.0605</v>
+        <v>0.0578</v>
       </c>
       <c r="V22">
         <v>0.22</v>
       </c>
       <c r="W22">
-        <v>0.04719</v>
+        <v>0.04508400000000001</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3135,7 +3489,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>2.602234045020563</v>
+        <v>2.723791690722215</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3146,13 +3500,13 @@
         <v>0.21</v>
       </c>
       <c r="B23">
-        <v>0.08041536881853008</v>
+        <v>0.07950906621365603</v>
       </c>
       <c r="C23">
-        <v>44166.32345095893</v>
+        <v>45534.13842585089</v>
       </c>
       <c r="D23">
-        <v>54771.81545095893</v>
+        <v>56139.63042585089</v>
       </c>
       <c r="E23">
         <v>5087.791999999999</v>
@@ -3179,45 +3533,45 @@
         <v>1781.7</v>
       </c>
       <c r="M23">
-        <v>750.9987744000001</v>
+        <v>686.8311576</v>
       </c>
       <c r="N23">
-        <v>1030.7012256</v>
+        <v>1094.8688424</v>
       </c>
       <c r="O23">
-        <v>226.754269632</v>
+        <v>240.871145328</v>
       </c>
       <c r="P23">
-        <v>803.9469559679999</v>
+        <v>853.9976970720002</v>
       </c>
       <c r="Q23">
-        <v>1640.146955968</v>
+        <v>1690.197697072</v>
       </c>
       <c r="R23">
         <v>0.2658227848101266</v>
       </c>
       <c r="S23">
-        <v>0.08868760609940515</v>
+        <v>0.08866003318184307</v>
       </c>
       <c r="T23">
         <v>0.9898391035067685</v>
       </c>
       <c r="U23">
-        <v>0.06320000000000001</v>
+        <v>0.0578</v>
       </c>
       <c r="V23">
         <v>0.22</v>
       </c>
       <c r="W23">
-        <v>0.04929600000000001</v>
+        <v>0.04508400000000001</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y23">
-        <v>2.372440622720675</v>
+        <v>2.594087324497348</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3228,13 +3582,13 @@
         <v>0.22</v>
       </c>
       <c r="B24">
-        <v>0.08037217966839298</v>
+        <v>0.08002440730647419</v>
       </c>
       <c r="C24">
-        <v>43665.74175764262</v>
+        <v>44162.76759461478</v>
       </c>
       <c r="D24">
-        <v>54837.08575764262</v>
+        <v>55334.11159461478</v>
       </c>
       <c r="E24">
         <v>5653.643999999998</v>
@@ -3261,37 +3615,37 @@
         <v>1781.7</v>
       </c>
       <c r="M24">
-        <v>786.7606208</v>
+        <v>763.1080072</v>
       </c>
       <c r="N24">
-        <v>994.9393792000001</v>
+        <v>1018.5919928</v>
       </c>
       <c r="O24">
-        <v>218.886663424</v>
+        <v>224.090238416</v>
       </c>
       <c r="P24">
-        <v>776.052715776</v>
+        <v>794.501754384</v>
       </c>
       <c r="Q24">
-        <v>1612.252715776</v>
+        <v>1630.701754384</v>
       </c>
       <c r="R24">
         <v>0.282051282051282</v>
       </c>
       <c r="S24">
-        <v>0.08913725598511921</v>
+        <v>0.08910939398265921</v>
       </c>
       <c r="T24">
         <v>1.000216951100675</v>
       </c>
       <c r="U24">
-        <v>0.06320000000000001</v>
+        <v>0.0613</v>
       </c>
       <c r="V24">
         <v>0.22</v>
       </c>
       <c r="W24">
-        <v>0.04929600000000001</v>
+        <v>0.047814</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3299,7 +3653,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>2.264602412597009</v>
+        <v>2.334794004504583</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3310,13 +3664,13 @@
         <v>0.23</v>
       </c>
       <c r="B25">
-        <v>0.08117217051825588</v>
+        <v>0.08046876839929236</v>
       </c>
       <c r="C25">
-        <v>41915.59129018788</v>
+        <v>42920.67673191128</v>
       </c>
       <c r="D25">
-        <v>53652.78729018787</v>
+        <v>54657.87273191127</v>
       </c>
       <c r="E25">
         <v>6219.495999999999</v>
@@ -3343,37 +3697,37 @@
         <v>1781.7</v>
       </c>
       <c r="M25">
-        <v>883.6910683999999</v>
+        <v>834.2356036</v>
       </c>
       <c r="N25">
-        <v>898.0089316000001</v>
+        <v>947.4643964000001</v>
       </c>
       <c r="O25">
-        <v>197.561964952</v>
+        <v>208.442167208</v>
       </c>
       <c r="P25">
-        <v>700.4469666480001</v>
+        <v>739.0222291920001</v>
       </c>
       <c r="Q25">
-        <v>1536.646966648</v>
+        <v>1575.222229192</v>
       </c>
       <c r="R25">
         <v>0.2987012987012987</v>
       </c>
       <c r="S25">
-        <v>0.089598585088644</v>
+        <v>0.08957042649258747</v>
       </c>
       <c r="T25">
         <v>1.01086435317754</v>
       </c>
       <c r="U25">
-        <v>0.0679</v>
+        <v>0.0641</v>
       </c>
       <c r="V25">
         <v>0.22</v>
       </c>
       <c r="W25">
-        <v>0.052962</v>
+        <v>0.04999800000000001</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3381,7 +3735,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>2.016202340062035</v>
+        <v>2.135727595791142</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3392,13 +3746,13 @@
         <v>0.24</v>
       </c>
       <c r="B26">
-        <v>0.08378644136811879</v>
+        <v>0.0804326494921105</v>
       </c>
       <c r="C26">
-        <v>37812.80122319389</v>
+        <v>42409.17355061348</v>
       </c>
       <c r="D26">
-        <v>50115.84922319389</v>
+        <v>54712.22155061347</v>
       </c>
       <c r="E26">
         <v>6785.347999999998</v>
@@ -3425,45 +3779,45 @@
         <v>1781.7</v>
       </c>
       <c r="M26">
-        <v>1112.2386912</v>
+        <v>870.5067167999999</v>
       </c>
       <c r="N26">
-        <v>669.4613088000001</v>
+        <v>911.1932832000001</v>
       </c>
       <c r="O26">
-        <v>147.281487936</v>
+        <v>200.462522304</v>
       </c>
       <c r="P26">
-        <v>522.179820864</v>
+        <v>710.7307608960001</v>
       </c>
       <c r="Q26">
-        <v>1358.379820864</v>
+        <v>1546.930760896</v>
       </c>
       <c r="R26">
         <v>0.3157894736842105</v>
       </c>
       <c r="S26">
-        <v>0.09007205443173524</v>
+        <v>0.09004359143698751</v>
       </c>
       <c r="T26">
         <v>1.021791950045901</v>
       </c>
       <c r="U26">
-        <v>0.0819</v>
+        <v>0.0641</v>
       </c>
       <c r="V26">
         <v>0.22</v>
       </c>
       <c r="W26">
-        <v>0.06388200000000001</v>
+        <v>0.04999800000000001</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y26">
-        <v>1.601904352093448</v>
+        <v>2.046738945966511</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3474,13 +3828,13 @@
         <v>0.25</v>
       </c>
       <c r="B27">
-        <v>0.08388911221798168</v>
+        <v>0.08191753058492866</v>
       </c>
       <c r="C27">
-        <v>37117.5344360287</v>
+        <v>39694.60667683034</v>
       </c>
       <c r="D27">
-        <v>49986.43443602869</v>
+        <v>52563.50667683034</v>
       </c>
       <c r="E27">
         <v>7351.199999999999</v>
@@ -3507,45 +3861,45 @@
         <v>1781.7</v>
       </c>
       <c r="M27">
-        <v>1158.58197</v>
+        <v>1017.11897</v>
       </c>
       <c r="N27">
-        <v>623.1180300000001</v>
+        <v>764.5810300000001</v>
       </c>
       <c r="O27">
-        <v>137.0859666</v>
+        <v>168.2078266</v>
       </c>
       <c r="P27">
-        <v>486.0320634000001</v>
+        <v>596.3732034000001</v>
       </c>
       <c r="Q27">
-        <v>1322.2320634</v>
+        <v>1432.5732034</v>
       </c>
       <c r="R27">
         <v>0.3333333333333333</v>
       </c>
       <c r="S27">
-        <v>0.09055814962397557</v>
+        <v>0.09052937411323821</v>
       </c>
       <c r="T27">
         <v>1.033010949497418</v>
       </c>
       <c r="U27">
-        <v>0.0819</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V27">
         <v>0.22</v>
       </c>
       <c r="W27">
-        <v>0.06388200000000001</v>
+        <v>0.05608200000000001</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y27">
-        <v>1.53782817800971</v>
+        <v>1.751712486495066</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3556,13 +3910,13 @@
         <v>0.26</v>
       </c>
       <c r="B28">
-        <v>0.09464137363277617</v>
+        <v>0.08273317167774683</v>
       </c>
       <c r="C28">
-        <v>25911.19605032925</v>
+        <v>38018.77003649347</v>
       </c>
       <c r="D28">
-        <v>39345.94805032925</v>
+        <v>51453.52203649347</v>
       </c>
       <c r="E28">
         <v>7917.052</v>
@@ -3589,45 +3943,45 @@
         <v>1781.7</v>
       </c>
       <c r="M28">
-        <v>1925.8206968</v>
+        <v>1115.1811216</v>
       </c>
       <c r="N28">
-        <v>-144.1206967999999</v>
+        <v>666.5188783999999</v>
       </c>
       <c r="O28">
-        <v>-31.70655329599998</v>
+        <v>146.634153248</v>
       </c>
       <c r="P28">
-        <v>-112.4141435039999</v>
+        <v>519.884725152</v>
       </c>
       <c r="Q28">
-        <v>723.7858564960002</v>
+        <v>1356.084725152</v>
       </c>
       <c r="R28">
         <v>0.3513513513513514</v>
       </c>
       <c r="S28">
-        <v>0.09126286575759582</v>
+        <v>0.09102828605100921</v>
       </c>
       <c r="T28">
-        <v>1.049275685382015</v>
+        <v>1.044533165150328</v>
       </c>
       <c r="U28">
-        <v>0.1309</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V28">
-        <v>0.203536082383638</v>
+        <v>0.22</v>
       </c>
       <c r="W28">
-        <v>0.1042571268159818</v>
+        <v>0.05912400000000001</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y28">
-        <v>0.9251640108347183</v>
+        <v>1.597677691533834</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3638,13 +3992,13 @@
         <v>0.27</v>
       </c>
       <c r="B29">
-        <v>0.09549237363277618</v>
+        <v>0.08278831277056496</v>
       </c>
       <c r="C29">
-        <v>24693.44072586487</v>
+        <v>37379.56730360111</v>
       </c>
       <c r="D29">
-        <v>38694.04472586487</v>
+        <v>51380.17130360111</v>
       </c>
       <c r="E29">
         <v>8482.904</v>
@@ -3671,45 +4025,45 @@
         <v>1781.7</v>
       </c>
       <c r="M29">
-        <v>1999.8907236</v>
+        <v>1158.0727032</v>
       </c>
       <c r="N29">
-        <v>-218.1907236</v>
+        <v>623.6272967999998</v>
       </c>
       <c r="O29">
-        <v>-48.00195919199999</v>
+        <v>137.198005296</v>
       </c>
       <c r="P29">
-        <v>-170.188764408</v>
+        <v>486.4292915039999</v>
       </c>
       <c r="Q29">
-        <v>666.011235592</v>
+        <v>1322.629291504</v>
       </c>
       <c r="R29">
         <v>0.3698630136986302</v>
       </c>
       <c r="S29">
-        <v>0.0918856447405766</v>
+        <v>0.09154086680899311</v>
       </c>
       <c r="T29">
-        <v>1.063649324907796</v>
+        <v>1.056371057944414</v>
       </c>
       <c r="U29">
-        <v>0.1309</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V29">
-        <v>0.1959977089620218</v>
+        <v>0.22</v>
       </c>
       <c r="W29">
-        <v>0.1052438998968713</v>
+        <v>0.05912400000000001</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y29">
-        <v>0.8908986771000992</v>
+        <v>1.538504443699247</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3720,13 +4074,13 @@
         <v>0.28</v>
       </c>
       <c r="B30">
-        <v>0.09634337363277617</v>
+        <v>0.09268291375325338</v>
       </c>
       <c r="C30">
-        <v>23496.93544008212</v>
+        <v>26347.61370008667</v>
       </c>
       <c r="D30">
-        <v>38063.39144008212</v>
+        <v>40914.06970008666</v>
       </c>
       <c r="E30">
         <v>9048.756000000001</v>
@@ -3753,37 +4107,37 @@
         <v>1781.7</v>
       </c>
       <c r="M30">
-        <v>2073.9607504</v>
+        <v>1879.0813216</v>
       </c>
       <c r="N30">
-        <v>-292.2607504</v>
+        <v>-97.38132160000032</v>
       </c>
       <c r="O30">
-        <v>-64.29736508800001</v>
+        <v>-21.42389075200007</v>
       </c>
       <c r="P30">
-        <v>-227.963385312</v>
+        <v>-75.95743084800026</v>
       </c>
       <c r="Q30">
-        <v>608.236614688</v>
+        <v>760.2425691519998</v>
       </c>
       <c r="R30">
         <v>0.388888888888889</v>
       </c>
       <c r="S30">
-        <v>0.09252572313975127</v>
+        <v>0.09222508441819183</v>
       </c>
       <c r="T30">
-        <v>1.078422232198182</v>
+        <v>1.072172850304661</v>
       </c>
       <c r="U30">
-        <v>0.1309</v>
+        <v>0.1186</v>
       </c>
       <c r="V30">
-        <v>0.1889977907848067</v>
+        <v>0.2085987421056593</v>
       </c>
       <c r="W30">
-        <v>0.1061601891862688</v>
+        <v>0.09386018918626882</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3791,7 +4145,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>0.8590808672036671</v>
+        <v>0.9481761004802698</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3802,13 +4156,13 @@
         <v>0.29</v>
       </c>
       <c r="B31">
-        <v>0.09719437363277617</v>
+        <v>0.09341091375325339</v>
       </c>
       <c r="C31">
-        <v>22320.65782733838</v>
+        <v>25177.62589087673</v>
       </c>
       <c r="D31">
-        <v>37452.96582733838</v>
+        <v>40309.93389087672</v>
       </c>
       <c r="E31">
         <v>9614.607999999998</v>
@@ -3835,37 +4189,37 @@
         <v>1781.7</v>
       </c>
       <c r="M31">
-        <v>2148.0307772</v>
+        <v>1946.1913688</v>
       </c>
       <c r="N31">
-        <v>-366.3307771999996</v>
+        <v>-164.4913687999999</v>
       </c>
       <c r="O31">
-        <v>-80.59277098399991</v>
+        <v>-36.18810113599998</v>
       </c>
       <c r="P31">
-        <v>-285.7380062159997</v>
+        <v>-128.3032676639999</v>
       </c>
       <c r="Q31">
-        <v>550.4619937840004</v>
+        <v>707.8967323360001</v>
       </c>
       <c r="R31">
         <v>0.4084507042253521</v>
       </c>
       <c r="S31">
-        <v>0.09318383191636748</v>
+        <v>0.09287895884661707</v>
       </c>
       <c r="T31">
-        <v>1.0936112777221</v>
+        <v>1.08727387636529</v>
       </c>
       <c r="U31">
-        <v>0.1309</v>
+        <v>0.1186</v>
       </c>
       <c r="V31">
-        <v>0.1824806255853307</v>
+        <v>0.2014056820330505</v>
       </c>
       <c r="W31">
-        <v>0.1070132861108802</v>
+        <v>0.09471328611088023</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3873,7 +4227,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>0.8294573890242304</v>
+        <v>0.9154803728775021</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3884,13 +4238,13 @@
         <v>0.3</v>
       </c>
       <c r="B32">
-        <v>0.09804537363277616</v>
+        <v>0.09413891375325338</v>
       </c>
       <c r="C32">
-        <v>21163.65006986568</v>
+        <v>24025.21977006074</v>
       </c>
       <c r="D32">
-        <v>36861.81006986568</v>
+        <v>39723.37977006073</v>
       </c>
       <c r="E32">
         <v>10180.46</v>
@@ -3917,37 +4271,37 @@
         <v>1781.7</v>
       </c>
       <c r="M32">
-        <v>2222.100804</v>
+        <v>2013.301416</v>
       </c>
       <c r="N32">
-        <v>-440.4008039999997</v>
+        <v>-231.601416</v>
       </c>
       <c r="O32">
-        <v>-96.88817687999992</v>
+        <v>-50.95231151999999</v>
       </c>
       <c r="P32">
-        <v>-343.5126271199997</v>
+        <v>-180.64910448</v>
       </c>
       <c r="Q32">
-        <v>492.6873728800003</v>
+        <v>655.55089552</v>
       </c>
       <c r="R32">
         <v>0.4285714285714286</v>
       </c>
       <c r="S32">
-        <v>0.09386074380088702</v>
+        <v>0.09355151540156874</v>
       </c>
       <c r="T32">
-        <v>1.109234295975273</v>
+        <v>1.102806360313366</v>
       </c>
       <c r="U32">
-        <v>0.1309</v>
+        <v>0.1186</v>
       </c>
       <c r="V32">
-        <v>0.1763979380658197</v>
+        <v>0.1946921592986154</v>
       </c>
       <c r="W32">
-        <v>0.1078095099071842</v>
+        <v>0.09550950990718421</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3955,7 +4309,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.8018088093900894</v>
+        <v>0.884964360448252</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3966,13 +4320,13 @@
         <v>0.31</v>
       </c>
       <c r="B33">
-        <v>0.1259549322258527</v>
+        <v>0.09486691375325339</v>
       </c>
       <c r="C33">
-        <v>8024.675211775568</v>
+        <v>22889.63884638869</v>
       </c>
       <c r="D33">
-        <v>24288.68721177557</v>
+        <v>39153.65084638869</v>
       </c>
       <c r="E33">
         <v>10746.312</v>
@@ -3999,45 +4353,45 @@
         <v>1781.7</v>
       </c>
       <c r="M33">
-        <v>3785.436709600001</v>
+        <v>2080.4114632</v>
       </c>
       <c r="N33">
-        <v>-2003.7367096</v>
+        <v>-298.7114632</v>
       </c>
       <c r="O33">
-        <v>-440.8220761120001</v>
+        <v>-65.716521904</v>
       </c>
       <c r="P33">
-        <v>-1562.914633488</v>
+        <v>-232.994941296</v>
       </c>
       <c r="Q33">
-        <v>-726.7146334880003</v>
+        <v>603.2050587040001</v>
       </c>
       <c r="R33">
         <v>0.4492753623188406</v>
       </c>
       <c r="S33">
-        <v>0.09562910036767752</v>
+        <v>0.09424356634941757</v>
       </c>
       <c r="T33">
-        <v>1.150047683290367</v>
+        <v>1.118789061187473</v>
       </c>
       <c r="U33">
-        <v>0.2158</v>
+        <v>0.1186</v>
       </c>
       <c r="V33">
-        <v>0.1035478942247113</v>
+        <v>0.1884117670631762</v>
       </c>
       <c r="W33">
-        <v>0.1934543644263073</v>
+        <v>0.09625436442630732</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y33">
-        <v>0.4706722464759604</v>
+        <v>0.8564171230144373</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4048,13 +4402,13 @@
         <v>0.32</v>
       </c>
       <c r="B34">
-        <v>0.1276549322258528</v>
+        <v>0.09559491375325338</v>
       </c>
       <c r="C34">
-        <v>6964.471506482994</v>
+        <v>21770.16941458171</v>
       </c>
       <c r="D34">
-        <v>23794.33550648299</v>
+        <v>38600.03341458171</v>
       </c>
       <c r="E34">
         <v>11312.164</v>
@@ -4081,45 +4435,45 @@
         <v>1781.7</v>
       </c>
       <c r="M34">
-        <v>3907.5475712</v>
+        <v>2147.5215104</v>
       </c>
       <c r="N34">
-        <v>-2125.8475712</v>
+        <v>-365.8215103999999</v>
       </c>
       <c r="O34">
-        <v>-467.686465664</v>
+        <v>-80.48073228799997</v>
       </c>
       <c r="P34">
-        <v>-1658.161105536</v>
+        <v>-285.3407781119999</v>
       </c>
       <c r="Q34">
-        <v>-821.9611055359999</v>
+        <v>550.8592218880001</v>
       </c>
       <c r="R34">
         <v>0.4705882352941177</v>
       </c>
       <c r="S34">
-        <v>0.09636188125543747</v>
+        <v>0.09495597173690899</v>
       </c>
       <c r="T34">
-        <v>1.166960149221107</v>
+        <v>1.135241841499053</v>
       </c>
       <c r="U34">
-        <v>0.2158</v>
+        <v>0.1186</v>
       </c>
       <c r="V34">
-        <v>0.1003120225301891</v>
+        <v>0.182523899342452</v>
       </c>
       <c r="W34">
-        <v>0.1941526655379852</v>
+        <v>0.09695266553798521</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y34">
-        <v>0.4559637387735868</v>
+        <v>0.8296540879202362</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4130,13 +4484,13 @@
         <v>0.33</v>
       </c>
       <c r="B35">
-        <v>0.1293549322258528</v>
+        <v>0.09632291375325337</v>
       </c>
       <c r="C35">
-        <v>5923.989644774119</v>
+        <v>20666.13757262117</v>
       </c>
       <c r="D35">
-        <v>23319.70564477412</v>
+        <v>38061.85357262117</v>
       </c>
       <c r="E35">
         <v>11878.016</v>
@@ -4163,45 +4517,45 @@
         <v>1781.7</v>
       </c>
       <c r="M35">
-        <v>4029.6584328</v>
+        <v>2214.6315576</v>
       </c>
       <c r="N35">
-        <v>-2247.9584328</v>
+        <v>-432.9315576000001</v>
       </c>
       <c r="O35">
-        <v>-494.550855216</v>
+        <v>-95.24494267200004</v>
       </c>
       <c r="P35">
-        <v>-1753.407577584</v>
+        <v>-337.6866149280001</v>
       </c>
       <c r="Q35">
-        <v>-917.2075775840001</v>
+        <v>498.5133850719999</v>
       </c>
       <c r="R35">
         <v>0.4925373134328359</v>
       </c>
       <c r="S35">
-        <v>0.09711653619954849</v>
+        <v>0.09568964295686286</v>
       </c>
       <c r="T35">
-        <v>1.184377464881124</v>
+        <v>1.152185749581129</v>
       </c>
       <c r="U35">
-        <v>0.2158</v>
+        <v>0.1186</v>
       </c>
       <c r="V35">
-        <v>0.09727226427169851</v>
+        <v>0.1769928720896504</v>
       </c>
       <c r="W35">
-        <v>0.1948086453701675</v>
+        <v>0.09760864537016749</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y35">
-        <v>0.4421466557804477</v>
+        <v>0.8045130549529562</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4212,13 +4566,13 @@
         <v>0.34</v>
       </c>
       <c r="B36">
-        <v>0.1310549322258527</v>
+        <v>0.1258477034551138</v>
       </c>
       <c r="C36">
-        <v>4902.072522204984</v>
+        <v>6352.094411330028</v>
       </c>
       <c r="D36">
-        <v>22863.64052220498</v>
+        <v>24313.66241133003</v>
       </c>
       <c r="E36">
         <v>12443.868</v>
@@ -4245,37 +4599,37 @@
         <v>1781.7</v>
       </c>
       <c r="M36">
-        <v>4151.769294400001</v>
+        <v>3863.1847744</v>
       </c>
       <c r="N36">
-        <v>-2370.069294400001</v>
+        <v>-2081.4847744</v>
       </c>
       <c r="O36">
-        <v>-521.4152447680002</v>
+        <v>-457.926650368</v>
       </c>
       <c r="P36">
-        <v>-1848.654049632001</v>
+        <v>-1623.558124032</v>
       </c>
       <c r="Q36">
-        <v>-1012.454049632001</v>
+        <v>-787.3581240319998</v>
       </c>
       <c r="R36">
         <v>0.5151515151515152</v>
       </c>
       <c r="S36">
-        <v>0.09789405947529922</v>
+        <v>0.09773159164084619</v>
       </c>
       <c r="T36">
-        <v>1.202322577985383</v>
+        <v>1.199343917802452</v>
       </c>
       <c r="U36">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V36">
-        <v>0.09441131532253087</v>
+        <v>0.1014639534193335</v>
       </c>
       <c r="W36">
-        <v>0.1954260381533978</v>
+        <v>0.1804260381533979</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4283,7 +4637,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.4291423423751403</v>
+        <v>0.4611997882696978</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4294,13 +4648,13 @@
         <v>0.35</v>
       </c>
       <c r="B37">
-        <v>0.1327549322258528</v>
+        <v>0.1273977034551138</v>
       </c>
       <c r="C37">
-        <v>3897.651816308022</v>
+        <v>5333.769480477567</v>
       </c>
       <c r="D37">
-        <v>22425.07181630802</v>
+        <v>23861.18948047757</v>
       </c>
       <c r="E37">
         <v>13009.72</v>
@@ -4327,37 +4681,37 @@
         <v>1781.7</v>
       </c>
       <c r="M37">
-        <v>4273.880156</v>
+        <v>3976.807856</v>
       </c>
       <c r="N37">
-        <v>-2492.180156</v>
+        <v>-2195.107856</v>
       </c>
       <c r="O37">
-        <v>-548.2796343200001</v>
+        <v>-482.9237283199999</v>
       </c>
       <c r="P37">
-        <v>-1943.90052168</v>
+        <v>-1712.18412768</v>
       </c>
       <c r="Q37">
-        <v>-1107.70052168</v>
+        <v>-875.9841276799996</v>
       </c>
       <c r="R37">
         <v>0.5384615384615385</v>
       </c>
       <c r="S37">
-        <v>0.09869550654414999</v>
+        <v>0.09853053920455151</v>
       </c>
       <c r="T37">
-        <v>1.220819848415928</v>
+        <v>1.217795362691721</v>
       </c>
       <c r="U37">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V37">
-        <v>0.09171384917045858</v>
+        <v>0.09856498332163827</v>
       </c>
       <c r="W37">
-        <v>0.1960081513490151</v>
+        <v>0.181008151349015</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4365,7 +4719,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.4168811325929935</v>
+        <v>0.4480226514619922</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4376,13 +4730,13 @@
         <v>0.36</v>
       </c>
       <c r="B38">
-        <v>0.1344549322258528</v>
+        <v>0.1289477034551137</v>
       </c>
       <c r="C38">
-        <v>2909.739631805707</v>
+        <v>4331.977751138027</v>
       </c>
       <c r="D38">
-        <v>22003.0116318057</v>
+        <v>23425.24975113802</v>
       </c>
       <c r="E38">
         <v>13575.572</v>
@@ -4409,37 +4763,37 @@
         <v>1781.7</v>
       </c>
       <c r="M38">
-        <v>4395.9910176</v>
+        <v>4090.4309376</v>
       </c>
       <c r="N38">
-        <v>-2614.2910176</v>
+        <v>-2308.730937599999</v>
       </c>
       <c r="O38">
-        <v>-575.1440238720002</v>
+        <v>-507.9208062719999</v>
       </c>
       <c r="P38">
-        <v>-2039.146993728</v>
+        <v>-1800.810131327999</v>
       </c>
       <c r="Q38">
-        <v>-1202.946993728</v>
+        <v>-964.6101313279994</v>
       </c>
       <c r="R38">
         <v>0.5625</v>
       </c>
       <c r="S38">
-        <v>0.09952199883390231</v>
+        <v>0.09935445387962263</v>
       </c>
       <c r="T38">
-        <v>1.239895158547426</v>
+        <v>1.236823415233779</v>
       </c>
       <c r="U38">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V38">
-        <v>0.08916624224905696</v>
+        <v>0.09582706711825943</v>
       </c>
       <c r="W38">
-        <v>0.1965579249226535</v>
+        <v>0.1815579249226535</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4447,7 +4801,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.405301101132077</v>
+        <v>0.4355775778102702</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4458,13 +4812,13 @@
         <v>0.37</v>
       </c>
       <c r="B39">
-        <v>0.1361549322258528</v>
+        <v>0.1304977034551137</v>
       </c>
       <c r="C39">
-        <v>1937.421071862987</v>
+        <v>3345.829305906296</v>
       </c>
       <c r="D39">
-        <v>21596.54507186298</v>
+        <v>23004.95330590629</v>
       </c>
       <c r="E39">
         <v>14141.424</v>
@@ -4491,37 +4845,37 @@
         <v>1781.7</v>
       </c>
       <c r="M39">
-        <v>4518.1018792</v>
+        <v>4204.0540192</v>
       </c>
       <c r="N39">
-        <v>-2736.4018792</v>
+        <v>-2422.3540192</v>
       </c>
       <c r="O39">
-        <v>-602.008413424</v>
+        <v>-532.917884224</v>
       </c>
       <c r="P39">
-        <v>-2134.393465776</v>
+        <v>-1889.436134976</v>
       </c>
       <c r="Q39">
-        <v>-1298.193465776</v>
+        <v>-1053.236134976</v>
       </c>
       <c r="R39">
         <v>0.5873015873015873</v>
       </c>
       <c r="S39">
-        <v>0.100374728974123</v>
+        <v>0.1002045245761246</v>
       </c>
       <c r="T39">
-        <v>1.259576034079925</v>
+        <v>1.256455532935902</v>
       </c>
       <c r="U39">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V39">
-        <v>0.08675634380989326</v>
+        <v>0.09323714638533349</v>
       </c>
       <c r="W39">
-        <v>0.197077981005825</v>
+        <v>0.182077981005825</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4529,7 +4883,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.3943470173176966</v>
+        <v>0.423805210842425</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4540,13 +4894,13 @@
         <v>0.38</v>
       </c>
       <c r="B40">
-        <v>0.1378549322258528</v>
+        <v>0.1320477034551137</v>
       </c>
       <c r="C40">
-        <v>979.8476178025157</v>
+        <v>2374.496969344887</v>
       </c>
       <c r="D40">
-        <v>21204.82361780251</v>
+        <v>22599.47296934489</v>
       </c>
       <c r="E40">
         <v>14707.276</v>
@@ -4573,37 +4927,37 @@
         <v>1781.7</v>
       </c>
       <c r="M40">
-        <v>4640.212740800001</v>
+        <v>4317.677100800001</v>
       </c>
       <c r="N40">
-        <v>-2858.512740800001</v>
+        <v>-2535.977100800001</v>
       </c>
       <c r="O40">
-        <v>-628.8728029760001</v>
+        <v>-557.9149621760001</v>
       </c>
       <c r="P40">
-        <v>-2229.639937824001</v>
+        <v>-1978.062138624</v>
       </c>
       <c r="Q40">
-        <v>-1393.439937824001</v>
+        <v>-1141.862138624</v>
       </c>
       <c r="R40">
         <v>0.6129032258064516</v>
       </c>
       <c r="S40">
-        <v>0.1012549665382217</v>
+        <v>0.1010820169079975</v>
       </c>
       <c r="T40">
-        <v>1.279891776565085</v>
+        <v>1.276720944757449</v>
       </c>
       <c r="U40">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V40">
-        <v>0.08447328213068553</v>
+        <v>0.09078353726992996</v>
       </c>
       <c r="W40">
-        <v>0.1975706657161981</v>
+        <v>0.1825706657161981</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4611,7 +4965,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.3839694642303887</v>
+        <v>0.4126524421360452</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4622,13 +4976,13 @@
         <v>0.39</v>
       </c>
       <c r="B41">
-        <v>0.1395549322258527</v>
+        <v>0.1335977034551137</v>
       </c>
       <c r="C41">
-        <v>36.23121646290747</v>
+        <v>1417.210874373788</v>
       </c>
       <c r="D41">
-        <v>20827.05921646291</v>
+        <v>22208.03887437379</v>
       </c>
       <c r="E41">
         <v>15273.128</v>
@@ -4655,37 +5009,37 @@
         <v>1781.7</v>
       </c>
       <c r="M41">
-        <v>4762.3236024</v>
+        <v>4431.3001824</v>
       </c>
       <c r="N41">
-        <v>-2980.6236024</v>
+        <v>-2649.6001824</v>
       </c>
       <c r="O41">
-        <v>-655.737192528</v>
+        <v>-582.9120401280001</v>
       </c>
       <c r="P41">
-        <v>-2324.886409872</v>
+        <v>-2066.688142272</v>
       </c>
       <c r="Q41">
-        <v>-1488.686409872</v>
+        <v>-1230.488142272</v>
       </c>
       <c r="R41">
         <v>0.639344262295082</v>
       </c>
       <c r="S41">
-        <v>0.1021640643503237</v>
+        <v>0.1019882794802598</v>
       </c>
       <c r="T41">
-        <v>1.300873608967792</v>
+        <v>1.29765079631085</v>
       </c>
       <c r="U41">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V41">
-        <v>0.08230730053759104</v>
+        <v>0.0884557542630087</v>
       </c>
       <c r="W41">
-        <v>0.1980380845439879</v>
+        <v>0.1830380845439879</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4693,7 +5047,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.3741240933526865</v>
+        <v>0.402071610286403</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4704,13 +5058,13 @@
         <v>0.4</v>
       </c>
       <c r="B42">
-        <v>0.1412549322258528</v>
+        <v>0.1351477034551137</v>
       </c>
       <c r="C42">
-        <v>-894.1610115020485</v>
+        <v>473.2535837232135</v>
       </c>
       <c r="D42">
-        <v>20462.51898849795</v>
+        <v>21829.93358372321</v>
       </c>
       <c r="E42">
         <v>15838.98</v>
@@ -4737,37 +5091,37 @@
         <v>1781.7</v>
       </c>
       <c r="M42">
-        <v>4884.434464000001</v>
+        <v>4544.923264000001</v>
       </c>
       <c r="N42">
-        <v>-3102.734464000001</v>
+        <v>-2763.223264000001</v>
       </c>
       <c r="O42">
-        <v>-682.6015820800002</v>
+        <v>-607.9091180800002</v>
       </c>
       <c r="P42">
-        <v>-2420.132881920001</v>
+        <v>-2155.314145920001</v>
       </c>
       <c r="Q42">
-        <v>-1583.932881920001</v>
+        <v>-1319.114145920001</v>
       </c>
       <c r="R42">
         <v>0.6666666666666667</v>
       </c>
       <c r="S42">
-        <v>0.1031034654228292</v>
+        <v>0.1029247508049308</v>
       </c>
       <c r="T42">
-        <v>1.322554835783922</v>
+        <v>1.319278309582697</v>
       </c>
       <c r="U42">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V42">
-        <v>0.08024961802415125</v>
+        <v>0.08624436040643346</v>
       </c>
       <c r="W42">
-        <v>0.1984821324303882</v>
+        <v>0.1834821324303882</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4775,7 +5129,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.3647709910188692</v>
+        <v>0.392019820029243</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4786,13 +5140,13 @@
         <v>0.41</v>
       </c>
       <c r="B43">
-        <v>0.1429549322258528</v>
+        <v>0.1366977034551138</v>
       </c>
       <c r="C43">
-        <v>-1812.011517153573</v>
+        <v>-458.0442985951158</v>
       </c>
       <c r="D43">
-        <v>20110.52048284643</v>
+        <v>21464.48770140488</v>
       </c>
       <c r="E43">
         <v>16404.832</v>
@@ -4819,37 +5173,37 @@
         <v>1781.7</v>
       </c>
       <c r="M43">
-        <v>5006.545325600001</v>
+        <v>4658.546345600001</v>
       </c>
       <c r="N43">
-        <v>-3224.845325600001</v>
+        <v>-2876.846345600001</v>
       </c>
       <c r="O43">
-        <v>-709.4659716320002</v>
+        <v>-632.9061960320001</v>
       </c>
       <c r="P43">
-        <v>-2515.379353968001</v>
+        <v>-2243.940149568001</v>
       </c>
       <c r="Q43">
-        <v>-1679.179353968001</v>
+        <v>-1407.740149568001</v>
       </c>
       <c r="R43">
         <v>0.6949152542372882</v>
       </c>
       <c r="S43">
-        <v>0.1040747105994873</v>
+        <v>0.1038929669202686</v>
       </c>
       <c r="T43">
-        <v>1.344971019441276</v>
+        <v>1.341638958897658</v>
       </c>
       <c r="U43">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V43">
-        <v>0.07829231026746464</v>
+        <v>0.0841408394209107</v>
       </c>
       <c r="W43">
-        <v>0.1989045194442811</v>
+        <v>0.1839045194442812</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4857,7 +5211,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.3558741375793847</v>
+        <v>0.3824583610041394</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4868,13 +5222,13 @@
         <v>0.42</v>
       </c>
       <c r="B44">
-        <v>0.1446549322258527</v>
+        <v>0.1382477034551138</v>
       </c>
       <c r="C44">
-        <v>-2717.956587282439</v>
+        <v>-1377.308082275238</v>
       </c>
       <c r="D44">
-        <v>19770.42741271756</v>
+        <v>21111.07591772476</v>
       </c>
       <c r="E44">
         <v>16970.684</v>
@@ -4901,37 +5255,37 @@
         <v>1781.7</v>
       </c>
       <c r="M44">
-        <v>5128.6561872</v>
+        <v>4772.1694272</v>
       </c>
       <c r="N44">
-        <v>-3346.9561872</v>
+        <v>-2990.469427200001</v>
       </c>
       <c r="O44">
-        <v>-736.3303611840001</v>
+        <v>-657.9032739840002</v>
       </c>
       <c r="P44">
-        <v>-2610.625826016</v>
+        <v>-2332.566153216</v>
       </c>
       <c r="Q44">
-        <v>-1774.425826016</v>
+        <v>-1496.366153216</v>
       </c>
       <c r="R44">
         <v>0.7241379310344827</v>
       </c>
       <c r="S44">
-        <v>0.1050794469891336</v>
+        <v>0.1048945697982043</v>
       </c>
       <c r="T44">
-        <v>1.368160174948884</v>
+        <v>1.364770665085549</v>
       </c>
       <c r="U44">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V44">
-        <v>0.07642820764204883</v>
+        <v>0.0821374861013652</v>
       </c>
       <c r="W44">
-        <v>0.1993067927908459</v>
+        <v>0.1843067927908459</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4939,7 +5293,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.3474009438274945</v>
+        <v>0.37335220955166</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4950,13 +5304,13 @@
         <v>0.43</v>
       </c>
       <c r="B45">
-        <v>0.1463549322258527</v>
+        <v>0.1397977034551137</v>
       </c>
       <c r="C45">
-        <v>-3612.590182960914</v>
+        <v>-2285.122561320932</v>
       </c>
       <c r="D45">
-        <v>19441.64581703908</v>
+        <v>20769.11343867907</v>
       </c>
       <c r="E45">
         <v>17536.536</v>
@@ -4983,37 +5337,37 @@
         <v>1781.7</v>
       </c>
       <c r="M45">
-        <v>5250.7670488</v>
+        <v>4885.7925088</v>
       </c>
       <c r="N45">
-        <v>-3469.067048800001</v>
+        <v>-3104.0925088</v>
       </c>
       <c r="O45">
-        <v>-763.1947507360002</v>
+        <v>-682.9003519360001</v>
       </c>
       <c r="P45">
-        <v>-2705.872298064</v>
+        <v>-2421.192156864</v>
       </c>
       <c r="Q45">
-        <v>-1869.672298064</v>
+        <v>-1584.992156864</v>
       </c>
       <c r="R45">
         <v>0.7543859649122806</v>
       </c>
       <c r="S45">
-        <v>0.1061194372871886</v>
+        <v>0.1059313166367693</v>
       </c>
       <c r="T45">
-        <v>1.392162985035707</v>
+        <v>1.38871401008705</v>
       </c>
       <c r="U45">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V45">
-        <v>0.07465080746432676</v>
+        <v>0.08022731200598462</v>
       </c>
       <c r="W45">
-        <v>0.1996903557491983</v>
+        <v>0.1846903557491983</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5021,7 +5375,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.3393218521105761</v>
+        <v>0.3646696000272028</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5032,13 +5386,13 @@
         <v>0.44</v>
       </c>
       <c r="B46">
-        <v>0.1480549322258528</v>
+        <v>0.1413477034551138</v>
       </c>
       <c r="C46">
-        <v>-4496.467401349943</v>
+        <v>-3182.035243156162</v>
       </c>
       <c r="D46">
-        <v>19123.62059865005</v>
+        <v>20438.05275684383</v>
       </c>
       <c r="E46">
         <v>18102.388</v>
@@ -5065,37 +5419,37 @@
         <v>1781.7</v>
       </c>
       <c r="M46">
-        <v>5372.8779104</v>
+        <v>4999.4155904</v>
       </c>
       <c r="N46">
-        <v>-3591.1779104</v>
+        <v>-3217.7155904</v>
       </c>
       <c r="O46">
-        <v>-790.059140288</v>
+        <v>-707.897429888</v>
       </c>
       <c r="P46">
-        <v>-2801.118770112</v>
+        <v>-2509.818160512</v>
       </c>
       <c r="Q46">
-        <v>-1964.918770112</v>
+        <v>-1673.618160512</v>
       </c>
       <c r="R46">
         <v>0.7857142857142857</v>
       </c>
       <c r="S46">
-        <v>0.1071965700958884</v>
+        <v>0.1070050901481401</v>
       </c>
       <c r="T46">
-        <v>1.417023038339916</v>
+        <v>1.41351247455289</v>
       </c>
       <c r="U46">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V46">
-        <v>0.07295419820377388</v>
+        <v>0.07840396400584862</v>
       </c>
       <c r="W46">
-        <v>0.2000564840276256</v>
+        <v>0.1850564840276256</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5103,7 +5457,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.3316099918353358</v>
+        <v>0.3563816545720391</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5114,13 +5468,13 @@
         <v>0.45</v>
       </c>
       <c r="B47">
-        <v>0.1497549322258528</v>
+        <v>0.1428977034551137</v>
       </c>
       <c r="C47">
-        <v>-5370.107603206659</v>
+        <v>-4068.559273747916</v>
       </c>
       <c r="D47">
-        <v>18815.83239679334</v>
+        <v>20117.38072625208</v>
       </c>
       <c r="E47">
         <v>18668.24</v>
@@ -5147,37 +5501,37 @@
         <v>1781.7</v>
       </c>
       <c r="M47">
-        <v>5494.988772000001</v>
+        <v>5113.038672000001</v>
       </c>
       <c r="N47">
-        <v>-3713.288772000001</v>
+        <v>-3331.338672000001</v>
       </c>
       <c r="O47">
-        <v>-816.9235298400001</v>
+        <v>-732.8945078400002</v>
       </c>
       <c r="P47">
-        <v>-2896.365242160001</v>
+        <v>-2598.444164160001</v>
       </c>
       <c r="Q47">
-        <v>-2060.165242160001</v>
+        <v>-1762.244164160001</v>
       </c>
       <c r="R47">
         <v>0.8181818181818181</v>
       </c>
       <c r="S47">
-        <v>0.1083128713703591</v>
+        <v>0.1081179099690154</v>
       </c>
       <c r="T47">
-        <v>1.44278709358246</v>
+        <v>1.439212701362943</v>
       </c>
       <c r="U47">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V47">
-        <v>0.07133299379924556</v>
+        <v>0.07666165369460752</v>
       </c>
       <c r="W47">
-        <v>0.2004063399381228</v>
+        <v>0.1854063399381228</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5185,7 +5539,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.3242408809056616</v>
+        <v>0.348462062248216</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5196,13 +5550,13 @@
         <v>0.46</v>
       </c>
       <c r="B48">
-        <v>0.1514549322258528</v>
+        <v>0.1444477034551138</v>
       </c>
       <c r="C48">
-        <v>-6233.997243158694</v>
+        <v>-4945.176091612801</v>
       </c>
       <c r="D48">
-        <v>18517.7947568413</v>
+        <v>19806.6159083872</v>
       </c>
       <c r="E48">
         <v>19234.092</v>
@@ -5229,37 +5583,37 @@
         <v>1781.7</v>
       </c>
       <c r="M48">
-        <v>5617.099633600001</v>
+        <v>5226.6617536</v>
       </c>
       <c r="N48">
-        <v>-3835.399633600001</v>
+        <v>-3444.961753600001</v>
       </c>
       <c r="O48">
-        <v>-843.7879193920002</v>
+        <v>-757.8915857920001</v>
       </c>
       <c r="P48">
-        <v>-2991.611714208001</v>
+        <v>-2687.070167808</v>
       </c>
       <c r="Q48">
-        <v>-2155.411714208</v>
+        <v>-1850.870167808</v>
       </c>
       <c r="R48">
         <v>0.8518518518518519</v>
       </c>
       <c r="S48">
-        <v>0.1094705171364768</v>
+        <v>0.109271945338812</v>
       </c>
       <c r="T48">
-        <v>1.469505373093246</v>
+        <v>1.46586478842522</v>
       </c>
       <c r="U48">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V48">
-        <v>0.06978227654274022</v>
+        <v>0.07499509600559433</v>
       </c>
       <c r="W48">
-        <v>0.2007409847220767</v>
+        <v>0.1857409847220767</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5267,7 +5621,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.3171921661033645</v>
+        <v>0.3408868000254287</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5278,13 +5632,13 @@
         <v>0.47</v>
       </c>
       <c r="B49">
-        <v>0.1531549322258527</v>
+        <v>0.1459977034551138</v>
       </c>
       <c r="C49">
-        <v>-7088.592435188108</v>
+        <v>-5812.337839577784</v>
       </c>
       <c r="D49">
-        <v>18229.05156481189</v>
+        <v>19505.30616042222</v>
       </c>
       <c r="E49">
         <v>19799.944</v>
@@ -5311,37 +5665,37 @@
         <v>1781.7</v>
       </c>
       <c r="M49">
-        <v>5739.210495200001</v>
+        <v>5340.2848352</v>
       </c>
       <c r="N49">
-        <v>-3957.510495200001</v>
+        <v>-3558.5848352</v>
       </c>
       <c r="O49">
-        <v>-870.6523089440002</v>
+        <v>-782.888663744</v>
       </c>
       <c r="P49">
-        <v>-3086.858186256001</v>
+        <v>-2775.696171456</v>
       </c>
       <c r="Q49">
-        <v>-2250.658186256001</v>
+        <v>-1939.496171456</v>
       </c>
       <c r="R49">
         <v>0.8867924528301887</v>
       </c>
       <c r="S49">
-        <v>0.1106718476484858</v>
+        <v>0.1104695292131292</v>
       </c>
       <c r="T49">
-        <v>1.497231889566704</v>
+        <v>1.493522614621922</v>
       </c>
       <c r="U49">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V49">
-        <v>0.06829754725459682</v>
+        <v>0.07339945566504977</v>
       </c>
       <c r="W49">
-        <v>0.201061389302458</v>
+        <v>0.186061389302458</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5349,7 +5703,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.3104433966118036</v>
+        <v>0.3336338893865898</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5360,13 +5714,13 @@
         <v>0.48</v>
       </c>
       <c r="B50">
-        <v>0.1548549322258528</v>
+        <v>0.1475477034551138</v>
       </c>
       <c r="C50">
-        <v>-7934.321281782752</v>
+        <v>-6670.469559704947</v>
       </c>
       <c r="D50">
-        <v>17949.17471821724</v>
+        <v>19213.02644029505</v>
       </c>
       <c r="E50">
         <v>20365.79599999999</v>
@@ -5393,37 +5747,37 @@
         <v>1781.7</v>
       </c>
       <c r="M50">
-        <v>5861.3213568</v>
+        <v>5453.9079168</v>
       </c>
       <c r="N50">
-        <v>-4079.6213568</v>
+        <v>-3672.2079168</v>
       </c>
       <c r="O50">
-        <v>-897.5166984960001</v>
+        <v>-807.885741696</v>
       </c>
       <c r="P50">
-        <v>-3182.104658304</v>
+        <v>-2864.322175104</v>
       </c>
       <c r="Q50">
-        <v>-2345.904658304</v>
+        <v>-2028.122175104</v>
       </c>
       <c r="R50">
         <v>0.923076923076923</v>
       </c>
       <c r="S50">
-        <v>0.1119193831801875</v>
+        <v>0.1117131740056894</v>
       </c>
       <c r="T50">
-        <v>1.52602481051991</v>
+        <v>1.522244203364651</v>
       </c>
       <c r="U50">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V50">
-        <v>0.06687468168679271</v>
+        <v>0.07187030033869457</v>
       </c>
       <c r="W50">
-        <v>0.2013684436919902</v>
+        <v>0.1863684436919901</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5431,7 +5785,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.3039758258490578</v>
+        <v>0.3266831833577025</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5442,13 +5796,13 @@
         <v>0.49</v>
       </c>
       <c r="B51">
-        <v>0.1565549322258528</v>
+        <v>0.1490977034551138</v>
       </c>
       <c r="C51">
-        <v>-8771.585991770611</v>
+        <v>-7519.971193788995</v>
       </c>
       <c r="D51">
-        <v>17677.76200822939</v>
+        <v>18929.376806211</v>
       </c>
       <c r="E51">
         <v>20931.648</v>
@@ -5475,37 +5829,37 @@
         <v>1781.7</v>
       </c>
       <c r="M51">
-        <v>5983.4322184</v>
+        <v>5567.5309984</v>
       </c>
       <c r="N51">
-        <v>-4201.7322184</v>
+        <v>-3785.830998400001</v>
       </c>
       <c r="O51">
-        <v>-924.3810880480002</v>
+        <v>-832.8828196480001</v>
       </c>
       <c r="P51">
-        <v>-3277.351130352</v>
+        <v>-2952.948178752001</v>
       </c>
       <c r="Q51">
-        <v>-2441.151130352</v>
+        <v>-2116.748178752001</v>
       </c>
       <c r="R51">
         <v>0.9607843137254901</v>
       </c>
       <c r="S51">
-        <v>0.1132158416739166</v>
+        <v>0.1130055891822715</v>
       </c>
       <c r="T51">
-        <v>1.555946865628143</v>
+        <v>1.55209212892082</v>
       </c>
       <c r="U51">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V51">
-        <v>0.06550989226461328</v>
+        <v>0.07040355951545589</v>
       </c>
       <c r="W51">
-        <v>0.2016629652492965</v>
+        <v>0.1866629652492965</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5513,7 +5867,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.2977722375664239</v>
+        <v>0.3200161796157086</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5524,13 +5878,13 @@
         <v>0.5</v>
       </c>
       <c r="B52">
-        <v>0.1582549322258527</v>
+        <v>0.1506477034551137</v>
       </c>
       <c r="C52">
-        <v>-9600.764808871285</v>
+        <v>-8361.219409227822</v>
       </c>
       <c r="D52">
-        <v>17414.43519112871</v>
+        <v>18653.98059077217</v>
       </c>
       <c r="E52">
         <v>21497.5</v>
@@ -5557,37 +5911,37 @@
         <v>1781.7</v>
       </c>
       <c r="M52">
-        <v>6105.54308</v>
+        <v>5681.15408</v>
       </c>
       <c r="N52">
-        <v>-4323.843080000001</v>
+        <v>-3899.45408</v>
       </c>
       <c r="O52">
-        <v>-951.2454776000001</v>
+        <v>-857.8798976</v>
       </c>
       <c r="P52">
-        <v>-3372.597602400001</v>
+        <v>-3041.574182400001</v>
       </c>
       <c r="Q52">
-        <v>-2536.3976024</v>
+        <v>-2205.374182400001</v>
       </c>
       <c r="R52">
         <v>1</v>
       </c>
       <c r="S52">
-        <v>0.114564158507395</v>
+        <v>0.114349700965917</v>
       </c>
       <c r="T52">
-        <v>1.587065802940706</v>
+        <v>1.583133971499237</v>
       </c>
       <c r="U52">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V52">
-        <v>0.06419969441932101</v>
+        <v>0.06899548832514679</v>
       </c>
       <c r="W52">
-        <v>0.2019457059443105</v>
+        <v>0.1869457059443105</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5595,7 +5949,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.2918167928150954</v>
+        <v>0.3136158560233944</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5606,13 +5960,13 @@
         <v>0.51</v>
       </c>
       <c r="B53">
-        <v>0.1599549322258527</v>
+        <v>0.1521977034551137</v>
       </c>
       <c r="C53">
-        <v>-10422.21377041197</v>
+        <v>-9194.56926779541</v>
       </c>
       <c r="D53">
-        <v>17158.83822958803</v>
+        <v>18386.48273220459</v>
       </c>
       <c r="E53">
         <v>22063.352</v>
@@ -5639,37 +5993,37 @@
         <v>1781.7</v>
       </c>
       <c r="M53">
-        <v>6227.6539416</v>
+        <v>5794.7771616</v>
       </c>
       <c r="N53">
-        <v>-4445.9539416</v>
+        <v>-4013.0771616</v>
       </c>
       <c r="O53">
-        <v>-978.109867152</v>
+        <v>-882.8769755520001</v>
       </c>
       <c r="P53">
-        <v>-3467.844074448</v>
+        <v>-3130.200186048</v>
       </c>
       <c r="Q53">
-        <v>-2631.644074448</v>
+        <v>-2294.000186048</v>
       </c>
       <c r="R53">
         <v>1.040816326530612</v>
       </c>
       <c r="S53">
-        <v>0.1159675086810153</v>
+        <v>0.1157486744550173</v>
       </c>
       <c r="T53">
-        <v>1.619454900959904</v>
+        <v>1.615442828060446</v>
       </c>
       <c r="U53">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V53">
-        <v>0.06294087688168727</v>
+        <v>0.067642635612889</v>
       </c>
       <c r="W53">
-        <v>0.2022173587689319</v>
+        <v>0.1872173587689319</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5677,7 +6031,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.2860948949167603</v>
+        <v>0.3074665255131318</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5688,13 +6042,13 @@
         <v>0.52</v>
       </c>
       <c r="B54">
-        <v>0.1616549322258528</v>
+        <v>0.1537477034551138</v>
       </c>
       <c r="C54">
-        <v>-11236.26831340442</v>
+        <v>-10020.35575286344</v>
       </c>
       <c r="D54">
-        <v>16910.63568659558</v>
+        <v>18126.54824713656</v>
       </c>
       <c r="E54">
         <v>22629.204</v>
@@ -5721,37 +6075,37 @@
         <v>1781.7</v>
       </c>
       <c r="M54">
-        <v>6349.764803200001</v>
+        <v>5908.4002432</v>
       </c>
       <c r="N54">
-        <v>-4568.064803200001</v>
+        <v>-4126.7002432</v>
       </c>
       <c r="O54">
-        <v>-1004.974256704</v>
+        <v>-907.874053504</v>
       </c>
       <c r="P54">
-        <v>-3563.090546496001</v>
+        <v>-3218.826189696</v>
       </c>
       <c r="Q54">
-        <v>-2726.890546496001</v>
+        <v>-2382.626189696</v>
       </c>
       <c r="R54">
         <v>1.083333333333333</v>
       </c>
       <c r="S54">
-        <v>0.1174293317785364</v>
+        <v>0.1172059385061635</v>
       </c>
       <c r="T54">
-        <v>1.653193544729902</v>
+        <v>1.649097886978372</v>
       </c>
       <c r="U54">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V54">
-        <v>0.06173047540319328</v>
+        <v>0.06634181569725653</v>
       </c>
       <c r="W54">
-        <v>0.2024785634079909</v>
+        <v>0.1874785634079909</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5759,7 +6113,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.2805930700145148</v>
+        <v>0.3015537077148024</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5770,13 +6124,13 @@
         <v>0.53</v>
       </c>
       <c r="B55">
-        <v>0.1633549322258528</v>
+        <v>0.1552977034551137</v>
       </c>
       <c r="C55">
-        <v>-12043.2447432181</v>
+        <v>-10838.89516888433</v>
       </c>
       <c r="D55">
-        <v>16669.51125678189</v>
+        <v>17873.86083111567</v>
       </c>
       <c r="E55">
         <v>23195.056</v>
@@ -5803,37 +6157,37 @@
         <v>1781.7</v>
       </c>
       <c r="M55">
-        <v>6471.875664800001</v>
+        <v>6022.0233248</v>
       </c>
       <c r="N55">
-        <v>-4690.175664800001</v>
+        <v>-4240.323324800001</v>
       </c>
       <c r="O55">
-        <v>-1031.838646256</v>
+        <v>-932.8711314560002</v>
       </c>
       <c r="P55">
-        <v>-3658.337018544001</v>
+        <v>-3307.452193344001</v>
       </c>
       <c r="Q55">
-        <v>-2822.137018544001</v>
+        <v>-2471.252193344</v>
       </c>
       <c r="R55">
         <v>1.127659574468085</v>
       </c>
       <c r="S55">
-        <v>0.11895336011425</v>
+        <v>0.1187252137935287</v>
       </c>
       <c r="T55">
-        <v>1.688367875468836</v>
+        <v>1.684185076063018</v>
       </c>
       <c r="U55">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V55">
-        <v>0.06056574945218962</v>
+        <v>0.06509008332561017</v>
       </c>
       <c r="W55">
-        <v>0.2027299112682175</v>
+        <v>0.1877299112682175</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5841,7 +6195,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.2752988611463164</v>
+        <v>0.2958640151164098</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5852,13 +6206,13 @@
         <v>0.54</v>
       </c>
       <c r="B56">
-        <v>0.1650549322258528</v>
+        <v>0.1568477034551137</v>
       </c>
       <c r="C56">
-        <v>-12843.44157837113</v>
+        <v>-11650.48642542943</v>
       </c>
       <c r="D56">
-        <v>16435.16642162887</v>
+        <v>17628.12157457057</v>
       </c>
       <c r="E56">
         <v>23760.908</v>
@@ -5885,37 +6239,37 @@
         <v>1781.7</v>
       </c>
       <c r="M56">
-        <v>6593.986526400001</v>
+        <v>6135.6464064</v>
       </c>
       <c r="N56">
-        <v>-4812.286526400001</v>
+        <v>-4353.9464064</v>
       </c>
       <c r="O56">
-        <v>-1058.703035808</v>
+        <v>-957.8682094080001</v>
       </c>
       <c r="P56">
-        <v>-3753.583490592001</v>
+        <v>-3396.078196992</v>
       </c>
       <c r="Q56">
-        <v>-2917.383490592001</v>
+        <v>-2559.878196992</v>
       </c>
       <c r="R56">
         <v>1.173913043478261</v>
       </c>
       <c r="S56">
-        <v>0.1205436505515163</v>
+        <v>0.1203105445281706</v>
       </c>
       <c r="T56">
-        <v>1.72507152493555</v>
+        <v>1.720797795107866</v>
       </c>
       <c r="U56">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V56">
-        <v>0.0594441614993713</v>
+        <v>0.06388471141217295</v>
       </c>
       <c r="W56">
-        <v>0.2029719499484357</v>
+        <v>0.1879719499484357</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5923,7 +6277,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.2702007340880513</v>
+        <v>0.2903850518735134</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5934,13 +6288,13 @@
         <v>0.55</v>
       </c>
       <c r="B57">
-        <v>0.1667549322258527</v>
+        <v>0.1583977034551138</v>
       </c>
       <c r="C57">
-        <v>-13637.14078346103</v>
+        <v>-12455.41221674184</v>
       </c>
       <c r="D57">
-        <v>16207.31921653897</v>
+        <v>17389.04778325816</v>
       </c>
       <c r="E57">
         <v>24326.76</v>
@@ -5967,37 +6321,37 @@
         <v>1781.7</v>
       </c>
       <c r="M57">
-        <v>6716.097388000001</v>
+        <v>6249.269488</v>
       </c>
       <c r="N57">
-        <v>-4934.397388000001</v>
+        <v>-4467.569488</v>
       </c>
       <c r="O57">
-        <v>-1085.56742536</v>
+        <v>-982.86528736</v>
       </c>
       <c r="P57">
-        <v>-3848.829962640001</v>
+        <v>-3484.70420064</v>
       </c>
       <c r="Q57">
-        <v>-3012.629962640001</v>
+        <v>-2648.50420064</v>
       </c>
       <c r="R57">
         <v>1.222222222222223</v>
       </c>
       <c r="S57">
-        <v>0.1222046205637722</v>
+        <v>0.1219663344065744</v>
       </c>
       <c r="T57">
-        <v>1.763406447711896</v>
+        <v>1.759037746110264</v>
       </c>
       <c r="U57">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V57">
-        <v>0.05836335856301909</v>
+        <v>0.06272317120467889</v>
       </c>
       <c r="W57">
-        <v>0.2032051872221005</v>
+        <v>0.1882051872221005</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6005,7 +6359,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.2652879934682686</v>
+        <v>0.2851053236576313</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6016,13 +6370,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1684549322258528</v>
+        <v>0.1599477034551137</v>
       </c>
       <c r="C58">
-        <v>-14424.60890094213</v>
+        <v>-13253.94010659048</v>
       </c>
       <c r="D58">
-        <v>15985.70309905787</v>
+        <v>17156.37189340952</v>
       </c>
       <c r="E58">
         <v>24892.612</v>
@@ -6049,37 +6403,37 @@
         <v>1781.7</v>
       </c>
       <c r="M58">
-        <v>6838.208249600001</v>
+        <v>6362.892569600001</v>
       </c>
       <c r="N58">
-        <v>-5056.508249600001</v>
+        <v>-4581.192569600001</v>
       </c>
       <c r="O58">
-        <v>-1112.431814912</v>
+        <v>-1007.862365312</v>
       </c>
       <c r="P58">
-        <v>-3944.076434688001</v>
+        <v>-3573.330204288</v>
       </c>
       <c r="Q58">
-        <v>-3107.876434688001</v>
+        <v>-2737.130204288001</v>
       </c>
       <c r="R58">
         <v>1.272727272727273</v>
       </c>
       <c r="S58">
-        <v>0.1239410892129488</v>
+        <v>0.1236973874612693</v>
       </c>
       <c r="T58">
-        <v>1.803483866978075</v>
+        <v>1.799015876703678</v>
       </c>
       <c r="U58">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V58">
-        <v>0.05732115573153661</v>
+        <v>0.06160311457602392</v>
       </c>
       <c r="W58">
-        <v>0.2034300945931344</v>
+        <v>0.1884300945931344</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6087,7 +6441,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.260550707870621</v>
+        <v>0.280014157163745</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6098,13 +6452,13 @@
         <v>0.5700000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1701549322258528</v>
+        <v>0.1614977034551138</v>
       </c>
       <c r="C59">
-        <v>-15206.0980913012</v>
+        <v>-14046.3235271782</v>
       </c>
       <c r="D59">
-        <v>15770.0659086988</v>
+        <v>16929.8404728218</v>
       </c>
       <c r="E59">
         <v>25458.464</v>
@@ -6131,37 +6485,37 @@
         <v>1781.7</v>
       </c>
       <c r="M59">
-        <v>6960.319111200001</v>
+        <v>6476.5156512</v>
       </c>
       <c r="N59">
-        <v>-5178.619111200001</v>
+        <v>-4694.815651200001</v>
       </c>
       <c r="O59">
-        <v>-1139.296204464</v>
+        <v>-1032.859443264</v>
       </c>
       <c r="P59">
-        <v>-4039.322906736001</v>
+        <v>-3661.956207936</v>
       </c>
       <c r="Q59">
-        <v>-3203.122906736001</v>
+        <v>-2825.756207936</v>
       </c>
       <c r="R59">
         <v>1.325581395348838</v>
       </c>
       <c r="S59">
-        <v>0.1257583238458081</v>
+        <v>0.1255089546115314</v>
       </c>
       <c r="T59">
-        <v>1.845425352256635</v>
+        <v>1.840853455231671</v>
       </c>
       <c r="U59">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V59">
-        <v>0.05631552142045701</v>
+        <v>0.06052235817995331</v>
       </c>
       <c r="W59">
-        <v>0.2036471104774654</v>
+        <v>0.1886471104774654</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6169,7 +6523,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.2559796428202591</v>
+        <v>0.2751016280906968</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6180,13 +6534,13 @@
         <v>0.58</v>
       </c>
       <c r="B60">
-        <v>0.1718549322258527</v>
+        <v>0.1630477034551137</v>
       </c>
       <c r="C60">
-        <v>-15981.84709016557</v>
+        <v>-14832.80269994419</v>
       </c>
       <c r="D60">
-        <v>15560.16890983443</v>
+        <v>16709.21330005581</v>
       </c>
       <c r="E60">
         <v>26024.316</v>
@@ -6213,37 +6567,37 @@
         <v>1781.7</v>
       </c>
       <c r="M60">
-        <v>7082.429972800001</v>
+        <v>6590.1387328</v>
       </c>
       <c r="N60">
-        <v>-5300.729972800001</v>
+        <v>-4808.4387328</v>
       </c>
       <c r="O60">
-        <v>-1166.160594016</v>
+        <v>-1057.856521216</v>
       </c>
       <c r="P60">
-        <v>-4134.569378784001</v>
+        <v>-3750.582211584</v>
       </c>
       <c r="Q60">
-        <v>-3298.369378784001</v>
+        <v>-2914.382211584</v>
       </c>
       <c r="R60">
         <v>1.380952380952381</v>
       </c>
       <c r="S60">
-        <v>0.1276620934611845</v>
+        <v>0.1274067868641869</v>
       </c>
       <c r="T60">
-        <v>1.889364051119888</v>
+        <v>1.884683299403853</v>
       </c>
       <c r="U60">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V60">
-        <v>0.05534456415458707</v>
+        <v>0.05947886924581619</v>
       </c>
       <c r="W60">
-        <v>0.2038566430554401</v>
+        <v>0.1888566430554401</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6251,7 +6605,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.2515662007026684</v>
+        <v>0.2703584965718917</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6262,13 +6616,13 @@
         <v>0.59</v>
       </c>
       <c r="B61">
-        <v>0.1735549322258528</v>
+        <v>0.1645977034551137</v>
       </c>
       <c r="C61">
-        <v>-16752.08208998162</v>
+        <v>-15613.60548529397</v>
       </c>
       <c r="D61">
-        <v>15355.78591001838</v>
+        <v>16494.26251470602</v>
       </c>
       <c r="E61">
         <v>26590.168</v>
@@ -6295,37 +6649,37 @@
         <v>1781.7</v>
       </c>
       <c r="M61">
-        <v>7204.5408344</v>
+        <v>6703.7618144</v>
       </c>
       <c r="N61">
-        <v>-5422.8408344</v>
+        <v>-4922.0618144</v>
       </c>
       <c r="O61">
-        <v>-1193.024983568</v>
+        <v>-1082.853599168</v>
       </c>
       <c r="P61">
-        <v>-4229.815850832</v>
+        <v>-3839.208215232</v>
       </c>
       <c r="Q61">
-        <v>-3393.615850832</v>
+        <v>-3003.008215232</v>
       </c>
       <c r="R61">
         <v>1.439024390243902</v>
       </c>
       <c r="S61">
-        <v>0.129658729887067</v>
+        <v>0.1293971962998987</v>
       </c>
       <c r="T61">
-        <v>1.935446101147202</v>
+        <v>1.930651184755167</v>
       </c>
       <c r="U61">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V61">
-        <v>0.05440652069433984</v>
+        <v>0.058470752817921</v>
       </c>
       <c r="W61">
-        <v>0.2040590728341615</v>
+        <v>0.1890590728341615</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6333,7 +6687,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.2473023667924538</v>
+        <v>0.2657761491723681</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6344,13 +6698,13 @@
         <v>0.6</v>
       </c>
       <c r="B62">
-        <v>0.1752549322258528</v>
+        <v>0.1661477034551138</v>
       </c>
       <c r="C62">
-        <v>-17517.01755310888</v>
+        <v>-16388.94816757583</v>
       </c>
       <c r="D62">
-        <v>15156.70244689112</v>
+        <v>16284.77183242417</v>
       </c>
       <c r="E62">
         <v>27156.02</v>
@@ -6377,37 +6731,37 @@
         <v>1781.7</v>
       </c>
       <c r="M62">
-        <v>7326.651696</v>
+        <v>6817.384896</v>
       </c>
       <c r="N62">
-        <v>-5544.951696</v>
+        <v>-5035.684896</v>
       </c>
       <c r="O62">
-        <v>-1219.88937312</v>
+        <v>-1107.85067712</v>
       </c>
       <c r="P62">
-        <v>-4325.06232288</v>
+        <v>-3927.83421888</v>
       </c>
       <c r="Q62">
-        <v>-3488.86232288</v>
+        <v>-3091.63421888</v>
       </c>
       <c r="R62">
         <v>1.5</v>
       </c>
       <c r="S62">
-        <v>0.1317551981342437</v>
+        <v>0.1314871262073962</v>
       </c>
       <c r="T62">
-        <v>1.983832253675883</v>
+        <v>1.978917464374046</v>
       </c>
       <c r="U62">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V62">
-        <v>0.05349974534943418</v>
+        <v>0.05749624027095566</v>
       </c>
       <c r="W62">
-        <v>0.2042547549535921</v>
+        <v>0.1892547549535921</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6415,7 +6769,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.2431806606792463</v>
+        <v>0.2613465466861621</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6426,13 +6780,13 @@
         <v>0.61</v>
       </c>
       <c r="B63">
-        <v>0.1769549322258528</v>
+        <v>0.1676977034551138</v>
       </c>
       <c r="C63">
-        <v>-18276.85696247446</v>
+        <v>-17159.03618098831</v>
       </c>
       <c r="D63">
-        <v>14962.71503752553</v>
+        <v>16080.53581901169</v>
       </c>
       <c r="E63">
         <v>27721.872</v>
@@ -6459,37 +6813,37 @@
         <v>1781.7</v>
       </c>
       <c r="M63">
-        <v>7448.762557599999</v>
+        <v>6931.007977599999</v>
       </c>
       <c r="N63">
-        <v>-5667.062557599999</v>
+        <v>-5149.3079776</v>
       </c>
       <c r="O63">
-        <v>-1246.753762672</v>
+        <v>-1132.847755072</v>
       </c>
       <c r="P63">
-        <v>-4420.308794928</v>
+        <v>-4016.460222528</v>
       </c>
       <c r="Q63">
-        <v>-3584.108794928</v>
+        <v>-3180.260222528</v>
       </c>
       <c r="R63">
         <v>1.564102564102564</v>
       </c>
       <c r="S63">
-        <v>0.1339591775735833</v>
+        <v>0.1336842320075859</v>
       </c>
       <c r="T63">
-        <v>2.03469974735988</v>
+        <v>2.029658937819535</v>
       </c>
       <c r="U63">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V63">
-        <v>0.05262270034370575</v>
+        <v>0.05655367895503836</v>
       </c>
       <c r="W63">
-        <v>0.2044440212658283</v>
+        <v>0.1894440212658283</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6497,7 +6851,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.2391940924713898</v>
+        <v>0.2570621770683561</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6508,13 +6862,13 @@
         <v>0.62</v>
       </c>
       <c r="B64">
-        <v>0.1786549322258528</v>
+        <v>0.1692477034551138</v>
       </c>
       <c r="C64">
-        <v>-19031.79351531114</v>
+        <v>-17924.06478154047</v>
       </c>
       <c r="D64">
-        <v>14773.63048468886</v>
+        <v>15881.35921845953</v>
       </c>
       <c r="E64">
         <v>28287.724</v>
@@ -6541,37 +6895,37 @@
         <v>1781.7</v>
       </c>
       <c r="M64">
-        <v>7570.873419200001</v>
+        <v>7044.6310592</v>
       </c>
       <c r="N64">
-        <v>-5789.173419200001</v>
+        <v>-5262.9310592</v>
       </c>
       <c r="O64">
-        <v>-1273.618152224</v>
+        <v>-1157.844833024</v>
       </c>
       <c r="P64">
-        <v>-4515.555266976001</v>
+        <v>-4105.086226176</v>
       </c>
       <c r="Q64">
-        <v>-3679.355266976001</v>
+        <v>-3268.886226176</v>
       </c>
       <c r="R64">
         <v>1.631578947368421</v>
       </c>
       <c r="S64">
-        <v>0.1362791559307829</v>
+        <v>0.1359969749551539</v>
       </c>
       <c r="T64">
-        <v>2.08824447755356</v>
+        <v>2.083071015130575</v>
       </c>
       <c r="U64">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V64">
-        <v>0.05177394711235565</v>
+        <v>0.05564152284286031</v>
       </c>
       <c r="W64">
-        <v>0.2046271822131537</v>
+        <v>0.1896271822131537</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6579,7 +6933,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.2353361232379801</v>
+        <v>0.2529160129220923</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6590,13 +6944,13 @@
         <v>0.63</v>
       </c>
       <c r="B65">
-        <v>0.1803549322258527</v>
+        <v>0.1707977034551137</v>
       </c>
       <c r="C65">
-        <v>-19782.0107649511</v>
+        <v>-18684.2196696848</v>
       </c>
       <c r="D65">
-        <v>14589.2652350489</v>
+        <v>15687.0563303152</v>
       </c>
       <c r="E65">
         <v>28853.576</v>
@@ -6623,37 +6977,37 @@
         <v>1781.7</v>
       </c>
       <c r="M65">
-        <v>7692.9842808</v>
+        <v>7158.2541408</v>
       </c>
       <c r="N65">
-        <v>-5911.2842808</v>
+        <v>-5376.5541408</v>
       </c>
       <c r="O65">
-        <v>-1300.482541776</v>
+        <v>-1182.841910976</v>
       </c>
       <c r="P65">
-        <v>-4610.801739024</v>
+        <v>-4193.712229824</v>
       </c>
       <c r="Q65">
-        <v>-3774.601739024</v>
+        <v>-3357.512229824</v>
       </c>
       <c r="R65">
         <v>1.702702702702703</v>
       </c>
       <c r="S65">
-        <v>0.1387245385235067</v>
+        <v>0.1384347310350229</v>
       </c>
       <c r="T65">
-        <v>2.144683517487441</v>
+        <v>2.139370231755726</v>
       </c>
       <c r="U65">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V65">
-        <v>0.05095213842803254</v>
+        <v>0.05475832406757682</v>
       </c>
       <c r="W65">
-        <v>0.2048045285272306</v>
+        <v>0.1898045285272306</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6661,7 +7015,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.2316006292183297</v>
+        <v>0.24890147303444</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6672,13 +7026,13 @@
         <v>0.64</v>
       </c>
       <c r="B66">
-        <v>0.1820549322258528</v>
+        <v>0.1723477034551137</v>
       </c>
       <c r="C66">
-        <v>-20527.6832151569</v>
+        <v>-19439.67756779652</v>
       </c>
       <c r="D66">
-        <v>14409.4447848431</v>
+        <v>15497.45043220348</v>
       </c>
       <c r="E66">
         <v>29419.428</v>
@@ -6705,37 +7059,37 @@
         <v>1781.7</v>
       </c>
       <c r="M66">
-        <v>7815.0951424</v>
+        <v>7271.877222399999</v>
       </c>
       <c r="N66">
-        <v>-6033.395142400001</v>
+        <v>-5490.1772224</v>
       </c>
       <c r="O66">
-        <v>-1327.346931328</v>
+        <v>-1207.838988928</v>
       </c>
       <c r="P66">
-        <v>-4706.048211072</v>
+        <v>-4282.338233472</v>
       </c>
       <c r="Q66">
-        <v>-3869.848211072001</v>
+        <v>-3446.138233472</v>
       </c>
       <c r="R66">
         <v>1.777777777777778</v>
       </c>
       <c r="S66">
-        <v>0.1413057757047152</v>
+        <v>0.141007918008218</v>
       </c>
       <c r="T66">
-        <v>2.204258059639869</v>
+        <v>2.198797182637829</v>
       </c>
       <c r="U66">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V66">
-        <v>0.05015601126509454</v>
+        <v>0.05390272525402093</v>
       </c>
       <c r="W66">
-        <v>0.2049763327689926</v>
+        <v>0.1899763327689926</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6743,7 +7097,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.2279818693867933</v>
+        <v>0.2450123875182769</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6754,13 +7108,13 @@
         <v>0.65</v>
       </c>
       <c r="B67">
-        <v>0.1837549322258527</v>
+        <v>0.1738977034551137</v>
       </c>
       <c r="C67">
-        <v>-21268.97687103496</v>
+        <v>-20190.60675627373</v>
       </c>
       <c r="D67">
-        <v>14234.00312896503</v>
+        <v>15312.37324372627</v>
       </c>
       <c r="E67">
         <v>29985.28</v>
@@ -6787,37 +7141,37 @@
         <v>1781.7</v>
       </c>
       <c r="M67">
-        <v>7937.206004000001</v>
+        <v>7385.500304</v>
       </c>
       <c r="N67">
-        <v>-6155.506004000001</v>
+        <v>-5603.800304</v>
       </c>
       <c r="O67">
-        <v>-1354.21132088</v>
+        <v>-1232.83606688</v>
       </c>
       <c r="P67">
-        <v>-4801.294683120001</v>
+        <v>-4370.964237120001</v>
       </c>
       <c r="Q67">
-        <v>-3965.094683120001</v>
+        <v>-3534.764237120001</v>
       </c>
       <c r="R67">
         <v>1.857142857142857</v>
       </c>
       <c r="S67">
-        <v>0.1440345121534214</v>
+        <v>0.1437281442370242</v>
       </c>
       <c r="T67">
-        <v>2.267236861343866</v>
+        <v>2.261619959284624</v>
       </c>
       <c r="U67">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V67">
-        <v>0.04938438032255462</v>
+        <v>0.05307345255780522</v>
       </c>
       <c r="W67">
-        <v>0.2051428507263927</v>
+        <v>0.1901428507263927</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6825,7 +7179,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.2244744560116119</v>
+        <v>0.2412429661718418</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6836,13 +7190,13 @@
         <v>0.66</v>
       </c>
       <c r="B68">
-        <v>0.1854549322258528</v>
+        <v>0.1754477034551138</v>
       </c>
       <c r="C68">
-        <v>-22006.04975018743</v>
+        <v>-20937.16757167703</v>
       </c>
       <c r="D68">
-        <v>14062.78224981256</v>
+        <v>15131.66442832297</v>
       </c>
       <c r="E68">
         <v>30551.132</v>
@@ -6869,37 +7223,37 @@
         <v>1781.7</v>
       </c>
       <c r="M68">
-        <v>8059.3168656</v>
+        <v>7499.1233856</v>
       </c>
       <c r="N68">
-        <v>-6277.6168656</v>
+        <v>-5717.4233856</v>
       </c>
       <c r="O68">
-        <v>-1381.075710432</v>
+        <v>-1257.833144832</v>
       </c>
       <c r="P68">
-        <v>-4896.541155168</v>
+        <v>-4459.590240768001</v>
       </c>
       <c r="Q68">
-        <v>-4060.341155168</v>
+        <v>-3623.390240768001</v>
       </c>
       <c r="R68">
         <v>1.941176470588236</v>
       </c>
       <c r="S68">
-        <v>0.146923762510875</v>
+        <v>0.1466083837734073</v>
       </c>
       <c r="T68">
-        <v>2.333920298442215</v>
+        <v>2.328138193381231</v>
       </c>
       <c r="U68">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V68">
-        <v>0.04863613213584925</v>
+        <v>0.05226930933723242</v>
       </c>
       <c r="W68">
-        <v>0.2053043226850838</v>
+        <v>0.1903043226850837</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6907,7 +7261,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.2210733278902238</v>
+        <v>0.2375877697146928</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6918,13 +7272,13 @@
         <v>0.67</v>
       </c>
       <c r="B69">
-        <v>0.1871549322258528</v>
+        <v>0.1769977034551137</v>
       </c>
       <c r="C69">
-        <v>-22739.0523574106</v>
+        <v>-21679.51287000763</v>
       </c>
       <c r="D69">
-        <v>13895.6316425894</v>
+        <v>14955.17112999238</v>
       </c>
       <c r="E69">
         <v>31116.984</v>
@@ -6951,37 +7305,37 @@
         <v>1781.7</v>
       </c>
       <c r="M69">
-        <v>8181.427727200001</v>
+        <v>7612.746467200001</v>
       </c>
       <c r="N69">
-        <v>-6399.727727200001</v>
+        <v>-5831.046467200001</v>
       </c>
       <c r="O69">
-        <v>-1407.940099984</v>
+        <v>-1282.830222784</v>
       </c>
       <c r="P69">
-        <v>-4991.787627216001</v>
+        <v>-4548.216244416</v>
       </c>
       <c r="Q69">
-        <v>-4155.587627216001</v>
+        <v>-3712.016244416001</v>
       </c>
       <c r="R69">
         <v>2.030303030303031</v>
       </c>
       <c r="S69">
-        <v>0.1499881189505984</v>
+        <v>0.1496631832816924</v>
       </c>
       <c r="T69">
-        <v>2.404645155970767</v>
+        <v>2.398687835604905</v>
       </c>
       <c r="U69">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V69">
-        <v>0.0479102197159112</v>
+        <v>0.05148917039190058</v>
       </c>
       <c r="W69">
-        <v>0.2054609745853064</v>
+        <v>0.1904609745853064</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6989,7 +7343,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.2177737259814145</v>
+        <v>0.234041683599548</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7000,13 +7354,13 @@
         <v>0.68</v>
       </c>
       <c r="B70">
-        <v>0.1888549322258528</v>
+        <v>0.1785477034551138</v>
       </c>
       <c r="C70">
-        <v>-23468.12812593738</v>
+        <v>-22417.78845793782</v>
       </c>
       <c r="D70">
-        <v>13732.40787406262</v>
+        <v>14782.74754206218</v>
       </c>
       <c r="E70">
         <v>31682.836</v>
@@ -7033,37 +7387,37 @@
         <v>1781.7</v>
       </c>
       <c r="M70">
-        <v>8303.538588800002</v>
+        <v>7726.3695488</v>
       </c>
       <c r="N70">
-        <v>-6521.838588800002</v>
+        <v>-5944.6695488</v>
       </c>
       <c r="O70">
-        <v>-1434.804489536001</v>
+        <v>-1307.827300736</v>
       </c>
       <c r="P70">
-        <v>-5087.034099264001</v>
+        <v>-4636.842248064</v>
       </c>
       <c r="Q70">
-        <v>-4250.834099264001</v>
+        <v>-3800.642248064</v>
       </c>
       <c r="R70">
         <v>2.125</v>
       </c>
       <c r="S70">
-        <v>0.1532439976678047</v>
+        <v>0.1529089077592453</v>
       </c>
       <c r="T70">
-        <v>2.479790317094853</v>
+        <v>2.473646830467558</v>
       </c>
       <c r="U70">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V70">
-        <v>0.04720565766126544</v>
+        <v>0.05073197670966675</v>
       </c>
       <c r="W70">
-        <v>0.205613019076699</v>
+        <v>0.1906130190766989</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7071,7 +7425,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.2145711711875702</v>
+        <v>0.2305998941348488</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7082,13 +7436,13 @@
         <v>0.6900000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1905549322258528</v>
+        <v>0.1800977034551137</v>
       </c>
       <c r="C71">
-        <v>-24193.41382794265</v>
+        <v>-23152.13349455049</v>
       </c>
       <c r="D71">
-        <v>13572.97417205735</v>
+        <v>14614.25450544951</v>
       </c>
       <c r="E71">
         <v>32248.688</v>
@@ -7115,37 +7469,37 @@
         <v>1781.7</v>
       </c>
       <c r="M71">
-        <v>8425.6494504</v>
+        <v>7839.9926304</v>
       </c>
       <c r="N71">
-        <v>-6643.9494504</v>
+        <v>-6058.2926304</v>
       </c>
       <c r="O71">
-        <v>-1461.668879088</v>
+        <v>-1332.824378688</v>
       </c>
       <c r="P71">
-        <v>-5182.280571312001</v>
+        <v>-4725.468251712</v>
       </c>
       <c r="Q71">
-        <v>-4346.080571312001</v>
+        <v>-3889.268251712</v>
       </c>
       <c r="R71">
         <v>2.225806451612904</v>
       </c>
       <c r="S71">
-        <v>0.1567099330764435</v>
+        <v>0.1563640338159951</v>
       </c>
       <c r="T71">
-        <v>2.559783553130171</v>
+        <v>2.553441889514899</v>
       </c>
       <c r="U71">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V71">
-        <v>0.04652151769516015</v>
+        <v>0.04999673067039621</v>
       </c>
       <c r="W71">
-        <v>0.2057606564813845</v>
+        <v>0.1907606564813844</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7153,7 +7507,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.2114614440689098</v>
+        <v>0.2272578666836191</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7164,13 +7518,13 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1922549322258528</v>
+        <v>0.1816477034551138</v>
       </c>
       <c r="C72">
-        <v>-24915.03995678105</v>
+        <v>-23882.68086591425</v>
       </c>
       <c r="D72">
-        <v>13417.20004321895</v>
+        <v>14449.55913408575</v>
       </c>
       <c r="E72">
         <v>32814.54</v>
@@ -7197,37 +7551,37 @@
         <v>1781.7</v>
       </c>
       <c r="M72">
-        <v>8547.760312</v>
+        <v>7953.615712</v>
       </c>
       <c r="N72">
-        <v>-6766.060312000001</v>
+        <v>-6171.915712</v>
       </c>
       <c r="O72">
-        <v>-1488.53326864</v>
+        <v>-1357.82145664</v>
       </c>
       <c r="P72">
-        <v>-5277.52704336</v>
+        <v>-4814.09425536</v>
       </c>
       <c r="Q72">
-        <v>-4441.32704336</v>
+        <v>-3977.89425536</v>
       </c>
       <c r="R72">
         <v>2.333333333333334</v>
       </c>
       <c r="S72">
-        <v>0.1604069308456583</v>
+        <v>0.1600495016098616</v>
       </c>
       <c r="T72">
-        <v>2.645109671567844</v>
+        <v>2.638556619165395</v>
       </c>
       <c r="U72">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V72">
-        <v>0.04585692458522929</v>
+        <v>0.04928249166081913</v>
       </c>
       <c r="W72">
-        <v>0.2059040756745076</v>
+        <v>0.1909040756745075</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7235,7 +7589,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.2084405662964968</v>
+        <v>0.224011325730996</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7246,13 +7600,13 @@
         <v>0.71</v>
       </c>
       <c r="B73">
-        <v>0.1939549322258527</v>
+        <v>0.1831977034551137</v>
       </c>
       <c r="C73">
-        <v>-25633.13108320211</v>
+        <v>-24609.55753461309</v>
       </c>
       <c r="D73">
-        <v>13264.96091679789</v>
+        <v>14288.53446538691</v>
       </c>
       <c r="E73">
         <v>33380.392</v>
@@ -7279,37 +7633,37 @@
         <v>1781.7</v>
       </c>
       <c r="M73">
-        <v>8669.8711736</v>
+        <v>8067.2387936</v>
       </c>
       <c r="N73">
-        <v>-6888.171173600001</v>
+        <v>-6285.5387936</v>
       </c>
       <c r="O73">
-        <v>-1515.397658192</v>
+        <v>-1382.818534592</v>
       </c>
       <c r="P73">
-        <v>-5372.773515408</v>
+        <v>-4902.720259008</v>
       </c>
       <c r="Q73">
-        <v>-4536.573515408</v>
+        <v>-4066.520259008</v>
       </c>
       <c r="R73">
         <v>2.448275862068965</v>
       </c>
       <c r="S73">
-        <v>0.1643588939782672</v>
+        <v>0.1639891395964085</v>
       </c>
       <c r="T73">
-        <v>2.736320349897769</v>
+        <v>2.729541330171098</v>
       </c>
       <c r="U73">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V73">
-        <v>0.04521105240797254</v>
+        <v>0.04858837205996253</v>
       </c>
       <c r="W73">
-        <v>0.2060434548903596</v>
+        <v>0.1910434548903595</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7317,7 +7671,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.2055047836726024</v>
+        <v>0.2208562366361932</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7328,13 +7682,13 @@
         <v>0.72</v>
       </c>
       <c r="B74">
-        <v>0.1956549322258528</v>
+        <v>0.1847477034551137</v>
       </c>
       <c r="C74">
-        <v>-26347.80618758665</v>
+        <v>-25332.88486616298</v>
       </c>
       <c r="D74">
-        <v>13116.13781241335</v>
+        <v>14131.05913383702</v>
       </c>
       <c r="E74">
         <v>33946.244</v>
@@ -7361,37 +7715,37 @@
         <v>1781.7</v>
       </c>
       <c r="M74">
-        <v>8791.982035200001</v>
+        <v>8180.861875199999</v>
       </c>
       <c r="N74">
-        <v>-7010.282035200001</v>
+        <v>-6399.161875199999</v>
       </c>
       <c r="O74">
-        <v>-1542.262047744</v>
+        <v>-1407.815612544</v>
       </c>
       <c r="P74">
-        <v>-5468.019987456</v>
+        <v>-4991.346262655999</v>
       </c>
       <c r="Q74">
-        <v>-4631.819987456</v>
+        <v>-4155.146262656</v>
       </c>
       <c r="R74">
         <v>2.571428571428571</v>
       </c>
       <c r="S74">
-        <v>0.1685931401917767</v>
+        <v>0.1682101802962803</v>
       </c>
       <c r="T74">
-        <v>2.834046076679832</v>
+        <v>2.82702494910578</v>
       </c>
       <c r="U74">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V74">
-        <v>0.04458312112452848</v>
+        <v>0.04791353355912972</v>
       </c>
       <c r="W74">
-        <v>0.2061789624613268</v>
+        <v>0.1911789624613268</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7399,7 +7753,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.2026505505660385</v>
+        <v>0.2177887889051351</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7410,13 +7764,13 @@
         <v>0.73</v>
       </c>
       <c r="B75">
-        <v>0.2193941016787875</v>
+        <v>0.1862977034551138</v>
       </c>
       <c r="C75">
-        <v>-28690.21107835805</v>
+        <v>-26052.77893407879</v>
       </c>
       <c r="D75">
-        <v>11339.58492164195</v>
+        <v>13977.01706592121</v>
       </c>
       <c r="E75">
         <v>34512.096</v>
@@ -7443,45 +7797,45 @@
         <v>1781.7</v>
       </c>
       <c r="M75">
-        <v>10153.3087768</v>
+        <v>8294.484956799999</v>
       </c>
       <c r="N75">
-        <v>-8371.6087768</v>
+        <v>-6512.784956799999</v>
       </c>
       <c r="O75">
-        <v>-1841.753930896</v>
+        <v>-1432.812690496</v>
       </c>
       <c r="P75">
-        <v>-6529.854845903999</v>
+        <v>-5079.972266303999</v>
       </c>
       <c r="Q75">
-        <v>-5693.654845904</v>
+        <v>-4243.772266303999</v>
       </c>
       <c r="R75">
         <v>2.703703703703703</v>
       </c>
       <c r="S75">
-        <v>0.1736564766912303</v>
+        <v>0.172743890677624</v>
       </c>
       <c r="T75">
-        <v>2.950907074930834</v>
+        <v>2.931729576850439</v>
       </c>
       <c r="U75">
-        <v>0.2458</v>
+        <v>0.2008</v>
       </c>
       <c r="V75">
-        <v>0.0386055431403454</v>
+        <v>0.04725718378434712</v>
       </c>
       <c r="W75">
-        <v>0.2363107574961031</v>
+        <v>0.1913107574961031</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y75">
-        <v>0.1754797415470246</v>
+        <v>0.2148053808379414</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7492,13 +7846,13 @@
         <v>0.74</v>
       </c>
       <c r="B76">
-        <v>0.2213941016787875</v>
+        <v>0.1878477034551137</v>
       </c>
       <c r="C76">
-        <v>-29384.00297181764</v>
+        <v>-26769.3508052033</v>
       </c>
       <c r="D76">
-        <v>11211.64502818235</v>
+        <v>13826.29719479669</v>
       </c>
       <c r="E76">
         <v>35077.948</v>
@@ -7525,45 +7879,45 @@
         <v>1781.7</v>
       </c>
       <c r="M76">
-        <v>10292.3951984</v>
+        <v>8408.1080384</v>
       </c>
       <c r="N76">
-        <v>-8510.695198399999</v>
+        <v>-6626.4080384</v>
       </c>
       <c r="O76">
-        <v>-1872.352943648</v>
+        <v>-1457.809768448</v>
       </c>
       <c r="P76">
-        <v>-6638.342254751999</v>
+        <v>-5168.598269952</v>
       </c>
       <c r="Q76">
-        <v>-5802.142254751999</v>
+        <v>-4332.398269952</v>
       </c>
       <c r="R76">
         <v>2.846153846153846</v>
       </c>
       <c r="S76">
-        <v>0.1785740334870469</v>
+        <v>0.1776263480113788</v>
       </c>
       <c r="T76">
-        <v>3.064403500889712</v>
+        <v>3.044488406729302</v>
       </c>
       <c r="U76">
-        <v>0.2458</v>
+        <v>0.2008</v>
       </c>
       <c r="V76">
-        <v>0.03808384661142182</v>
+        <v>0.04661857319266675</v>
       </c>
       <c r="W76">
-        <v>0.2364389905029125</v>
+        <v>0.1914389905029125</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y76">
-        <v>0.173108393688281</v>
+        <v>0.2119026054212124</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7574,13 +7928,13 @@
         <v>0.75</v>
       </c>
       <c r="B77">
-        <v>0.2233941016787875</v>
+        <v>0.1893977034551138</v>
       </c>
       <c r="C77">
-        <v>-30074.94008770278</v>
+        <v>-27482.70680677235</v>
       </c>
       <c r="D77">
-        <v>11086.55991229722</v>
+        <v>13678.79319322764</v>
       </c>
       <c r="E77">
         <v>35643.8</v>
@@ -7607,45 +7961,45 @@
         <v>1781.7</v>
       </c>
       <c r="M77">
-        <v>10431.48162</v>
+        <v>8521.731119999999</v>
       </c>
       <c r="N77">
-        <v>-8649.781619999998</v>
+        <v>-6740.031119999999</v>
       </c>
       <c r="O77">
-        <v>-1902.9519564</v>
+        <v>-1482.8068464</v>
       </c>
       <c r="P77">
-        <v>-6746.829663599999</v>
+        <v>-5257.224273599999</v>
       </c>
       <c r="Q77">
-        <v>-5910.629663599999</v>
+        <v>-4421.024273599999</v>
       </c>
       <c r="R77">
         <v>3</v>
       </c>
       <c r="S77">
-        <v>0.1838849948265288</v>
+        <v>0.1828994019318339</v>
       </c>
       <c r="T77">
-        <v>3.186979640925301</v>
+        <v>3.166267942998473</v>
       </c>
       <c r="U77">
-        <v>0.2458</v>
+        <v>0.2008</v>
       </c>
       <c r="V77">
-        <v>0.0375760619899362</v>
+        <v>0.04599699221676453</v>
       </c>
       <c r="W77">
-        <v>0.2365638039628737</v>
+        <v>0.1915638039628737</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y77">
-        <v>0.1708002817724373</v>
+        <v>0.2090772373489297</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7656,13 +8010,13 @@
         <v>0.76</v>
       </c>
       <c r="B78">
-        <v>0.2253941016787875</v>
+        <v>0.1909477034551137</v>
       </c>
       <c r="C78">
-        <v>-30763.11692156352</v>
+        <v>-28192.94877656535</v>
       </c>
       <c r="D78">
-        <v>10964.23507843648</v>
+        <v>13534.40322343465</v>
       </c>
       <c r="E78">
         <v>36209.652</v>
@@ -7689,45 +8043,45 @@
         <v>1781.7</v>
       </c>
       <c r="M78">
-        <v>10570.5680416</v>
+        <v>8635.354201600001</v>
       </c>
       <c r="N78">
-        <v>-8788.868041600001</v>
+        <v>-6853.654201600001</v>
       </c>
       <c r="O78">
-        <v>-1933.550969152</v>
+        <v>-1507.803924352</v>
       </c>
       <c r="P78">
-        <v>-6855.317072448001</v>
+        <v>-5345.850277248001</v>
       </c>
       <c r="Q78">
-        <v>-6019.117072448001</v>
+        <v>-4509.650277248001</v>
       </c>
       <c r="R78">
         <v>3.166666666666667</v>
       </c>
       <c r="S78">
-        <v>0.1896385362776341</v>
+        <v>0.188611877012327</v>
       </c>
       <c r="T78">
-        <v>3.319770459297189</v>
+        <v>3.298195773956744</v>
       </c>
       <c r="U78">
-        <v>0.2458</v>
+        <v>0.2008</v>
       </c>
       <c r="V78">
-        <v>0.03708164012164755</v>
+        <v>0.04539176863496498</v>
       </c>
       <c r="W78">
-        <v>0.236685332858099</v>
+        <v>0.1916853328580991</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y78">
-        <v>0.1685529096438526</v>
+        <v>0.2063262210680227</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7738,13 +8092,13 @@
         <v>0.77</v>
       </c>
       <c r="B79">
-        <v>0.2273941016787875</v>
+        <v>0.1924977034551137</v>
       </c>
       <c r="C79">
-        <v>-31448.62384395351</v>
+        <v>-28900.17429737826</v>
       </c>
       <c r="D79">
-        <v>10844.58015604649</v>
+        <v>13393.02970262174</v>
       </c>
       <c r="E79">
         <v>36775.504</v>
@@ -7771,45 +8125,45 @@
         <v>1781.7</v>
       </c>
       <c r="M79">
-        <v>10709.6544632</v>
+        <v>8748.9772832</v>
       </c>
       <c r="N79">
-        <v>-8927.9544632</v>
+        <v>-6967.2772832</v>
       </c>
       <c r="O79">
-        <v>-1964.149981904</v>
+        <v>-1532.801002304</v>
       </c>
       <c r="P79">
-        <v>-6963.804481296</v>
+        <v>-5434.476280896</v>
       </c>
       <c r="Q79">
-        <v>-6127.604481296</v>
+        <v>-4598.276280896001</v>
       </c>
       <c r="R79">
         <v>3.347826086956522</v>
       </c>
       <c r="S79">
-        <v>0.1958923856810096</v>
+        <v>0.1948210890563412</v>
       </c>
       <c r="T79">
-        <v>3.464108305353589</v>
+        <v>3.441595590215733</v>
       </c>
       <c r="U79">
-        <v>0.2458</v>
+        <v>0.2008</v>
       </c>
       <c r="V79">
-        <v>0.03660006037980798</v>
+        <v>0.04480226514619921</v>
       </c>
       <c r="W79">
-        <v>0.2368037051586432</v>
+        <v>0.1918037051586432</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y79">
-        <v>0.1663639108173091</v>
+        <v>0.2036466597554509</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7820,13 +8174,13 @@
         <v>0.78</v>
       </c>
       <c r="B80">
-        <v>0.2293941016787875</v>
+        <v>0.1940477034551137</v>
       </c>
       <c r="C80">
-        <v>-32131.54732308466</v>
+        <v>-29604.47691695334</v>
       </c>
       <c r="D80">
-        <v>10727.50867691534</v>
+        <v>13254.57908304666</v>
       </c>
       <c r="E80">
         <v>37341.356</v>
@@ -7853,45 +8207,45 @@
         <v>1781.7</v>
       </c>
       <c r="M80">
-        <v>10848.7408848</v>
+        <v>8862.600364800001</v>
       </c>
       <c r="N80">
-        <v>-9067.040884799999</v>
+        <v>-7080.900364800001</v>
       </c>
       <c r="O80">
-        <v>-1994.748994656</v>
+        <v>-1557.798080256</v>
       </c>
       <c r="P80">
-        <v>-7072.291890143999</v>
+        <v>-5523.102284544</v>
       </c>
       <c r="Q80">
-        <v>-6236.091890143999</v>
+        <v>-4686.902284544</v>
       </c>
       <c r="R80">
         <v>3.545454545454546</v>
       </c>
       <c r="S80">
-        <v>0.2027147668483281</v>
+        <v>0.2015947749225385</v>
       </c>
       <c r="T80">
-        <v>3.621567773778751</v>
+        <v>3.598031753407357</v>
       </c>
       <c r="U80">
-        <v>0.2458</v>
+        <v>0.2008</v>
       </c>
       <c r="V80">
-        <v>0.03613082883647711</v>
+        <v>0.04422787713150435</v>
       </c>
       <c r="W80">
-        <v>0.236919042271994</v>
+        <v>0.1919190422719939</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y80">
-        <v>0.1642310401658051</v>
+        <v>0.2010358051432015</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7902,13 +8256,13 @@
         <v>0.79</v>
       </c>
       <c r="B81">
-        <v>0.2313941016787875</v>
+        <v>0.2234294797373575</v>
       </c>
       <c r="C81">
-        <v>-32811.97013321407</v>
+        <v>-32342.09240808849</v>
       </c>
       <c r="D81">
-        <v>10612.93786678593</v>
+        <v>11082.8155919115</v>
       </c>
       <c r="E81">
         <v>37907.208</v>
@@ -7935,37 +8289,37 @@
         <v>1781.7</v>
       </c>
       <c r="M81">
-        <v>10987.8273064</v>
+        <v>10540.8042264</v>
       </c>
       <c r="N81">
-        <v>-9206.1273064</v>
+        <v>-8759.104226399999</v>
       </c>
       <c r="O81">
-        <v>-2025.348007408</v>
+        <v>-1927.002929808</v>
       </c>
       <c r="P81">
-        <v>-7180.779298992</v>
+        <v>-6832.101296591999</v>
       </c>
       <c r="Q81">
-        <v>-6344.579298992</v>
+        <v>-5995.901296591999</v>
       </c>
       <c r="R81">
         <v>3.761904761904763</v>
       </c>
       <c r="S81">
-        <v>0.2101868986030105</v>
+        <v>0.2098791750723915</v>
       </c>
       <c r="T81">
-        <v>3.79402338205393</v>
+        <v>3.789357391972089</v>
       </c>
       <c r="U81">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.03567347657272423</v>
+        <v>0.03718634665638514</v>
       </c>
       <c r="W81">
-        <v>0.2370314594584244</v>
+        <v>0.2270314594584244</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7973,7 +8327,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.1621521662396557</v>
+        <v>0.1690288484381144</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7984,13 +8338,13 @@
         <v>0.8</v>
       </c>
       <c r="B82">
-        <v>0.2333941016787875</v>
+        <v>0.2253294797373575</v>
       </c>
       <c r="C82">
-        <v>-33489.9715498185</v>
+        <v>-33024.14139872145</v>
       </c>
       <c r="D82">
-        <v>10500.7884501815</v>
+        <v>10966.61860127855</v>
       </c>
       <c r="E82">
         <v>38473.06</v>
@@ -8017,37 +8371,37 @@
         <v>1781.7</v>
       </c>
       <c r="M82">
-        <v>11126.913728</v>
+        <v>10674.232128</v>
       </c>
       <c r="N82">
-        <v>-9345.213728000001</v>
+        <v>-8892.532128000001</v>
       </c>
       <c r="O82">
-        <v>-2055.94702016</v>
+        <v>-1956.35706816</v>
       </c>
       <c r="P82">
-        <v>-7289.266707840001</v>
+        <v>-6936.17505984</v>
       </c>
       <c r="Q82">
-        <v>-6453.066707840001</v>
+        <v>-6099.975059840001</v>
       </c>
       <c r="R82">
         <v>4.000000000000001</v>
       </c>
       <c r="S82">
-        <v>0.218406243533161</v>
+        <v>0.218083133826011</v>
       </c>
       <c r="T82">
-        <v>3.983724551156627</v>
+        <v>3.978825261570694</v>
       </c>
       <c r="U82">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.03522755811556517</v>
+        <v>0.03672151732318032</v>
       </c>
       <c r="W82">
-        <v>0.2371410662151941</v>
+        <v>0.2271410662151941</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8055,7 +8409,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.16012526416166</v>
+        <v>0.1669159878326379</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8066,13 +8420,13 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2353941016787875</v>
+        <v>0.2272294797373575</v>
       </c>
       <c r="C83">
-        <v>-34165.62753252343</v>
+        <v>-33703.77915166132</v>
       </c>
       <c r="D83">
-        <v>10390.98446747657</v>
+        <v>10852.83284833868</v>
       </c>
       <c r="E83">
         <v>39038.912</v>
@@ -8099,37 +8453,37 @@
         <v>1781.7</v>
       </c>
       <c r="M83">
-        <v>11266.0001496</v>
+        <v>10807.6600296</v>
       </c>
       <c r="N83">
-        <v>-9484.300149600002</v>
+        <v>-9025.960029600001</v>
       </c>
       <c r="O83">
-        <v>-2086.546032912001</v>
+        <v>-1985.711206512</v>
       </c>
       <c r="P83">
-        <v>-7397.754116688001</v>
+        <v>-7040.248823088001</v>
       </c>
       <c r="Q83">
-        <v>-6561.554116688001</v>
+        <v>-6204.048823088001</v>
       </c>
       <c r="R83">
         <v>4.263157894736843</v>
       </c>
       <c r="S83">
-        <v>0.2274907826664853</v>
+        <v>0.2271506671852748</v>
       </c>
       <c r="T83">
-        <v>4.193394264375397</v>
+        <v>4.188237117442837</v>
       </c>
       <c r="U83">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.03479264999068165</v>
+        <v>0.03626816525746204</v>
       </c>
       <c r="W83">
-        <v>0.2372479666322905</v>
+        <v>0.2272479666322905</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8137,7 +8491,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.158148409048553</v>
+        <v>0.1648552966248276</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8148,13 +8502,13 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2373941016787875</v>
+        <v>0.2291294797373575</v>
       </c>
       <c r="C84">
-        <v>-34839.01089667401</v>
+        <v>-34381.0799506132</v>
       </c>
       <c r="D84">
-        <v>10283.45310332599</v>
+        <v>10741.38404938681</v>
       </c>
       <c r="E84">
         <v>39604.764</v>
@@ -8181,37 +8535,37 @@
         <v>1781.7</v>
       </c>
       <c r="M84">
-        <v>11405.0865712</v>
+        <v>10941.0879312</v>
       </c>
       <c r="N84">
-        <v>-9623.386571200001</v>
+        <v>-9159.387931200001</v>
       </c>
       <c r="O84">
-        <v>-2117.145045664</v>
+        <v>-2015.065344864</v>
       </c>
       <c r="P84">
-        <v>-7506.241525536001</v>
+        <v>-7144.322586336</v>
       </c>
       <c r="Q84">
-        <v>-6670.041525536001</v>
+        <v>-6308.122586336</v>
       </c>
       <c r="R84">
         <v>4.555555555555557</v>
       </c>
       <c r="S84">
-        <v>0.2375847150368456</v>
+        <v>0.2372257042511234</v>
       </c>
       <c r="T84">
-        <v>4.426360612396253</v>
+        <v>4.420916957300772</v>
       </c>
       <c r="U84">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.0343683493810392</v>
+        <v>0.03582587055920031</v>
       </c>
       <c r="W84">
-        <v>0.2373522597221406</v>
+        <v>0.2273522597221406</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8219,7 +8573,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.1562197699138146</v>
+        <v>0.1628448661781833</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8230,13 +8584,13 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2393941016787875</v>
+        <v>0.2310294797373575</v>
       </c>
       <c r="C85">
-        <v>-35510.1914743619</v>
+        <v>-35056.11505899137</v>
       </c>
       <c r="D85">
-        <v>10178.12452563811</v>
+        <v>10632.20094100863</v>
       </c>
       <c r="E85">
         <v>40170.616</v>
@@ -8263,37 +8617,37 @@
         <v>1781.7</v>
       </c>
       <c r="M85">
-        <v>11544.1729928</v>
+        <v>11074.5158328</v>
       </c>
       <c r="N85">
-        <v>-9762.4729928</v>
+        <v>-9292.815832799999</v>
       </c>
       <c r="O85">
-        <v>-2147.744058416</v>
+        <v>-2044.419483216</v>
       </c>
       <c r="P85">
-        <v>-7614.728934384</v>
+        <v>-7248.396349583999</v>
       </c>
       <c r="Q85">
-        <v>-6778.528934384</v>
+        <v>-6412.196349583999</v>
       </c>
       <c r="R85">
         <v>4.882352941176473</v>
       </c>
       <c r="S85">
-        <v>0.2488661688625424</v>
+        <v>0.2484860397953071</v>
       </c>
       <c r="T85">
-        <v>4.686734766066621</v>
+        <v>4.680970895965523</v>
       </c>
       <c r="U85">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.03395427288247246</v>
+        <v>0.03539423356451116</v>
       </c>
       <c r="W85">
-        <v>0.2374540397254883</v>
+        <v>0.2274540397254883</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8301,7 +8655,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.1543376040112385</v>
+        <v>0.1608828798386871</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8312,13 +8666,13 @@
         <v>0.84</v>
       </c>
       <c r="B86">
-        <v>0.2413941016787875</v>
+        <v>0.2329294797373574</v>
       </c>
       <c r="C86">
-        <v>-36179.23626565665</v>
+        <v>-35728.95287187673</v>
       </c>
       <c r="D86">
-        <v>10074.93173434334</v>
+        <v>10525.21512812327</v>
       </c>
       <c r="E86">
         <v>40736.468</v>
@@ -8345,37 +8699,37 @@
         <v>1781.7</v>
       </c>
       <c r="M86">
-        <v>11683.2594144</v>
+        <v>11207.9437344</v>
       </c>
       <c r="N86">
-        <v>-9901.559414400001</v>
+        <v>-9426.243734399999</v>
       </c>
       <c r="O86">
-        <v>-2178.343071168</v>
+        <v>-2073.773621568</v>
       </c>
       <c r="P86">
-        <v>-7723.216343232</v>
+        <v>-7352.470112831999</v>
       </c>
       <c r="Q86">
-        <v>-6887.016343232001</v>
+        <v>-6516.270112832</v>
       </c>
       <c r="R86">
         <v>5.249999999999999</v>
       </c>
       <c r="S86">
-        <v>0.2615578044164512</v>
+        <v>0.2611539172825137</v>
       </c>
       <c r="T86">
-        <v>4.979655688945782</v>
+        <v>4.973531576963365</v>
       </c>
       <c r="U86">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.03355005534815731</v>
+        <v>0.03497287364112412</v>
       </c>
       <c r="W86">
-        <v>0.2375533963954229</v>
+        <v>0.2275533963954229</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8383,7 +8737,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.1525002515825333</v>
+        <v>0.1589676074596552</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8394,13 +8748,13 @@
         <v>0.85</v>
       </c>
       <c r="B87">
-        <v>0.2433941016787875</v>
+        <v>0.2348294797373575</v>
       </c>
       <c r="C87">
-        <v>-36846.20958072966</v>
+        <v>-36399.65905889115</v>
       </c>
       <c r="D87">
-        <v>9973.810419270345</v>
+        <v>10420.36094110885</v>
       </c>
       <c r="E87">
         <v>41302.32</v>
@@ -8427,37 +8781,37 @@
         <v>1781.7</v>
       </c>
       <c r="M87">
-        <v>11822.345836</v>
+        <v>11341.371636</v>
       </c>
       <c r="N87">
-        <v>-10040.645836</v>
+        <v>-9559.671635999999</v>
       </c>
       <c r="O87">
-        <v>-2208.94208392</v>
+        <v>-2103.12775992</v>
       </c>
       <c r="P87">
-        <v>-7831.70375208</v>
+        <v>-7456.543876079999</v>
       </c>
       <c r="Q87">
-        <v>-6995.503752080001</v>
+        <v>-6620.343876079999</v>
       </c>
       <c r="R87">
         <v>5.666666666666666</v>
       </c>
       <c r="S87">
-        <v>0.2759416580442146</v>
+        <v>0.275510845101348</v>
       </c>
       <c r="T87">
-        <v>5.311632734875501</v>
+        <v>5.305100348760924</v>
       </c>
       <c r="U87">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.03315534881464959</v>
+        <v>0.0345614280688756</v>
       </c>
       <c r="W87">
-        <v>0.2376504152613592</v>
+        <v>0.2276504152613591</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8465,7 +8819,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.15070613097568</v>
+        <v>0.157097400313071</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8476,13 +8830,13 @@
         <v>0.86</v>
       </c>
       <c r="B88">
-        <v>0.2453941016787874</v>
+        <v>0.2367294797373575</v>
       </c>
       <c r="C88">
-        <v>-37511.17317350414</v>
+        <v>-37068.29669861609</v>
       </c>
       <c r="D88">
-        <v>9874.698826495856</v>
+        <v>10317.57530138391</v>
       </c>
       <c r="E88">
         <v>41868.172</v>
@@ -8509,37 +8863,37 @@
         <v>1781.7</v>
       </c>
       <c r="M88">
-        <v>11961.4322576</v>
+        <v>11474.7995376</v>
       </c>
       <c r="N88">
-        <v>-10179.7322576</v>
+        <v>-9693.099537599999</v>
       </c>
       <c r="O88">
-        <v>-2239.541096672</v>
+        <v>-2132.481898272</v>
       </c>
       <c r="P88">
-        <v>-7940.191160928</v>
+        <v>-7560.617639327999</v>
       </c>
       <c r="Q88">
-        <v>-7103.991160928</v>
+        <v>-6724.417639327999</v>
       </c>
       <c r="R88">
         <v>6.142857142857142</v>
       </c>
       <c r="S88">
-        <v>0.2923803479045156</v>
+        <v>0.2919187626085871</v>
       </c>
       <c r="T88">
-        <v>5.691035073080895</v>
+        <v>5.684036087958133</v>
       </c>
       <c r="U88">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.03276982150285133</v>
+        <v>0.03415955099830728</v>
       </c>
       <c r="W88">
-        <v>0.2377451778745991</v>
+        <v>0.2277451778745992</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8547,7 +8901,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.1489537341038697</v>
+        <v>0.1552706863559422</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8558,13 +8912,13 @@
         <v>0.87</v>
       </c>
       <c r="B89">
-        <v>0.2473941016787874</v>
+        <v>0.2386294797373575</v>
       </c>
       <c r="C89">
-        <v>-38174.18636741512</v>
+        <v>-37734.92640513349</v>
       </c>
       <c r="D89">
-        <v>9777.537632584879</v>
+        <v>10216.7975948665</v>
       </c>
       <c r="E89">
         <v>42434.024</v>
@@ -8591,37 +8945,37 @@
         <v>1781.7</v>
       </c>
       <c r="M89">
-        <v>12100.5186792</v>
+        <v>11608.2274392</v>
       </c>
       <c r="N89">
-        <v>-10318.8186792</v>
+        <v>-9826.527439199999</v>
       </c>
       <c r="O89">
-        <v>-2270.140109424</v>
+        <v>-2161.836036624</v>
       </c>
       <c r="P89">
-        <v>-8048.678569776</v>
+        <v>-7664.691402576</v>
       </c>
       <c r="Q89">
-        <v>-7212.478569776</v>
+        <v>-6828.491402576</v>
       </c>
       <c r="R89">
         <v>6.692307692307692</v>
       </c>
       <c r="S89">
-        <v>0.3113480669740938</v>
+        <v>0.31085097511694</v>
       </c>
       <c r="T89">
-        <v>6.128807001779425</v>
+        <v>6.121269633185682</v>
       </c>
       <c r="U89">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.03239315688787603</v>
+        <v>0.03376691248108536</v>
       </c>
       <c r="W89">
-        <v>0.2378377620369601</v>
+        <v>0.2278377620369601</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8629,7 +8983,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.1472416222176184</v>
+        <v>0.1534859658231154</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8640,13 +8994,13 @@
         <v>0.88</v>
       </c>
       <c r="B90">
-        <v>0.2493941016787874</v>
+        <v>0.2405294797373575</v>
       </c>
       <c r="C90">
-        <v>-38835.30617381707</v>
+        <v>-38399.60644722251</v>
       </c>
       <c r="D90">
-        <v>9682.26982618293</v>
+        <v>10117.96955277748</v>
       </c>
       <c r="E90">
         <v>42999.876</v>
@@ -8673,37 +9027,37 @@
         <v>1781.7</v>
       </c>
       <c r="M90">
-        <v>12239.6051008</v>
+        <v>11741.6553408</v>
       </c>
       <c r="N90">
-        <v>-10457.9051008</v>
+        <v>-9959.955340799999</v>
       </c>
       <c r="O90">
-        <v>-2300.739122176</v>
+        <v>-2191.190174976</v>
       </c>
       <c r="P90">
-        <v>-8157.165978623999</v>
+        <v>-7768.765165823999</v>
       </c>
       <c r="Q90">
-        <v>-7320.965978623999</v>
+        <v>-6932.565165823999</v>
       </c>
       <c r="R90">
         <v>7.333333333333334</v>
       </c>
       <c r="S90">
-        <v>0.3334770725552683</v>
+        <v>0.3329385563766851</v>
       </c>
       <c r="T90">
-        <v>6.639540918594378</v>
+        <v>6.631375435951157</v>
       </c>
       <c r="U90">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.03202505283233199</v>
+        <v>0.03338319756652757</v>
       </c>
       <c r="W90">
-        <v>0.2379282420138128</v>
+        <v>0.2279282420138128</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8711,7 +9065,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.1455684219651454</v>
+        <v>0.1517418071205799</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8722,13 +9076,13 @@
         <v>0.89</v>
       </c>
       <c r="B91">
-        <v>0.2513941016787875</v>
+        <v>0.2424294797373575</v>
       </c>
       <c r="C91">
-        <v>-39494.58740353629</v>
+        <v>-39062.39286070444</v>
       </c>
       <c r="D91">
-        <v>9588.840596463713</v>
+        <v>10021.03513929556</v>
       </c>
       <c r="E91">
         <v>43565.728</v>
@@ -8755,37 +9109,37 @@
         <v>1781.7</v>
       </c>
       <c r="M91">
-        <v>12378.6915224</v>
+        <v>11875.0832424</v>
       </c>
       <c r="N91">
-        <v>-10596.9915224</v>
+        <v>-10093.3832424</v>
       </c>
       <c r="O91">
-        <v>-2331.338134928</v>
+        <v>-2220.544313328</v>
       </c>
       <c r="P91">
-        <v>-8265.653387472001</v>
+        <v>-7872.838929071999</v>
       </c>
       <c r="Q91">
-        <v>-7429.453387472001</v>
+        <v>-7036.638929071999</v>
       </c>
       <c r="R91">
         <v>8.090909090909092</v>
       </c>
       <c r="S91">
-        <v>0.3596295336966563</v>
+        <v>0.3590420615018383</v>
       </c>
       <c r="T91">
-        <v>7.243135547557503</v>
+        <v>7.234227748310352</v>
       </c>
       <c r="U91">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.03166522077803612</v>
+        <v>0.0330081054590385</v>
       </c>
       <c r="W91">
-        <v>0.2380166887327587</v>
+        <v>0.2280166887327587</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +9147,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.143932821718346</v>
+        <v>0.1500368429956296</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8804,13 +9158,13 @@
         <v>0.9</v>
       </c>
       <c r="B92">
-        <v>0.2533941016787875</v>
+        <v>0.2443294797373575</v>
       </c>
       <c r="C92">
-        <v>-40152.08277202635</v>
+        <v>-39723.33955439102</v>
       </c>
       <c r="D92">
-        <v>9497.197227973656</v>
+        <v>9925.940445608976</v>
       </c>
       <c r="E92">
         <v>44131.58</v>
@@ -8837,37 +9191,37 @@
         <v>1781.7</v>
       </c>
       <c r="M92">
-        <v>12517.777944</v>
+        <v>12008.511144</v>
       </c>
       <c r="N92">
-        <v>-10736.077944</v>
+        <v>-10226.811144</v>
       </c>
       <c r="O92">
-        <v>-2361.93714768</v>
+        <v>-2249.89845168</v>
       </c>
       <c r="P92">
-        <v>-8374.14079632</v>
+        <v>-7976.91269232</v>
       </c>
       <c r="Q92">
-        <v>-7537.94079632</v>
+        <v>-7140.71269232</v>
       </c>
       <c r="R92">
         <v>9.000000000000002</v>
       </c>
       <c r="S92">
-        <v>0.391012487066322</v>
+        <v>0.3903662676520221</v>
       </c>
       <c r="T92">
-        <v>7.967449102313254</v>
+        <v>7.957650523141388</v>
       </c>
       <c r="U92">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.03131338499161349</v>
+        <v>0.03264134873171584</v>
       </c>
       <c r="W92">
-        <v>0.2381031699690614</v>
+        <v>0.2281031699690614</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +9229,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.1423335681436977</v>
+        <v>0.1483697669623448</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8886,13 +9240,13 @@
         <v>0.91</v>
       </c>
       <c r="B93">
-        <v>0.2553941016787875</v>
+        <v>0.2462294797373575</v>
       </c>
       <c r="C93">
-        <v>-40807.84299855065</v>
+        <v>-40382.49841005722</v>
       </c>
       <c r="D93">
-        <v>9407.289001449351</v>
+        <v>9832.633589942781</v>
       </c>
       <c r="E93">
         <v>44697.432</v>
@@ -8919,37 +9273,37 @@
         <v>1781.7</v>
       </c>
       <c r="M93">
-        <v>12656.8643656</v>
+        <v>12141.9390456</v>
       </c>
       <c r="N93">
-        <v>-10875.1643656</v>
+        <v>-10360.2390456</v>
       </c>
       <c r="O93">
-        <v>-2392.536160432</v>
+        <v>-2279.252590032</v>
       </c>
       <c r="P93">
-        <v>-8482.628205167999</v>
+        <v>-8080.986455568</v>
       </c>
       <c r="Q93">
-        <v>-7646.428205167999</v>
+        <v>-7244.786455568</v>
       </c>
       <c r="R93">
         <v>10.11111111111111</v>
       </c>
       <c r="S93">
-        <v>0.4293694300736911</v>
+        <v>0.4286514085022469</v>
       </c>
       <c r="T93">
-        <v>8.852721224792505</v>
+        <v>8.841833914601544</v>
       </c>
       <c r="U93">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.03096928185983752</v>
+        <v>0.03228265259180688</v>
       </c>
       <c r="W93">
-        <v>0.238187750518852</v>
+        <v>0.228187750518852</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +9311,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.1407694629992615</v>
+        <v>0.1467393299627586</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8968,13 +9322,13 @@
         <v>0.92</v>
       </c>
       <c r="B94">
-        <v>0.2573941016787875</v>
+        <v>0.2481294797373575</v>
       </c>
       <c r="C94">
-        <v>-41461.91689978415</v>
+        <v>-41039.91937682766</v>
       </c>
       <c r="D94">
-        <v>9319.067100215851</v>
+        <v>9741.064623172339</v>
       </c>
       <c r="E94">
         <v>45263.284</v>
@@ -9001,37 +9355,37 @@
         <v>1781.7</v>
       </c>
       <c r="M94">
-        <v>12795.9507872</v>
+        <v>12275.3669472</v>
       </c>
       <c r="N94">
-        <v>-11014.2507872</v>
+        <v>-10493.6669472</v>
       </c>
       <c r="O94">
-        <v>-2423.135173184</v>
+        <v>-2308.606728384</v>
       </c>
       <c r="P94">
-        <v>-8591.115614016</v>
+        <v>-8185.060218815999</v>
       </c>
       <c r="Q94">
-        <v>-7754.915614016</v>
+        <v>-7348.860218815999</v>
       </c>
       <c r="R94">
         <v>11.50000000000001</v>
       </c>
       <c r="S94">
-        <v>0.4773156088329026</v>
+        <v>0.4765078345650278</v>
       </c>
       <c r="T94">
-        <v>9.959311377891572</v>
+        <v>9.94706315392674</v>
       </c>
       <c r="U94">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.03063265923092624</v>
+        <v>0.03193175419406985</v>
       </c>
       <c r="W94">
-        <v>0.2382704923610383</v>
+        <v>0.2282704923610384</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9393,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.1392393601405739</v>
+        <v>0.1451443372457721</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9050,13 +9404,13 @@
         <v>0.93</v>
       </c>
       <c r="B95">
-        <v>0.2593941016787875</v>
+        <v>0.2500294797373575</v>
       </c>
       <c r="C95">
-        <v>-42114.3514781972</v>
+        <v>-41695.65056033793</v>
       </c>
       <c r="D95">
-        <v>9232.484521802789</v>
+        <v>9651.185439662062</v>
       </c>
       <c r="E95">
         <v>45829.136</v>
@@ -9083,37 +9437,37 @@
         <v>1781.7</v>
       </c>
       <c r="M95">
-        <v>12935.0372088</v>
+        <v>12408.7948488</v>
       </c>
       <c r="N95">
-        <v>-11153.3372088</v>
+        <v>-10627.0948488</v>
       </c>
       <c r="O95">
-        <v>-2453.734185936</v>
+        <v>-2337.960866736</v>
       </c>
       <c r="P95">
-        <v>-8699.603022863999</v>
+        <v>-8289.133982063999</v>
       </c>
       <c r="Q95">
-        <v>-7863.403022863999</v>
+        <v>-7452.933982063999</v>
       </c>
       <c r="R95">
         <v>13.2857142857143</v>
       </c>
       <c r="S95">
-        <v>0.5389606958090316</v>
+        <v>0.5380375252171746</v>
       </c>
       <c r="T95">
-        <v>11.3820701461618</v>
+        <v>11.36807217591628</v>
       </c>
       <c r="U95">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.03030327579833563</v>
+        <v>0.03158840199843469</v>
       </c>
       <c r="W95">
-        <v>0.2383514548087691</v>
+        <v>0.2283514548087691</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9475,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.1377421627197075</v>
+        <v>0.1435836454474304</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9132,13 +9486,13 @@
         <v>0.9400000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2613941016787875</v>
+        <v>0.2519294797373575</v>
       </c>
       <c r="C96">
-        <v>-42765.19200555782</v>
+        <v>-42349.73830700485</v>
       </c>
       <c r="D96">
-        <v>9147.495994442188</v>
+        <v>9562.949692995153</v>
       </c>
       <c r="E96">
         <v>46394.988</v>
@@ -9165,37 +9519,37 @@
         <v>1781.7</v>
       </c>
       <c r="M96">
-        <v>13074.1236304</v>
+        <v>12542.2227504</v>
       </c>
       <c r="N96">
-        <v>-11292.4236304</v>
+        <v>-10760.5227504</v>
       </c>
       <c r="O96">
-        <v>-2484.333198688</v>
+        <v>-2367.315005088</v>
       </c>
       <c r="P96">
-        <v>-8808.090431712</v>
+        <v>-8393.207745312</v>
       </c>
       <c r="Q96">
-        <v>-7971.890431712</v>
+        <v>-7557.007745312</v>
       </c>
       <c r="R96">
         <v>15.66666666666668</v>
       </c>
       <c r="S96">
-        <v>0.621154145110537</v>
+        <v>0.6200771127533705</v>
       </c>
       <c r="T96">
-        <v>13.27908183718877</v>
+        <v>13.26275087190232</v>
       </c>
       <c r="U96">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.02998090052388526</v>
+        <v>0.03125235516866411</v>
       </c>
       <c r="W96">
-        <v>0.238430694651229</v>
+        <v>0.228430694651229</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9557,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.1362768205631149</v>
+        <v>0.1420561598575641</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9214,13 +9568,13 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2633941016787875</v>
+        <v>0.2538294797373575</v>
       </c>
       <c r="C97">
-        <v>-43414.48210186381</v>
+        <v>-43002.22728371595</v>
       </c>
       <c r="D97">
-        <v>9064.057898136192</v>
+        <v>9476.312716284046</v>
       </c>
       <c r="E97">
         <v>46960.84</v>
@@ -9247,37 +9601,37 @@
         <v>1781.7</v>
       </c>
       <c r="M97">
-        <v>13213.210052</v>
+        <v>12675.650652</v>
       </c>
       <c r="N97">
-        <v>-11431.510052</v>
+        <v>-10893.950652</v>
       </c>
       <c r="O97">
-        <v>-2514.93221144</v>
+        <v>-2396.66914344</v>
       </c>
       <c r="P97">
-        <v>-8916.577840560001</v>
+        <v>-8497.28150856</v>
       </c>
       <c r="Q97">
-        <v>-8080.377840560001</v>
+        <v>-7661.08150856</v>
       </c>
       <c r="R97">
         <v>19.00000000000003</v>
       </c>
       <c r="S97">
-        <v>0.7362249741326448</v>
+        <v>0.7349325353040449</v>
       </c>
       <c r="T97">
-        <v>15.93489820462653</v>
+        <v>15.91530104628279</v>
       </c>
       <c r="U97">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.02966531209731804</v>
+        <v>0.03092338300899396</v>
       </c>
       <c r="W97">
-        <v>0.2385082662864793</v>
+        <v>0.2285082662864792</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9639,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.1348423277150821</v>
+        <v>0.1405608318590635</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9296,13 +9650,13 @@
         <v>0.96</v>
       </c>
       <c r="B98">
-        <v>0.2653941016787875</v>
+        <v>0.2557294797373574</v>
       </c>
       <c r="C98">
-        <v>-44062.2638099944</v>
+        <v>-43653.16055322619</v>
       </c>
       <c r="D98">
-        <v>8982.128190005591</v>
+        <v>9391.231446773802</v>
       </c>
       <c r="E98">
         <v>47526.692</v>
@@ -9329,37 +9683,37 @@
         <v>1781.7</v>
       </c>
       <c r="M98">
-        <v>13352.2964736</v>
+        <v>12809.0785536</v>
       </c>
       <c r="N98">
-        <v>-11570.5964736</v>
+        <v>-11027.3785536</v>
       </c>
       <c r="O98">
-        <v>-2545.531224192</v>
+        <v>-2426.023281792</v>
       </c>
       <c r="P98">
-        <v>-9025.065249407999</v>
+        <v>-8601.355271807999</v>
       </c>
       <c r="Q98">
-        <v>-8188.865249407999</v>
+        <v>-7765.155271807999</v>
       </c>
       <c r="R98">
         <v>23.99999999999998</v>
       </c>
       <c r="S98">
-        <v>0.908831217665804</v>
+        <v>0.9072156691300542</v>
       </c>
       <c r="T98">
-        <v>19.91862275578312</v>
+        <v>19.89412630785345</v>
       </c>
       <c r="U98">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.02935629842963765</v>
+        <v>0.03060126443598361</v>
       </c>
       <c r="W98">
-        <v>0.2385842218459951</v>
+        <v>0.2285842218459951</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9721,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.1334377201347167</v>
+        <v>0.1390966565271983</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9378,13 +9732,13 @@
         <v>0.97</v>
       </c>
       <c r="B99">
-        <v>0.2673941016787875</v>
+        <v>0.2576294797373574</v>
       </c>
       <c r="C99">
-        <v>-44708.57766634927</v>
+        <v>-44302.57964552917</v>
       </c>
       <c r="D99">
-        <v>8901.666333650724</v>
+        <v>9307.664354470819</v>
       </c>
       <c r="E99">
         <v>48092.54399999999</v>
@@ -9411,37 +9765,37 @@
         <v>1781.7</v>
       </c>
       <c r="M99">
-        <v>13491.3828952</v>
+        <v>12942.5064552</v>
       </c>
       <c r="N99">
-        <v>-11709.6828952</v>
+        <v>-11160.8064552</v>
       </c>
       <c r="O99">
-        <v>-2576.130236944</v>
+        <v>-2455.377420144</v>
       </c>
       <c r="P99">
-        <v>-9133.552658255998</v>
+        <v>-8705.429035055999</v>
       </c>
       <c r="Q99">
-        <v>-8297.352658255997</v>
+        <v>-7869.229035055999</v>
       </c>
       <c r="R99">
         <v>32.33333333333331</v>
       </c>
       <c r="S99">
-        <v>1.196508290221072</v>
+        <v>1.194354225506739</v>
       </c>
       <c r="T99">
-        <v>26.55816367437749</v>
+        <v>26.5255017438046</v>
       </c>
       <c r="U99">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.02905365617778572</v>
+        <v>0.03028578748303533</v>
       </c>
       <c r="W99">
-        <v>0.2386586113115003</v>
+        <v>0.2286586113115003</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9803,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.1320620735353897</v>
+        <v>0.1376626703774333</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9460,13 +9814,13 @@
         <v>0.98</v>
       </c>
       <c r="B100">
-        <v>0.2693941016787875</v>
+        <v>0.2595294797373575</v>
       </c>
       <c r="C100">
-        <v>-45353.46276772461</v>
+        <v>-44950.52462545138</v>
       </c>
       <c r="D100">
-        <v>8822.63323227539</v>
+        <v>9225.571374548621</v>
       </c>
       <c r="E100">
         <v>48658.396</v>
@@ -9493,37 +9847,37 @@
         <v>1781.7</v>
       </c>
       <c r="M100">
-        <v>13630.4693168</v>
+        <v>13075.9343568</v>
       </c>
       <c r="N100">
-        <v>-11848.7693168</v>
+        <v>-11294.2343568</v>
       </c>
       <c r="O100">
-        <v>-2606.729249696</v>
+        <v>-2484.731558496</v>
       </c>
       <c r="P100">
-        <v>-9242.040067104001</v>
+        <v>-8809.502798304</v>
       </c>
       <c r="Q100">
-        <v>-8405.840067104</v>
+        <v>-7973.302798304</v>
       </c>
       <c r="R100">
         <v>48.99999999999996</v>
       </c>
       <c r="S100">
-        <v>1.771862435331608</v>
+        <v>1.768631338260109</v>
       </c>
       <c r="T100">
-        <v>39.83724551156623</v>
+        <v>39.7882526157069</v>
       </c>
       <c r="U100">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.02875719029842055</v>
+        <v>0.02997674883524925</v>
       </c>
       <c r="W100">
-        <v>0.2387314826246483</v>
+        <v>0.2287314826246482</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,7 +9885,7 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.1307145013564571</v>
+        <v>0.136257949251133</v>
       </c>
       <c r="Z100">
         <v>0</v>
@@ -9542,13 +9896,13 @@
         <v>0.99</v>
       </c>
       <c r="B101">
-        <v>0.2713941016787875</v>
+        <v>0.2614294797373575</v>
       </c>
       <c r="C101">
-        <v>-45996.9568346581</v>
+        <v>-45597.03415670063</v>
       </c>
       <c r="D101">
-        <v>8744.991165341899</v>
+        <v>9144.913843299375</v>
       </c>
       <c r="E101">
         <v>49224.248</v>
@@ -9575,37 +9929,37 @@
         <v>1781.7</v>
       </c>
       <c r="M101">
-        <v>13769.5557384</v>
+        <v>13209.3622584</v>
       </c>
       <c r="N101">
-        <v>-11987.8557384</v>
+        <v>-11427.6622584</v>
       </c>
       <c r="O101">
-        <v>-2637.328262448</v>
+        <v>-2514.085696848</v>
       </c>
       <c r="P101">
-        <v>-9350.527475952</v>
+        <v>-8913.576561551999</v>
       </c>
       <c r="Q101">
-        <v>-8514.327475951999</v>
+        <v>-8077.376561552</v>
       </c>
       <c r="R101">
         <v>98.99999999999991</v>
       </c>
       <c r="S101">
-        <v>3.497924870663216</v>
+        <v>3.491462676520217</v>
       </c>
       <c r="T101">
-        <v>79.67449102313246</v>
+        <v>79.5765052314138</v>
       </c>
       <c r="U101">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V101">
-        <v>0.02846671362873954</v>
+        <v>0.02967395339246895</v>
       </c>
       <c r="W101">
-        <v>0.2388028817900558</v>
+        <v>0.2288028817900558</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
@@ -9613,7 +9967,7 @@
         </is>
       </c>
       <c r="Y101">
-        <v>0.129394152857907</v>
+        <v>0.1348816063294044</v>
       </c>
       <c r="Z101">
         <v>0</v>

--- a/research/traditional_assets/database/data/denmark/denmark_transportation.xlsx
+++ b/research/traditional_assets/database/data/denmark/denmark_transportation.xlsx
@@ -1557,7 +1557,7 @@
         <v>0.907123348019059</v>
       </c>
       <c r="Z2">
-        <v>0.960224270129036</v>
+        <v>0.960224270129037</v>
       </c>
       <c r="AA2">
         <v>6795.1</v>
@@ -1638,7 +1638,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1775,22 +1775,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08129950326447477</v>
+        <v>0.08115574435729292</v>
       </c>
       <c r="C2">
-        <v>54714.38551556835</v>
+        <v>54355.89069389385</v>
       </c>
       <c r="D2">
-        <v>53436.98551556835</v>
+        <v>53644.34269389384</v>
       </c>
       <c r="E2">
-        <v>-6795.1</v>
+        <v>-6229.248000000001</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>565.852</v>
       </c>
       <c r="G2">
         <v>1277.4</v>
@@ -1811,28 +1811,28 @@
         <v>1781.7</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>28.4623556</v>
       </c>
       <c r="N2">
-        <v>1781.7</v>
+        <v>1753.2376444</v>
       </c>
       <c r="O2">
-        <v>391.974</v>
+        <v>385.712281768</v>
       </c>
       <c r="P2">
-        <v>1389.726</v>
+        <v>1367.525362632</v>
       </c>
       <c r="Q2">
-        <v>2225.926</v>
+        <v>2203.725362632</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08129950326447477</v>
+        <v>0.0815791963204979</v>
       </c>
       <c r="T2">
-        <v>0.8198499599185859</v>
+        <v>0.8263093838452171</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1849,7 +1849,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>62.59847305119047</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1857,22 +1857,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08115574435729292</v>
+        <v>0.08101198545011107</v>
       </c>
       <c r="C3">
-        <v>54355.89069389385</v>
+        <v>53999.01140104215</v>
       </c>
       <c r="D3">
-        <v>53644.34269389384</v>
+        <v>53853.31540104214</v>
       </c>
       <c r="E3">
-        <v>-6229.248000000001</v>
+        <v>-5663.396000000001</v>
       </c>
       <c r="F3">
-        <v>565.852</v>
+        <v>1131.704</v>
       </c>
       <c r="G3">
         <v>1277.4</v>
@@ -1893,28 +1893,28 @@
         <v>1781.7</v>
       </c>
       <c r="M3">
-        <v>28.4623556</v>
+        <v>56.9247112</v>
       </c>
       <c r="N3">
-        <v>1753.2376444</v>
+        <v>1724.7752888</v>
       </c>
       <c r="O3">
-        <v>385.712281768</v>
+        <v>379.450563536</v>
       </c>
       <c r="P3">
-        <v>1367.525362632</v>
+        <v>1345.324725264</v>
       </c>
       <c r="Q3">
-        <v>2203.725362632</v>
+        <v>2181.524725264</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.0815791963204979</v>
+        <v>0.08186459739807253</v>
       </c>
       <c r="T3">
-        <v>0.8263093838452171</v>
+        <v>0.832900632749943</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1931,7 +1931,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>62.59847305119047</v>
+        <v>31.29923652559523</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1939,22 +1939,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08101198545011107</v>
+        <v>0.08086822654292923</v>
       </c>
       <c r="C4">
-        <v>53999.01140104215</v>
+        <v>53643.76659083156</v>
       </c>
       <c r="D4">
-        <v>53853.31540104214</v>
+        <v>54063.92259083156</v>
       </c>
       <c r="E4">
-        <v>-5663.396000000001</v>
+        <v>-5097.544000000001</v>
       </c>
       <c r="F4">
-        <v>1131.704</v>
+        <v>1697.556</v>
       </c>
       <c r="G4">
         <v>1277.4</v>
@@ -1975,28 +1975,28 @@
         <v>1781.7</v>
       </c>
       <c r="M4">
-        <v>56.9247112</v>
+        <v>85.38706679999999</v>
       </c>
       <c r="N4">
-        <v>1724.7752888</v>
+        <v>1696.3129332</v>
       </c>
       <c r="O4">
-        <v>379.450563536</v>
+        <v>373.188845304</v>
       </c>
       <c r="P4">
-        <v>1345.324725264</v>
+        <v>1323.124087896</v>
       </c>
       <c r="Q4">
-        <v>2181.524725264</v>
+        <v>2159.324087896</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08186459739807253</v>
+        <v>0.08215588303394766</v>
       </c>
       <c r="T4">
-        <v>0.832900632749943</v>
+        <v>0.8396277836939414</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -2013,7 +2013,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>31.29923652559523</v>
+        <v>20.86615768373016</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -2021,22 +2021,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08086822654292923</v>
+        <v>0.08072446763574739</v>
       </c>
       <c r="C5">
-        <v>53643.76659083156</v>
+        <v>53290.17551473955</v>
       </c>
       <c r="D5">
-        <v>54063.92259083156</v>
+        <v>54276.18351473955</v>
       </c>
       <c r="E5">
-        <v>-5097.544000000001</v>
+        <v>-4531.692000000001</v>
       </c>
       <c r="F5">
-        <v>1697.556</v>
+        <v>2263.408</v>
       </c>
       <c r="G5">
         <v>1277.4</v>
@@ -2057,28 +2057,28 @@
         <v>1781.7</v>
       </c>
       <c r="M5">
-        <v>85.38706679999999</v>
+        <v>113.8494224</v>
       </c>
       <c r="N5">
-        <v>1696.3129332</v>
+        <v>1667.8505776</v>
       </c>
       <c r="O5">
-        <v>373.188845304</v>
+        <v>366.927127072</v>
       </c>
       <c r="P5">
-        <v>1323.124087896</v>
+        <v>1300.923450528</v>
       </c>
       <c r="Q5">
-        <v>2159.324087896</v>
+        <v>2137.123450528</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08215588303394766</v>
+        <v>0.08245323712057021</v>
       </c>
       <c r="T5">
-        <v>0.8396277836939414</v>
+        <v>0.8464950836159399</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -2095,7 +2095,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>20.86615768373016</v>
+        <v>15.64961826279762</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -2103,22 +2103,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08072446763574739</v>
+        <v>0.08058070872856554</v>
       </c>
       <c r="C6">
-        <v>53290.17551473955</v>
+        <v>52938.25772776897</v>
       </c>
       <c r="D6">
-        <v>54276.18351473955</v>
+        <v>54490.11772776897</v>
       </c>
       <c r="E6">
-        <v>-4531.692000000001</v>
+        <v>-3965.84</v>
       </c>
       <c r="F6">
-        <v>2263.408</v>
+        <v>2829.26</v>
       </c>
       <c r="G6">
         <v>1277.4</v>
@@ -2139,28 +2139,28 @@
         <v>1781.7</v>
       </c>
       <c r="M6">
-        <v>113.8494224</v>
+        <v>142.311778</v>
       </c>
       <c r="N6">
-        <v>1667.8505776</v>
+        <v>1639.388222</v>
       </c>
       <c r="O6">
-        <v>366.927127072</v>
+        <v>360.66540884</v>
       </c>
       <c r="P6">
-        <v>1300.923450528</v>
+        <v>1278.72281316</v>
       </c>
       <c r="Q6">
-        <v>2137.123450528</v>
+        <v>2114.92281316</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08245323712057021</v>
+        <v>0.08275685129322689</v>
       </c>
       <c r="T6">
-        <v>0.8464950836159399</v>
+        <v>0.8535069582731384</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -2177,7 +2177,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>15.64961826279762</v>
+        <v>12.51969461023809</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -2185,22 +2185,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08058070872856554</v>
+        <v>0.08043694982138369</v>
       </c>
       <c r="C7">
-        <v>52938.25772776897</v>
+        <v>52588.0330944535</v>
       </c>
       <c r="D7">
-        <v>54490.11772776897</v>
+        <v>54705.7450944535</v>
       </c>
       <c r="E7">
-        <v>-3965.84</v>
+        <v>-3399.988</v>
       </c>
       <c r="F7">
-        <v>2829.26</v>
+        <v>3395.112</v>
       </c>
       <c r="G7">
         <v>1277.4</v>
@@ -2221,28 +2221,28 @@
         <v>1781.7</v>
       </c>
       <c r="M7">
-        <v>142.311778</v>
+        <v>170.7741336</v>
       </c>
       <c r="N7">
-        <v>1639.388222</v>
+        <v>1610.9258664</v>
       </c>
       <c r="O7">
-        <v>360.66540884</v>
+        <v>354.403690608</v>
       </c>
       <c r="P7">
-        <v>1278.72281316</v>
+        <v>1256.522175792</v>
       </c>
       <c r="Q7">
-        <v>2114.92281316</v>
+        <v>2092.722175792</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08275685129322689</v>
+        <v>0.08306692534189755</v>
       </c>
       <c r="T7">
-        <v>0.8535069582731384</v>
+        <v>0.8606680217528303</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2259,7 +2259,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>12.51969461023809</v>
+        <v>10.43307884186508</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2267,22 +2267,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08043694982138369</v>
+        <v>0.08029319091420187</v>
       </c>
       <c r="C8">
-        <v>52588.0330944535</v>
+        <v>52239.5217950064</v>
       </c>
       <c r="D8">
-        <v>54705.7450944535</v>
+        <v>54923.0857950064</v>
       </c>
       <c r="E8">
-        <v>-3399.988000000001</v>
+        <v>-2834.136000000001</v>
       </c>
       <c r="F8">
-        <v>3395.112</v>
+        <v>3960.963999999999</v>
       </c>
       <c r="G8">
         <v>1277.4</v>
@@ -2303,28 +2303,28 @@
         <v>1781.7</v>
       </c>
       <c r="M8">
-        <v>170.7741336</v>
+        <v>199.2364892</v>
       </c>
       <c r="N8">
-        <v>1610.9258664</v>
+        <v>1582.4635108</v>
       </c>
       <c r="O8">
-        <v>354.403690608</v>
+        <v>348.141972376</v>
       </c>
       <c r="P8">
-        <v>1256.522175792</v>
+        <v>1234.321538424</v>
       </c>
       <c r="Q8">
-        <v>2092.722175792</v>
+        <v>2070.521538424</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08306692534189755</v>
+        <v>0.08338366764967942</v>
       </c>
       <c r="T8">
-        <v>0.8606680217528303</v>
+        <v>0.867983086597677</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2341,7 +2341,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>10.43307884186508</v>
+        <v>8.942639007312925</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2349,22 +2349,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08029319091420185</v>
+        <v>0.08024303200702002</v>
       </c>
       <c r="C9">
-        <v>52239.52179500643</v>
+        <v>51749.90907538091</v>
       </c>
       <c r="D9">
-        <v>54923.08579500642</v>
+        <v>54999.3250753809</v>
       </c>
       <c r="E9">
-        <v>-2834.136</v>
+        <v>-2268.284000000001</v>
       </c>
       <c r="F9">
-        <v>3960.964</v>
+        <v>4526.816</v>
       </c>
       <c r="G9">
         <v>1277.4</v>
@@ -2385,45 +2385,45 @@
         <v>1781.7</v>
       </c>
       <c r="M9">
-        <v>199.2364892</v>
+        <v>234.4890688</v>
       </c>
       <c r="N9">
-        <v>1582.4635108</v>
+        <v>1547.2109312</v>
       </c>
       <c r="O9">
-        <v>348.141972376</v>
+        <v>340.386404864</v>
       </c>
       <c r="P9">
-        <v>1234.321538424</v>
+        <v>1206.824526336</v>
       </c>
       <c r="Q9">
-        <v>2070.521538424</v>
+        <v>2043.024526336</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08338366764967942</v>
+        <v>0.08370729565980436</v>
       </c>
       <c r="T9">
-        <v>0.8679830865976772</v>
+        <v>0.8754571745913248</v>
       </c>
       <c r="U9">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V9">
         <v>0.22</v>
       </c>
       <c r="W9">
-        <v>0.039234</v>
+        <v>0.040404</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y9">
-        <v>8.942639007312923</v>
+        <v>7.59822199438919</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2431,22 +2431,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08024303200702002</v>
+        <v>0.08011097309983817</v>
       </c>
       <c r="C10">
-        <v>51749.90907538091</v>
+        <v>51385.79657776284</v>
       </c>
       <c r="D10">
-        <v>54999.3250753809</v>
+        <v>55201.06457776284</v>
       </c>
       <c r="E10">
-        <v>-2268.284000000001</v>
+        <v>-1702.432000000001</v>
       </c>
       <c r="F10">
-        <v>4526.816</v>
+        <v>5092.668</v>
       </c>
       <c r="G10">
         <v>1277.4</v>
@@ -2467,28 +2467,28 @@
         <v>1781.7</v>
       </c>
       <c r="M10">
-        <v>234.4890688</v>
+        <v>263.8002024</v>
       </c>
       <c r="N10">
-        <v>1547.2109312</v>
+        <v>1517.8997976</v>
       </c>
       <c r="O10">
-        <v>340.386404864</v>
+        <v>333.937955472</v>
       </c>
       <c r="P10">
-        <v>1206.824526336</v>
+        <v>1183.961842128</v>
       </c>
       <c r="Q10">
-        <v>2043.024526336</v>
+        <v>2020.161842128</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08370729565980436</v>
+        <v>0.08403803637344853</v>
       </c>
       <c r="T10">
-        <v>0.8754571745913248</v>
+        <v>0.8830955282551626</v>
       </c>
       <c r="U10">
         <v>0.0518</v>
@@ -2505,7 +2505,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>7.59822199438919</v>
+        <v>6.753975106123725</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2513,22 +2513,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08011097309983817</v>
+        <v>0.08011151419265632</v>
       </c>
       <c r="C11">
-        <v>51385.79657776284</v>
+        <v>50819.11495896857</v>
       </c>
       <c r="D11">
-        <v>55201.06457776284</v>
+        <v>55200.23495896856</v>
       </c>
       <c r="E11">
-        <v>-1702.432000000001</v>
+        <v>-1136.580000000001</v>
       </c>
       <c r="F11">
-        <v>5092.668</v>
+        <v>5658.52</v>
       </c>
       <c r="G11">
         <v>1277.4</v>
@@ -2549,45 +2549,45 @@
         <v>1781.7</v>
       </c>
       <c r="M11">
-        <v>263.8002024</v>
+        <v>302.73082</v>
       </c>
       <c r="N11">
-        <v>1517.8997976</v>
+        <v>1478.96918</v>
       </c>
       <c r="O11">
-        <v>333.937955472</v>
+        <v>325.3732196</v>
       </c>
       <c r="P11">
-        <v>1183.961842128</v>
+        <v>1153.5959604</v>
       </c>
       <c r="Q11">
-        <v>2020.161842128</v>
+        <v>1989.7959604</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08403803637344853</v>
+        <v>0.08437612688072925</v>
       </c>
       <c r="T11">
-        <v>0.8830955282551626</v>
+        <v>0.89090362311153</v>
       </c>
       <c r="U11">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V11">
         <v>0.22</v>
       </c>
       <c r="W11">
-        <v>0.040404</v>
+        <v>0.04173</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y11">
-        <v>6.753975106123725</v>
+        <v>5.885426531728749</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2595,22 +2595,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08011151419265632</v>
+        <v>0.08006135528547448</v>
       </c>
       <c r="C12">
-        <v>50819.11495896857</v>
+        <v>50330.27414709896</v>
       </c>
       <c r="D12">
-        <v>55200.23495896856</v>
+        <v>55277.24614709896</v>
       </c>
       <c r="E12">
-        <v>-1136.58</v>
+        <v>-570.728000000001</v>
       </c>
       <c r="F12">
-        <v>5658.52</v>
+        <v>6224.371999999999</v>
       </c>
       <c r="G12">
         <v>1277.4</v>
@@ -2631,45 +2631,45 @@
         <v>1781.7</v>
       </c>
       <c r="M12">
-        <v>302.73082</v>
+        <v>337.9833996</v>
       </c>
       <c r="N12">
-        <v>1478.96918</v>
+        <v>1443.7166004</v>
       </c>
       <c r="O12">
-        <v>325.3732196</v>
+        <v>317.617652088</v>
       </c>
       <c r="P12">
-        <v>1153.5959604</v>
+        <v>1126.098948312</v>
       </c>
       <c r="Q12">
-        <v>1989.7959604</v>
+        <v>1962.298948312</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08437612688072925</v>
+        <v>0.08472181492749942</v>
       </c>
       <c r="T12">
-        <v>0.89090362311153</v>
+        <v>0.8988871807736587</v>
       </c>
       <c r="U12">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V12">
         <v>0.22</v>
       </c>
       <c r="W12">
-        <v>0.04173</v>
+        <v>0.042354</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y12">
-        <v>5.885426531728749</v>
+        <v>5.271560680520476</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2677,22 +2677,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08006135528547448</v>
+        <v>0.07994879637829265</v>
       </c>
       <c r="C13">
-        <v>50330.27414709896</v>
+        <v>49938.02341271554</v>
       </c>
       <c r="D13">
-        <v>55277.24614709896</v>
+        <v>55450.84741271554</v>
       </c>
       <c r="E13">
-        <v>-570.728000000001</v>
+        <v>-4.876000000001113</v>
       </c>
       <c r="F13">
-        <v>6224.371999999999</v>
+        <v>6790.223999999999</v>
       </c>
       <c r="G13">
         <v>1277.4</v>
@@ -2713,28 +2713,28 @@
         <v>1781.7</v>
       </c>
       <c r="M13">
-        <v>337.9833996</v>
+        <v>368.7091632</v>
       </c>
       <c r="N13">
-        <v>1443.7166004</v>
+        <v>1412.9908368</v>
       </c>
       <c r="O13">
-        <v>317.617652088</v>
+        <v>310.8579840960001</v>
       </c>
       <c r="P13">
-        <v>1126.098948312</v>
+        <v>1102.132852704</v>
       </c>
       <c r="Q13">
-        <v>1962.298948312</v>
+        <v>1938.332852704</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08472181492749942</v>
+        <v>0.0850753595207871</v>
       </c>
       <c r="T13">
-        <v>0.8988871807736587</v>
+        <v>0.9070521829281083</v>
       </c>
       <c r="U13">
         <v>0.0543</v>
@@ -2751,7 +2751,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>5.271560680520476</v>
+        <v>4.83226395714377</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2759,22 +2759,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.07994879637829265</v>
+        <v>0.07983623747111079</v>
       </c>
       <c r="C14">
-        <v>49938.02341271554</v>
+        <v>49546.86652246857</v>
       </c>
       <c r="D14">
-        <v>55450.84741271554</v>
+        <v>55625.54252246857</v>
       </c>
       <c r="E14">
-        <v>-4.876000000001113</v>
+        <v>560.9759999999997</v>
       </c>
       <c r="F14">
-        <v>6790.223999999999</v>
+        <v>7356.076</v>
       </c>
       <c r="G14">
         <v>1277.4</v>
@@ -2795,28 +2795,28 @@
         <v>1781.7</v>
       </c>
       <c r="M14">
-        <v>368.7091632</v>
+        <v>399.4349268</v>
       </c>
       <c r="N14">
-        <v>1412.9908368</v>
+        <v>1382.2650732</v>
       </c>
       <c r="O14">
-        <v>310.8579840960001</v>
+        <v>304.098316104</v>
       </c>
       <c r="P14">
-        <v>1102.132852704</v>
+        <v>1078.166757096</v>
       </c>
       <c r="Q14">
-        <v>1938.332852704</v>
+        <v>1914.366757096</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.0850753595207871</v>
+        <v>0.08543703157598942</v>
       </c>
       <c r="T14">
-        <v>0.9070521829281083</v>
+        <v>0.9154048862815107</v>
       </c>
       <c r="U14">
         <v>0.0543</v>
@@ -2833,7 +2833,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>4.83226395714377</v>
+        <v>4.460551345055787</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2841,22 +2841,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.07983623747111079</v>
+        <v>0.07983287856392896</v>
       </c>
       <c r="C15">
-        <v>49546.86652246857</v>
+        <v>48986.24457181655</v>
       </c>
       <c r="D15">
-        <v>55625.54252246857</v>
+        <v>55630.77257181655</v>
       </c>
       <c r="E15">
-        <v>560.9759999999997</v>
+        <v>1126.828</v>
       </c>
       <c r="F15">
-        <v>7356.076</v>
+        <v>7921.928000000001</v>
       </c>
       <c r="G15">
         <v>1277.4</v>
@@ -2877,45 +2877,45 @@
         <v>1781.7</v>
       </c>
       <c r="M15">
-        <v>399.4349268</v>
+        <v>438.0826184000001</v>
       </c>
       <c r="N15">
-        <v>1382.2650732</v>
+        <v>1343.6173816</v>
       </c>
       <c r="O15">
-        <v>304.098316104</v>
+        <v>295.595823952</v>
       </c>
       <c r="P15">
-        <v>1078.166757096</v>
+        <v>1048.021557648</v>
       </c>
       <c r="Q15">
-        <v>1914.366757096</v>
+        <v>1884.221557648</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.08543703157598942</v>
+        <v>0.08580711460921971</v>
       </c>
       <c r="T15">
-        <v>0.9154048862815107</v>
+        <v>0.9239518385501087</v>
       </c>
       <c r="U15">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V15">
         <v>0.22</v>
       </c>
       <c r="W15">
-        <v>0.042354</v>
+        <v>0.04313400000000001</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y15">
-        <v>4.460551345055787</v>
+        <v>4.067041067521158</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2923,22 +2923,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.07983287856392896</v>
+        <v>0.0797281196567471</v>
       </c>
       <c r="C16">
-        <v>48986.24457181655</v>
+        <v>48584.0045043118</v>
       </c>
       <c r="D16">
-        <v>55630.77257181655</v>
+        <v>55794.3845043118</v>
       </c>
       <c r="E16">
-        <v>1126.828</v>
+        <v>1692.68</v>
       </c>
       <c r="F16">
-        <v>7921.928000000001</v>
+        <v>8487.780000000001</v>
       </c>
       <c r="G16">
         <v>1277.4</v>
@@ -2959,28 +2959,28 @@
         <v>1781.7</v>
       </c>
       <c r="M16">
-        <v>438.0826184000001</v>
+        <v>469.3742340000001</v>
       </c>
       <c r="N16">
-        <v>1343.6173816</v>
+        <v>1312.325766</v>
       </c>
       <c r="O16">
-        <v>295.595823952</v>
+        <v>288.71166852</v>
       </c>
       <c r="P16">
-        <v>1048.021557648</v>
+        <v>1023.61409748</v>
       </c>
       <c r="Q16">
-        <v>1884.221557648</v>
+        <v>1859.81409748</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.08580711460921971</v>
+        <v>0.086185905478526</v>
       </c>
       <c r="T16">
-        <v>0.9239518385501087</v>
+        <v>0.9326998955779677</v>
       </c>
       <c r="U16">
         <v>0.0553</v>
@@ -2997,7 +2997,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>4.067041067521158</v>
+        <v>3.79590499635308</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -3005,22 +3005,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.0797281196567471</v>
+        <v>0.07962336074956525</v>
       </c>
       <c r="C17">
-        <v>48584.0045043118</v>
+        <v>48182.72965168901</v>
       </c>
       <c r="D17">
-        <v>55794.3845043118</v>
+        <v>55958.961651689</v>
       </c>
       <c r="E17">
-        <v>1692.679999999998</v>
+        <v>2258.531999999999</v>
       </c>
       <c r="F17">
-        <v>8487.779999999999</v>
+        <v>9053.632</v>
       </c>
       <c r="G17">
         <v>1277.4</v>
@@ -3041,28 +3041,28 @@
         <v>1781.7</v>
       </c>
       <c r="M17">
-        <v>469.3742339999999</v>
+        <v>500.6658496</v>
       </c>
       <c r="N17">
-        <v>1312.325766</v>
+        <v>1281.0341504</v>
       </c>
       <c r="O17">
-        <v>288.71166852</v>
+        <v>281.827513088</v>
       </c>
       <c r="P17">
-        <v>1023.61409748</v>
+        <v>999.2066373120001</v>
       </c>
       <c r="Q17">
-        <v>1859.81409748</v>
+        <v>1835.406637312</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.086185905478526</v>
+        <v>0.08657371517805387</v>
       </c>
       <c r="T17">
-        <v>0.9326998955779677</v>
+        <v>0.9416562396779187</v>
       </c>
       <c r="U17">
         <v>0.0553</v>
@@ -3079,7 +3079,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>3.795904996353081</v>
+        <v>3.558660934081013</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -3087,22 +3087,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.07962336074956525</v>
+        <v>0.07951860184238341</v>
       </c>
       <c r="C18">
-        <v>48182.72965168901</v>
+        <v>47782.42858052348</v>
       </c>
       <c r="D18">
-        <v>55958.961651689</v>
+        <v>56124.51258052348</v>
       </c>
       <c r="E18">
-        <v>2258.531999999999</v>
+        <v>2824.384</v>
       </c>
       <c r="F18">
-        <v>9053.632</v>
+        <v>9619.484</v>
       </c>
       <c r="G18">
         <v>1277.4</v>
@@ -3123,28 +3123,28 @@
         <v>1781.7</v>
       </c>
       <c r="M18">
-        <v>500.6658496</v>
+        <v>531.9574652</v>
       </c>
       <c r="N18">
-        <v>1281.0341504</v>
+        <v>1249.7425348</v>
       </c>
       <c r="O18">
-        <v>281.827513088</v>
+        <v>274.943357656</v>
       </c>
       <c r="P18">
-        <v>999.2066373120001</v>
+        <v>974.7991771440002</v>
       </c>
       <c r="Q18">
-        <v>1835.406637312</v>
+        <v>1810.999177144</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.08657371517805387</v>
+        <v>0.08697086968961856</v>
       </c>
       <c r="T18">
-        <v>0.9416562396779187</v>
+        <v>0.9508283992983504</v>
       </c>
       <c r="U18">
         <v>0.0553</v>
@@ -3161,7 +3161,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>3.558660934081013</v>
+        <v>3.349327937958601</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -3169,22 +3169,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.07951860184238341</v>
+        <v>0.07941384293520155</v>
       </c>
       <c r="C19">
-        <v>47782.42858052348</v>
+        <v>47383.10995906605</v>
       </c>
       <c r="D19">
-        <v>56124.51258052348</v>
+        <v>56291.04595906605</v>
       </c>
       <c r="E19">
-        <v>2824.384</v>
+        <v>3390.236000000001</v>
       </c>
       <c r="F19">
-        <v>9619.484</v>
+        <v>10185.336</v>
       </c>
       <c r="G19">
         <v>1277.4</v>
@@ -3205,28 +3205,28 @@
         <v>1781.7</v>
       </c>
       <c r="M19">
-        <v>531.9574652</v>
+        <v>563.2490808000001</v>
       </c>
       <c r="N19">
-        <v>1249.7425348</v>
+        <v>1218.4509192</v>
       </c>
       <c r="O19">
-        <v>274.943357656</v>
+        <v>268.059202224</v>
       </c>
       <c r="P19">
-        <v>974.7991771440002</v>
+        <v>950.391716976</v>
       </c>
       <c r="Q19">
-        <v>1810.999177144</v>
+        <v>1786.591716976</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.08697086968961856</v>
+        <v>0.08737771089658727</v>
       </c>
       <c r="T19">
-        <v>0.9508283992983504</v>
+        <v>0.9602242701290366</v>
       </c>
       <c r="U19">
         <v>0.0553</v>
@@ -3243,7 +3243,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>3.349327937958601</v>
+        <v>3.163254163627567</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3251,22 +3251,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.07941384293520157</v>
+        <v>0.07967958402801972</v>
       </c>
       <c r="C20">
-        <v>47383.10995906603</v>
+        <v>46396.72587669203</v>
       </c>
       <c r="D20">
-        <v>56291.04595906602</v>
+        <v>55870.51387669204</v>
       </c>
       <c r="E20">
-        <v>3390.235999999999</v>
+        <v>3956.088</v>
       </c>
       <c r="F20">
-        <v>10185.336</v>
+        <v>10751.188</v>
       </c>
       <c r="G20">
         <v>1277.4</v>
@@ -3287,45 +3287,45 @@
         <v>1781.7</v>
       </c>
       <c r="M20">
-        <v>563.2490808</v>
+        <v>621.4186664</v>
       </c>
       <c r="N20">
-        <v>1218.4509192</v>
+        <v>1160.2813336</v>
       </c>
       <c r="O20">
-        <v>268.059202224</v>
+        <v>255.261893392</v>
       </c>
       <c r="P20">
-        <v>950.391716976</v>
+        <v>905.0194402079999</v>
       </c>
       <c r="Q20">
-        <v>1786.591716976</v>
+        <v>1741.219440208</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.08737771089658727</v>
+        <v>0.08779459756545645</v>
       </c>
       <c r="T20">
-        <v>0.9602242701290364</v>
+        <v>0.9698521377703568</v>
       </c>
       <c r="U20">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V20">
         <v>0.22</v>
       </c>
       <c r="W20">
-        <v>0.04313400000000001</v>
+        <v>0.04508400000000001</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y20">
-        <v>3.163254163627567</v>
+        <v>2.867149148128647</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3333,22 +3333,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.07967958402801972</v>
+        <v>0.07959432512083789</v>
       </c>
       <c r="C21">
-        <v>46396.72587669203</v>
+        <v>45965.1088603879</v>
       </c>
       <c r="D21">
-        <v>55870.51387669204</v>
+        <v>56004.7488603879</v>
       </c>
       <c r="E21">
-        <v>3956.088</v>
+        <v>4521.940000000001</v>
       </c>
       <c r="F21">
-        <v>10751.188</v>
+        <v>11317.04</v>
       </c>
       <c r="G21">
         <v>1277.4</v>
@@ -3369,28 +3369,28 @@
         <v>1781.7</v>
       </c>
       <c r="M21">
-        <v>621.4186664</v>
+        <v>654.1249120000001</v>
       </c>
       <c r="N21">
-        <v>1160.2813336</v>
+        <v>1127.575088</v>
       </c>
       <c r="O21">
-        <v>255.261893392</v>
+        <v>248.06651936</v>
       </c>
       <c r="P21">
-        <v>905.0194402079999</v>
+        <v>879.50856864</v>
       </c>
       <c r="Q21">
-        <v>1741.219440208</v>
+        <v>1715.70856864</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.08779459756545645</v>
+        <v>0.08822190640104735</v>
       </c>
       <c r="T21">
-        <v>0.9698521377703568</v>
+        <v>0.9797207021027102</v>
       </c>
       <c r="U21">
         <v>0.0578</v>
@@ -3407,7 +3407,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>2.867149148128647</v>
+        <v>2.723791690722215</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3415,22 +3415,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.07959432512083789</v>
+        <v>0.07950906621365605</v>
       </c>
       <c r="C22">
-        <v>45965.1088603879</v>
+        <v>45534.13842585084</v>
       </c>
       <c r="D22">
-        <v>56004.7488603879</v>
+        <v>56139.63042585084</v>
       </c>
       <c r="E22">
-        <v>4521.940000000001</v>
+        <v>5087.791999999999</v>
       </c>
       <c r="F22">
-        <v>11317.04</v>
+        <v>11882.892</v>
       </c>
       <c r="G22">
         <v>1277.4</v>
@@ -3451,28 +3451,28 @@
         <v>1781.7</v>
       </c>
       <c r="M22">
-        <v>654.1249120000001</v>
+        <v>686.8311576</v>
       </c>
       <c r="N22">
-        <v>1127.575088</v>
+        <v>1094.8688424</v>
       </c>
       <c r="O22">
-        <v>248.06651936</v>
+        <v>240.871145328</v>
       </c>
       <c r="P22">
-        <v>879.50856864</v>
+        <v>853.9976970720002</v>
       </c>
       <c r="Q22">
-        <v>1715.70856864</v>
+        <v>1690.197697072</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.08822190640104735</v>
+        <v>0.0886600331818431</v>
       </c>
       <c r="T22">
-        <v>0.9797207021027102</v>
+        <v>0.9898391035067687</v>
       </c>
       <c r="U22">
         <v>0.0578</v>
@@ -3489,7 +3489,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>2.723791690722215</v>
+        <v>2.594087324497348</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3497,22 +3497,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.07950906621365603</v>
+        <v>0.08002440730647419</v>
       </c>
       <c r="C23">
-        <v>45534.13842585089</v>
+        <v>44162.76759461478</v>
       </c>
       <c r="D23">
-        <v>56139.63042585089</v>
+        <v>55334.11159461478</v>
       </c>
       <c r="E23">
-        <v>5087.791999999999</v>
+        <v>5653.643999999998</v>
       </c>
       <c r="F23">
-        <v>11882.892</v>
+        <v>12448.744</v>
       </c>
       <c r="G23">
         <v>1277.4</v>
@@ -3533,45 +3533,45 @@
         <v>1781.7</v>
       </c>
       <c r="M23">
-        <v>686.8311576</v>
+        <v>763.1080072</v>
       </c>
       <c r="N23">
-        <v>1094.8688424</v>
+        <v>1018.5919928</v>
       </c>
       <c r="O23">
-        <v>240.871145328</v>
+        <v>224.090238416</v>
       </c>
       <c r="P23">
-        <v>853.9976970720002</v>
+        <v>794.501754384</v>
       </c>
       <c r="Q23">
-        <v>1690.197697072</v>
+        <v>1630.701754384</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.08866003318184307</v>
+        <v>0.08910939398265921</v>
       </c>
       <c r="T23">
-        <v>0.9898391035067685</v>
+        <v>1.000216951100675</v>
       </c>
       <c r="U23">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V23">
         <v>0.22</v>
       </c>
       <c r="W23">
-        <v>0.04508400000000001</v>
+        <v>0.047814</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y23">
-        <v>2.594087324497348</v>
+        <v>2.334794004504583</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3579,22 +3579,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08002440730647419</v>
+        <v>0.08046876839929236</v>
       </c>
       <c r="C24">
-        <v>44162.76759461478</v>
+        <v>42920.67673191128</v>
       </c>
       <c r="D24">
-        <v>55334.11159461478</v>
+        <v>54657.87273191127</v>
       </c>
       <c r="E24">
-        <v>5653.643999999998</v>
+        <v>6219.495999999999</v>
       </c>
       <c r="F24">
-        <v>12448.744</v>
+        <v>13014.596</v>
       </c>
       <c r="G24">
         <v>1277.4</v>
@@ -3615,45 +3615,45 @@
         <v>1781.7</v>
       </c>
       <c r="M24">
-        <v>763.1080072</v>
+        <v>834.2356036</v>
       </c>
       <c r="N24">
-        <v>1018.5919928</v>
+        <v>947.4643964000001</v>
       </c>
       <c r="O24">
-        <v>224.090238416</v>
+        <v>208.442167208</v>
       </c>
       <c r="P24">
-        <v>794.501754384</v>
+        <v>739.0222291920001</v>
       </c>
       <c r="Q24">
-        <v>1630.701754384</v>
+        <v>1575.222229192</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.08910939398265921</v>
+        <v>0.08957042649258747</v>
       </c>
       <c r="T24">
-        <v>1.000216951100675</v>
+        <v>1.01086435317754</v>
       </c>
       <c r="U24">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V24">
         <v>0.22</v>
       </c>
       <c r="W24">
-        <v>0.047814</v>
+        <v>0.04999800000000001</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y24">
-        <v>2.334794004504583</v>
+        <v>2.135727595791142</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3661,22 +3661,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08046876839929236</v>
+        <v>0.0804326494921105</v>
       </c>
       <c r="C25">
-        <v>42920.67673191128</v>
+        <v>42409.17355061347</v>
       </c>
       <c r="D25">
-        <v>54657.87273191127</v>
+        <v>54712.22155061347</v>
       </c>
       <c r="E25">
-        <v>6219.495999999999</v>
+        <v>6785.348</v>
       </c>
       <c r="F25">
-        <v>13014.596</v>
+        <v>13580.448</v>
       </c>
       <c r="G25">
         <v>1277.4</v>
@@ -3697,28 +3697,28 @@
         <v>1781.7</v>
       </c>
       <c r="M25">
-        <v>834.2356036</v>
+        <v>870.5067168</v>
       </c>
       <c r="N25">
-        <v>947.4643964000001</v>
+        <v>911.1932832</v>
       </c>
       <c r="O25">
-        <v>208.442167208</v>
+        <v>200.462522304</v>
       </c>
       <c r="P25">
-        <v>739.0222291920001</v>
+        <v>710.730760896</v>
       </c>
       <c r="Q25">
-        <v>1575.222229192</v>
+        <v>1546.930760896</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.08957042649258747</v>
+        <v>0.09004359143698751</v>
       </c>
       <c r="T25">
-        <v>1.01086435317754</v>
+        <v>1.021791950045901</v>
       </c>
       <c r="U25">
         <v>0.0641</v>
@@ -3735,7 +3735,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>2.135727595791142</v>
+        <v>2.046738945966511</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3743,22 +3743,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.0804326494921105</v>
+        <v>0.08191753058492866</v>
       </c>
       <c r="C26">
-        <v>42409.17355061348</v>
+        <v>39694.60667683034</v>
       </c>
       <c r="D26">
-        <v>54712.22155061347</v>
+        <v>52563.50667683034</v>
       </c>
       <c r="E26">
-        <v>6785.347999999998</v>
+        <v>7351.199999999999</v>
       </c>
       <c r="F26">
-        <v>13580.448</v>
+        <v>14146.3</v>
       </c>
       <c r="G26">
         <v>1277.4</v>
@@ -3779,45 +3779,45 @@
         <v>1781.7</v>
       </c>
       <c r="M26">
-        <v>870.5067167999999</v>
+        <v>1017.11897</v>
       </c>
       <c r="N26">
-        <v>911.1932832000001</v>
+        <v>764.5810300000001</v>
       </c>
       <c r="O26">
-        <v>200.462522304</v>
+        <v>168.2078266</v>
       </c>
       <c r="P26">
-        <v>710.7307608960001</v>
+        <v>596.3732034000001</v>
       </c>
       <c r="Q26">
-        <v>1546.930760896</v>
+        <v>1432.5732034</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09004359143698751</v>
+        <v>0.09052937411323821</v>
       </c>
       <c r="T26">
-        <v>1.021791950045901</v>
+        <v>1.033010949497418</v>
       </c>
       <c r="U26">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V26">
         <v>0.22</v>
       </c>
       <c r="W26">
-        <v>0.04999800000000001</v>
+        <v>0.05608200000000001</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y26">
-        <v>2.046738945966511</v>
+        <v>1.751712486495066</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3825,22 +3825,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08191753058492866</v>
+        <v>0.08273317167774683</v>
       </c>
       <c r="C27">
-        <v>39694.60667683034</v>
+        <v>38018.77003649347</v>
       </c>
       <c r="D27">
-        <v>52563.50667683034</v>
+        <v>51453.52203649347</v>
       </c>
       <c r="E27">
-        <v>7351.199999999999</v>
+        <v>7917.052</v>
       </c>
       <c r="F27">
-        <v>14146.3</v>
+        <v>14712.152</v>
       </c>
       <c r="G27">
         <v>1277.4</v>
@@ -3861,45 +3861,45 @@
         <v>1781.7</v>
       </c>
       <c r="M27">
-        <v>1017.11897</v>
+        <v>1115.1811216</v>
       </c>
       <c r="N27">
-        <v>764.5810300000001</v>
+        <v>666.5188783999999</v>
       </c>
       <c r="O27">
-        <v>168.2078266</v>
+        <v>146.634153248</v>
       </c>
       <c r="P27">
-        <v>596.3732034000001</v>
+        <v>519.884725152</v>
       </c>
       <c r="Q27">
-        <v>1432.5732034</v>
+        <v>1356.084725152</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09052937411323821</v>
+        <v>0.09102828605100921</v>
       </c>
       <c r="T27">
-        <v>1.033010949497418</v>
+        <v>1.044533165150328</v>
       </c>
       <c r="U27">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V27">
         <v>0.22</v>
       </c>
       <c r="W27">
-        <v>0.05608200000000001</v>
+        <v>0.05912400000000001</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y27">
-        <v>1.751712486495066</v>
+        <v>1.597677691533834</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3907,22 +3907,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08273317167774683</v>
+        <v>0.08278831277056496</v>
       </c>
       <c r="C28">
-        <v>38018.77003649347</v>
+        <v>37379.56730360111</v>
       </c>
       <c r="D28">
-        <v>51453.52203649347</v>
+        <v>51380.17130360111</v>
       </c>
       <c r="E28">
-        <v>7917.052</v>
+        <v>8482.904</v>
       </c>
       <c r="F28">
-        <v>14712.152</v>
+        <v>15278.004</v>
       </c>
       <c r="G28">
         <v>1277.4</v>
@@ -3943,28 +3943,28 @@
         <v>1781.7</v>
       </c>
       <c r="M28">
-        <v>1115.1811216</v>
+        <v>1158.0727032</v>
       </c>
       <c r="N28">
-        <v>666.5188783999999</v>
+        <v>623.6272967999998</v>
       </c>
       <c r="O28">
-        <v>146.634153248</v>
+        <v>137.198005296</v>
       </c>
       <c r="P28">
-        <v>519.884725152</v>
+        <v>486.4292915039999</v>
       </c>
       <c r="Q28">
-        <v>1356.084725152</v>
+        <v>1322.629291504</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09102828605100921</v>
+        <v>0.09154086680899311</v>
       </c>
       <c r="T28">
-        <v>1.044533165150328</v>
+        <v>1.056371057944414</v>
       </c>
       <c r="U28">
         <v>0.07580000000000001</v>
@@ -3981,7 +3981,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>1.597677691533834</v>
+        <v>1.538504443699247</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3989,22 +3989,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08278831277056496</v>
+        <v>0.09268291375325338</v>
       </c>
       <c r="C29">
-        <v>37379.56730360111</v>
+        <v>26347.61370008667</v>
       </c>
       <c r="D29">
-        <v>51380.17130360111</v>
+        <v>40914.06970008666</v>
       </c>
       <c r="E29">
-        <v>8482.904</v>
+        <v>9048.756000000001</v>
       </c>
       <c r="F29">
-        <v>15278.004</v>
+        <v>15843.856</v>
       </c>
       <c r="G29">
         <v>1277.4</v>
@@ -4025,45 +4025,45 @@
         <v>1781.7</v>
       </c>
       <c r="M29">
-        <v>1158.0727032</v>
+        <v>1879.0813216</v>
       </c>
       <c r="N29">
-        <v>623.6272967999998</v>
+        <v>-97.38132160000032</v>
       </c>
       <c r="O29">
-        <v>137.198005296</v>
+        <v>-21.42389075200007</v>
       </c>
       <c r="P29">
-        <v>486.4292915039999</v>
+        <v>-75.95743084800026</v>
       </c>
       <c r="Q29">
-        <v>1322.629291504</v>
+        <v>760.2425691519998</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.09154086680899311</v>
+        <v>0.09222508441819183</v>
       </c>
       <c r="T29">
-        <v>1.056371057944414</v>
+        <v>1.072172850304661</v>
       </c>
       <c r="U29">
-        <v>0.07580000000000001</v>
+        <v>0.1186</v>
       </c>
       <c r="V29">
-        <v>0.22</v>
+        <v>0.2085987421056593</v>
       </c>
       <c r="W29">
-        <v>0.05912400000000001</v>
+        <v>0.09386018918626882</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y29">
-        <v>1.538504443699247</v>
+        <v>0.9481761004802698</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -4071,22 +4071,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.09268291375325338</v>
+        <v>0.09341091375325339</v>
       </c>
       <c r="C30">
-        <v>26347.61370008667</v>
+        <v>25177.62589087672</v>
       </c>
       <c r="D30">
-        <v>40914.06970008666</v>
+        <v>40309.93389087672</v>
       </c>
       <c r="E30">
-        <v>9048.756000000001</v>
+        <v>9614.608000000002</v>
       </c>
       <c r="F30">
-        <v>15843.856</v>
+        <v>16409.708</v>
       </c>
       <c r="G30">
         <v>1277.4</v>
@@ -4107,37 +4107,37 @@
         <v>1781.7</v>
       </c>
       <c r="M30">
-        <v>1879.0813216</v>
+        <v>1946.1913688</v>
       </c>
       <c r="N30">
-        <v>-97.38132160000032</v>
+        <v>-164.4913688000004</v>
       </c>
       <c r="O30">
-        <v>-21.42389075200007</v>
+        <v>-36.18810113600009</v>
       </c>
       <c r="P30">
-        <v>-75.95743084800026</v>
+        <v>-128.3032676640003</v>
       </c>
       <c r="Q30">
-        <v>760.2425691519998</v>
+        <v>707.8967323359998</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.09222508441819183</v>
+        <v>0.09287895884661707</v>
       </c>
       <c r="T30">
-        <v>1.072172850304661</v>
+        <v>1.08727387636529</v>
       </c>
       <c r="U30">
         <v>0.1186</v>
       </c>
       <c r="V30">
-        <v>0.2085987421056593</v>
+        <v>0.2014056820330504</v>
       </c>
       <c r="W30">
-        <v>0.09386018918626882</v>
+        <v>0.09471328611088023</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -4145,7 +4145,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>0.9481761004802698</v>
+        <v>0.9154803728775018</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -4153,22 +4153,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.09341091375325339</v>
+        <v>0.09413891375325338</v>
       </c>
       <c r="C31">
-        <v>25177.62589087673</v>
+        <v>24025.21977006074</v>
       </c>
       <c r="D31">
-        <v>40309.93389087672</v>
+        <v>39723.37977006073</v>
       </c>
       <c r="E31">
-        <v>9614.607999999998</v>
+        <v>10180.46</v>
       </c>
       <c r="F31">
-        <v>16409.708</v>
+        <v>16975.56</v>
       </c>
       <c r="G31">
         <v>1277.4</v>
@@ -4189,37 +4189,37 @@
         <v>1781.7</v>
       </c>
       <c r="M31">
-        <v>1946.1913688</v>
+        <v>2013.301416</v>
       </c>
       <c r="N31">
-        <v>-164.4913687999999</v>
+        <v>-231.601416</v>
       </c>
       <c r="O31">
-        <v>-36.18810113599998</v>
+        <v>-50.95231151999999</v>
       </c>
       <c r="P31">
-        <v>-128.3032676639999</v>
+        <v>-180.64910448</v>
       </c>
       <c r="Q31">
-        <v>707.8967323360001</v>
+        <v>655.55089552</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.09287895884661707</v>
+        <v>0.09355151540156874</v>
       </c>
       <c r="T31">
-        <v>1.08727387636529</v>
+        <v>1.102806360313366</v>
       </c>
       <c r="U31">
         <v>0.1186</v>
       </c>
       <c r="V31">
-        <v>0.2014056820330505</v>
+        <v>0.1946921592986154</v>
       </c>
       <c r="W31">
-        <v>0.09471328611088023</v>
+        <v>0.09550950990718421</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -4227,7 +4227,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>0.9154803728775021</v>
+        <v>0.884964360448252</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4235,22 +4235,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.09413891375325338</v>
+        <v>0.09486691375325339</v>
       </c>
       <c r="C32">
-        <v>24025.21977006074</v>
+        <v>22889.63884638869</v>
       </c>
       <c r="D32">
-        <v>39723.37977006073</v>
+        <v>39153.65084638869</v>
       </c>
       <c r="E32">
-        <v>10180.46</v>
+        <v>10746.312</v>
       </c>
       <c r="F32">
-        <v>16975.56</v>
+        <v>17541.412</v>
       </c>
       <c r="G32">
         <v>1277.4</v>
@@ -4271,37 +4271,37 @@
         <v>1781.7</v>
       </c>
       <c r="M32">
-        <v>2013.301416</v>
+        <v>2080.4114632</v>
       </c>
       <c r="N32">
-        <v>-231.601416</v>
+        <v>-298.7114632</v>
       </c>
       <c r="O32">
-        <v>-50.95231151999999</v>
+        <v>-65.716521904</v>
       </c>
       <c r="P32">
-        <v>-180.64910448</v>
+        <v>-232.994941296</v>
       </c>
       <c r="Q32">
-        <v>655.55089552</v>
+        <v>603.2050587040001</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.09355151540156874</v>
+        <v>0.09424356634941757</v>
       </c>
       <c r="T32">
-        <v>1.102806360313366</v>
+        <v>1.118789061187473</v>
       </c>
       <c r="U32">
         <v>0.1186</v>
       </c>
       <c r="V32">
-        <v>0.1946921592986154</v>
+        <v>0.1884117670631762</v>
       </c>
       <c r="W32">
-        <v>0.09550950990718421</v>
+        <v>0.09625436442630732</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -4309,7 +4309,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.884964360448252</v>
+        <v>0.8564171230144373</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4317,22 +4317,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.09486691375325339</v>
+        <v>0.09559491375325338</v>
       </c>
       <c r="C33">
-        <v>22889.63884638869</v>
+        <v>21770.16941458171</v>
       </c>
       <c r="D33">
-        <v>39153.65084638869</v>
+        <v>38600.03341458171</v>
       </c>
       <c r="E33">
-        <v>10746.312</v>
+        <v>11312.164</v>
       </c>
       <c r="F33">
-        <v>17541.412</v>
+        <v>18107.264</v>
       </c>
       <c r="G33">
         <v>1277.4</v>
@@ -4353,37 +4353,37 @@
         <v>1781.7</v>
       </c>
       <c r="M33">
-        <v>2080.4114632</v>
+        <v>2147.5215104</v>
       </c>
       <c r="N33">
-        <v>-298.7114632</v>
+        <v>-365.8215103999999</v>
       </c>
       <c r="O33">
-        <v>-65.716521904</v>
+        <v>-80.48073228799997</v>
       </c>
       <c r="P33">
-        <v>-232.994941296</v>
+        <v>-285.3407781119999</v>
       </c>
       <c r="Q33">
-        <v>603.2050587040001</v>
+        <v>550.8592218880001</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.09424356634941757</v>
+        <v>0.09495597173690899</v>
       </c>
       <c r="T33">
-        <v>1.118789061187473</v>
+        <v>1.135241841499053</v>
       </c>
       <c r="U33">
         <v>0.1186</v>
       </c>
       <c r="V33">
-        <v>0.1884117670631762</v>
+        <v>0.182523899342452</v>
       </c>
       <c r="W33">
-        <v>0.09625436442630732</v>
+        <v>0.09695266553798521</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4391,7 +4391,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.8564171230144373</v>
+        <v>0.8296540879202362</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4399,22 +4399,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.09559491375325338</v>
+        <v>0.09632291375325337</v>
       </c>
       <c r="C34">
-        <v>21770.16941458171</v>
+        <v>20666.13757262117</v>
       </c>
       <c r="D34">
-        <v>38600.03341458171</v>
+        <v>38061.85357262117</v>
       </c>
       <c r="E34">
-        <v>11312.164</v>
+        <v>11878.016</v>
       </c>
       <c r="F34">
-        <v>18107.264</v>
+        <v>18673.116</v>
       </c>
       <c r="G34">
         <v>1277.4</v>
@@ -4435,37 +4435,37 @@
         <v>1781.7</v>
       </c>
       <c r="M34">
-        <v>2147.5215104</v>
+        <v>2214.6315576</v>
       </c>
       <c r="N34">
-        <v>-365.8215103999999</v>
+        <v>-432.9315576000001</v>
       </c>
       <c r="O34">
-        <v>-80.48073228799997</v>
+        <v>-95.24494267200004</v>
       </c>
       <c r="P34">
-        <v>-285.3407781119999</v>
+        <v>-337.6866149280001</v>
       </c>
       <c r="Q34">
-        <v>550.8592218880001</v>
+        <v>498.5133850719999</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.09495597173690899</v>
+        <v>0.09568964295686286</v>
       </c>
       <c r="T34">
-        <v>1.135241841499053</v>
+        <v>1.152185749581129</v>
       </c>
       <c r="U34">
         <v>0.1186</v>
       </c>
       <c r="V34">
-        <v>0.182523899342452</v>
+        <v>0.1769928720896504</v>
       </c>
       <c r="W34">
-        <v>0.09695266553798521</v>
+        <v>0.09760864537016749</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.8296540879202362</v>
+        <v>0.8045130549529562</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4481,22 +4481,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.09632291375325337</v>
+        <v>0.1258477034551138</v>
       </c>
       <c r="C35">
-        <v>20666.13757262117</v>
+        <v>6352.094411330028</v>
       </c>
       <c r="D35">
-        <v>38061.85357262117</v>
+        <v>24313.66241133003</v>
       </c>
       <c r="E35">
-        <v>11878.016</v>
+        <v>12443.868</v>
       </c>
       <c r="F35">
-        <v>18673.116</v>
+        <v>19238.968</v>
       </c>
       <c r="G35">
         <v>1277.4</v>
@@ -4517,45 +4517,45 @@
         <v>1781.7</v>
       </c>
       <c r="M35">
-        <v>2214.6315576</v>
+        <v>3863.1847744</v>
       </c>
       <c r="N35">
-        <v>-432.9315576000001</v>
+        <v>-2081.4847744</v>
       </c>
       <c r="O35">
-        <v>-95.24494267200004</v>
+        <v>-457.926650368</v>
       </c>
       <c r="P35">
-        <v>-337.6866149280001</v>
+        <v>-1623.558124032</v>
       </c>
       <c r="Q35">
-        <v>498.5133850719999</v>
+        <v>-787.3581240319998</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.09568964295686286</v>
+        <v>0.09773159164084619</v>
       </c>
       <c r="T35">
-        <v>1.152185749581129</v>
+        <v>1.199343917802452</v>
       </c>
       <c r="U35">
-        <v>0.1186</v>
+        <v>0.2008</v>
       </c>
       <c r="V35">
-        <v>0.1769928720896504</v>
+        <v>0.1014639534193335</v>
       </c>
       <c r="W35">
-        <v>0.09760864537016749</v>
+        <v>0.1804260381533979</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y35">
-        <v>0.8045130549529562</v>
+        <v>0.4611997882696978</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4563,22 +4563,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1258477034551138</v>
+        <v>0.1273977034551138</v>
       </c>
       <c r="C36">
-        <v>6352.094411330028</v>
+        <v>5333.769480477567</v>
       </c>
       <c r="D36">
-        <v>24313.66241133003</v>
+        <v>23861.18948047757</v>
       </c>
       <c r="E36">
-        <v>12443.868</v>
+        <v>13009.72</v>
       </c>
       <c r="F36">
-        <v>19238.968</v>
+        <v>19804.82</v>
       </c>
       <c r="G36">
         <v>1277.4</v>
@@ -4599,37 +4599,37 @@
         <v>1781.7</v>
       </c>
       <c r="M36">
-        <v>3863.1847744</v>
+        <v>3976.807856</v>
       </c>
       <c r="N36">
-        <v>-2081.4847744</v>
+        <v>-2195.107856</v>
       </c>
       <c r="O36">
-        <v>-457.926650368</v>
+        <v>-482.9237283199999</v>
       </c>
       <c r="P36">
-        <v>-1623.558124032</v>
+        <v>-1712.18412768</v>
       </c>
       <c r="Q36">
-        <v>-787.3581240319998</v>
+        <v>-875.9841276799996</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.09773159164084619</v>
+        <v>0.09853053920455151</v>
       </c>
       <c r="T36">
-        <v>1.199343917802452</v>
+        <v>1.217795362691721</v>
       </c>
       <c r="U36">
         <v>0.2008</v>
       </c>
       <c r="V36">
-        <v>0.1014639534193335</v>
+        <v>0.09856498332163827</v>
       </c>
       <c r="W36">
-        <v>0.1804260381533979</v>
+        <v>0.181008151349015</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4637,7 +4637,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.4611997882696978</v>
+        <v>0.4480226514619922</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4645,22 +4645,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1273977034551138</v>
+        <v>0.1289477034551137</v>
       </c>
       <c r="C37">
-        <v>5333.769480477567</v>
+        <v>4331.977751138023</v>
       </c>
       <c r="D37">
-        <v>23861.18948047757</v>
+        <v>23425.24975113802</v>
       </c>
       <c r="E37">
-        <v>13009.72</v>
+        <v>13575.572</v>
       </c>
       <c r="F37">
-        <v>19804.82</v>
+        <v>20370.672</v>
       </c>
       <c r="G37">
         <v>1277.4</v>
@@ -4681,37 +4681,37 @@
         <v>1781.7</v>
       </c>
       <c r="M37">
-        <v>3976.807856</v>
+        <v>4090.430937600001</v>
       </c>
       <c r="N37">
-        <v>-2195.107856</v>
+        <v>-2308.7309376</v>
       </c>
       <c r="O37">
-        <v>-482.9237283199999</v>
+        <v>-507.920806272</v>
       </c>
       <c r="P37">
-        <v>-1712.18412768</v>
+        <v>-1800.810131328</v>
       </c>
       <c r="Q37">
-        <v>-875.9841276799996</v>
+        <v>-964.6101313280003</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.09853053920455151</v>
+        <v>0.09935445387962263</v>
       </c>
       <c r="T37">
-        <v>1.217795362691721</v>
+        <v>1.236823415233779</v>
       </c>
       <c r="U37">
         <v>0.2008</v>
       </c>
       <c r="V37">
-        <v>0.09856498332163827</v>
+        <v>0.0958270671182594</v>
       </c>
       <c r="W37">
-        <v>0.181008151349015</v>
+        <v>0.1815579249226535</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4719,7 +4719,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.4480226514619922</v>
+        <v>0.4355775778102701</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4727,22 +4727,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1289477034551137</v>
+        <v>0.1304977034551137</v>
       </c>
       <c r="C38">
-        <v>4331.977751138027</v>
+        <v>3345.829305906296</v>
       </c>
       <c r="D38">
-        <v>23425.24975113802</v>
+        <v>23004.95330590629</v>
       </c>
       <c r="E38">
-        <v>13575.572</v>
+        <v>14141.424</v>
       </c>
       <c r="F38">
-        <v>20370.672</v>
+        <v>20936.524</v>
       </c>
       <c r="G38">
         <v>1277.4</v>
@@ -4763,37 +4763,37 @@
         <v>1781.7</v>
       </c>
       <c r="M38">
-        <v>4090.4309376</v>
+        <v>4204.0540192</v>
       </c>
       <c r="N38">
-        <v>-2308.730937599999</v>
+        <v>-2422.3540192</v>
       </c>
       <c r="O38">
-        <v>-507.9208062719999</v>
+        <v>-532.917884224</v>
       </c>
       <c r="P38">
-        <v>-1800.810131327999</v>
+        <v>-1889.436134976</v>
       </c>
       <c r="Q38">
-        <v>-964.6101313279994</v>
+        <v>-1053.236134976</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.09935445387962263</v>
+        <v>0.1002045245761246</v>
       </c>
       <c r="T38">
-        <v>1.236823415233779</v>
+        <v>1.256455532935902</v>
       </c>
       <c r="U38">
         <v>0.2008</v>
       </c>
       <c r="V38">
-        <v>0.09582706711825943</v>
+        <v>0.09323714638533349</v>
       </c>
       <c r="W38">
-        <v>0.1815579249226535</v>
+        <v>0.182077981005825</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4801,7 +4801,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.4355775778102702</v>
+        <v>0.423805210842425</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4809,22 +4809,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1304977034551137</v>
+        <v>0.1320477034551137</v>
       </c>
       <c r="C39">
-        <v>3345.829305906296</v>
+        <v>2374.496969344887</v>
       </c>
       <c r="D39">
-        <v>23004.95330590629</v>
+        <v>22599.47296934489</v>
       </c>
       <c r="E39">
-        <v>14141.424</v>
+        <v>14707.276</v>
       </c>
       <c r="F39">
-        <v>20936.524</v>
+        <v>21502.376</v>
       </c>
       <c r="G39">
         <v>1277.4</v>
@@ -4845,37 +4845,37 @@
         <v>1781.7</v>
       </c>
       <c r="M39">
-        <v>4204.0540192</v>
+        <v>4317.677100800001</v>
       </c>
       <c r="N39">
-        <v>-2422.3540192</v>
+        <v>-2535.977100800001</v>
       </c>
       <c r="O39">
-        <v>-532.917884224</v>
+        <v>-557.9149621760001</v>
       </c>
       <c r="P39">
-        <v>-1889.436134976</v>
+        <v>-1978.062138624</v>
       </c>
       <c r="Q39">
-        <v>-1053.236134976</v>
+        <v>-1141.862138624</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1002045245761246</v>
+        <v>0.1010820169079975</v>
       </c>
       <c r="T39">
-        <v>1.256455532935902</v>
+        <v>1.276720944757449</v>
       </c>
       <c r="U39">
         <v>0.2008</v>
       </c>
       <c r="V39">
-        <v>0.09323714638533349</v>
+        <v>0.09078353726992996</v>
       </c>
       <c r="W39">
-        <v>0.182077981005825</v>
+        <v>0.1825706657161981</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4883,7 +4883,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.423805210842425</v>
+        <v>0.4126524421360452</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4891,22 +4891,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1320477034551137</v>
+        <v>0.1335977034551137</v>
       </c>
       <c r="C40">
-        <v>2374.496969344887</v>
+        <v>1417.210874373788</v>
       </c>
       <c r="D40">
-        <v>22599.47296934489</v>
+        <v>22208.03887437379</v>
       </c>
       <c r="E40">
-        <v>14707.276</v>
+        <v>15273.128</v>
       </c>
       <c r="F40">
-        <v>21502.376</v>
+        <v>22068.228</v>
       </c>
       <c r="G40">
         <v>1277.4</v>
@@ -4927,37 +4927,37 @@
         <v>1781.7</v>
       </c>
       <c r="M40">
-        <v>4317.677100800001</v>
+        <v>4431.3001824</v>
       </c>
       <c r="N40">
-        <v>-2535.977100800001</v>
+        <v>-2649.6001824</v>
       </c>
       <c r="O40">
-        <v>-557.9149621760001</v>
+        <v>-582.9120401280001</v>
       </c>
       <c r="P40">
-        <v>-1978.062138624</v>
+        <v>-2066.688142272</v>
       </c>
       <c r="Q40">
-        <v>-1141.862138624</v>
+        <v>-1230.488142272</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1010820169079975</v>
+        <v>0.1019882794802598</v>
       </c>
       <c r="T40">
-        <v>1.276720944757449</v>
+        <v>1.29765079631085</v>
       </c>
       <c r="U40">
         <v>0.2008</v>
       </c>
       <c r="V40">
-        <v>0.09078353726992996</v>
+        <v>0.0884557542630087</v>
       </c>
       <c r="W40">
-        <v>0.1825706657161981</v>
+        <v>0.1830380845439879</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4965,7 +4965,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.4126524421360452</v>
+        <v>0.402071610286403</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4973,22 +4973,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1335977034551137</v>
+        <v>0.1351477034551137</v>
       </c>
       <c r="C41">
-        <v>1417.210874373788</v>
+        <v>473.2535837232135</v>
       </c>
       <c r="D41">
-        <v>22208.03887437379</v>
+        <v>21829.93358372321</v>
       </c>
       <c r="E41">
-        <v>15273.128</v>
+        <v>15838.98</v>
       </c>
       <c r="F41">
-        <v>22068.228</v>
+        <v>22634.08</v>
       </c>
       <c r="G41">
         <v>1277.4</v>
@@ -5009,37 +5009,37 @@
         <v>1781.7</v>
       </c>
       <c r="M41">
-        <v>4431.3001824</v>
+        <v>4544.923264000001</v>
       </c>
       <c r="N41">
-        <v>-2649.6001824</v>
+        <v>-2763.223264000001</v>
       </c>
       <c r="O41">
-        <v>-582.9120401280001</v>
+        <v>-607.9091180800002</v>
       </c>
       <c r="P41">
-        <v>-2066.688142272</v>
+        <v>-2155.314145920001</v>
       </c>
       <c r="Q41">
-        <v>-1230.488142272</v>
+        <v>-1319.114145920001</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1019882794802598</v>
+        <v>0.1029247508049308</v>
       </c>
       <c r="T41">
-        <v>1.29765079631085</v>
+        <v>1.319278309582697</v>
       </c>
       <c r="U41">
         <v>0.2008</v>
       </c>
       <c r="V41">
-        <v>0.0884557542630087</v>
+        <v>0.08624436040643346</v>
       </c>
       <c r="W41">
-        <v>0.1830380845439879</v>
+        <v>0.1834821324303882</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -5047,7 +5047,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.402071610286403</v>
+        <v>0.392019820029243</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -5055,22 +5055,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1351477034551137</v>
+        <v>0.1366977034551138</v>
       </c>
       <c r="C42">
-        <v>473.2535837232135</v>
+        <v>-458.0442985951158</v>
       </c>
       <c r="D42">
-        <v>21829.93358372321</v>
+        <v>21464.48770140488</v>
       </c>
       <c r="E42">
-        <v>15838.98</v>
+        <v>16404.832</v>
       </c>
       <c r="F42">
-        <v>22634.08</v>
+        <v>23199.932</v>
       </c>
       <c r="G42">
         <v>1277.4</v>
@@ -5091,37 +5091,37 @@
         <v>1781.7</v>
       </c>
       <c r="M42">
-        <v>4544.923264000001</v>
+        <v>4658.546345600001</v>
       </c>
       <c r="N42">
-        <v>-2763.223264000001</v>
+        <v>-2876.846345600001</v>
       </c>
       <c r="O42">
-        <v>-607.9091180800002</v>
+        <v>-632.9061960320001</v>
       </c>
       <c r="P42">
-        <v>-2155.314145920001</v>
+        <v>-2243.940149568001</v>
       </c>
       <c r="Q42">
-        <v>-1319.114145920001</v>
+        <v>-1407.740149568001</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1029247508049308</v>
+        <v>0.1038929669202686</v>
       </c>
       <c r="T42">
-        <v>1.319278309582697</v>
+        <v>1.341638958897658</v>
       </c>
       <c r="U42">
         <v>0.2008</v>
       </c>
       <c r="V42">
-        <v>0.08624436040643346</v>
+        <v>0.0841408394209107</v>
       </c>
       <c r="W42">
-        <v>0.1834821324303882</v>
+        <v>0.1839045194442812</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -5129,7 +5129,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.392019820029243</v>
+        <v>0.3824583610041394</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -5137,22 +5137,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1366977034551138</v>
+        <v>0.1382477034551138</v>
       </c>
       <c r="C43">
-        <v>-458.0442985951158</v>
+        <v>-1377.308082275238</v>
       </c>
       <c r="D43">
-        <v>21464.48770140488</v>
+        <v>21111.07591772476</v>
       </c>
       <c r="E43">
-        <v>16404.832</v>
+        <v>16970.684</v>
       </c>
       <c r="F43">
-        <v>23199.932</v>
+        <v>23765.784</v>
       </c>
       <c r="G43">
         <v>1277.4</v>
@@ -5173,37 +5173,37 @@
         <v>1781.7</v>
       </c>
       <c r="M43">
-        <v>4658.546345600001</v>
+        <v>4772.1694272</v>
       </c>
       <c r="N43">
-        <v>-2876.846345600001</v>
+        <v>-2990.469427200001</v>
       </c>
       <c r="O43">
-        <v>-632.9061960320001</v>
+        <v>-657.9032739840002</v>
       </c>
       <c r="P43">
-        <v>-2243.940149568001</v>
+        <v>-2332.566153216</v>
       </c>
       <c r="Q43">
-        <v>-1407.740149568001</v>
+        <v>-1496.366153216</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1038929669202686</v>
+        <v>0.1048945697982043</v>
       </c>
       <c r="T43">
-        <v>1.341638958897658</v>
+        <v>1.364770665085549</v>
       </c>
       <c r="U43">
         <v>0.2008</v>
       </c>
       <c r="V43">
-        <v>0.0841408394209107</v>
+        <v>0.0821374861013652</v>
       </c>
       <c r="W43">
-        <v>0.1839045194442812</v>
+        <v>0.1843067927908459</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -5211,7 +5211,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.3824583610041394</v>
+        <v>0.37335220955166</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -5219,22 +5219,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1382477034551138</v>
+        <v>0.1397977034551137</v>
       </c>
       <c r="C44">
-        <v>-1377.308082275238</v>
+        <v>-2285.122561320932</v>
       </c>
       <c r="D44">
-        <v>21111.07591772476</v>
+        <v>20769.11343867907</v>
       </c>
       <c r="E44">
-        <v>16970.684</v>
+        <v>17536.536</v>
       </c>
       <c r="F44">
-        <v>23765.784</v>
+        <v>24331.636</v>
       </c>
       <c r="G44">
         <v>1277.4</v>
@@ -5255,37 +5255,37 @@
         <v>1781.7</v>
       </c>
       <c r="M44">
-        <v>4772.1694272</v>
+        <v>4885.7925088</v>
       </c>
       <c r="N44">
-        <v>-2990.469427200001</v>
+        <v>-3104.0925088</v>
       </c>
       <c r="O44">
-        <v>-657.9032739840002</v>
+        <v>-682.9003519360001</v>
       </c>
       <c r="P44">
-        <v>-2332.566153216</v>
+        <v>-2421.192156864</v>
       </c>
       <c r="Q44">
-        <v>-1496.366153216</v>
+        <v>-1584.992156864</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1048945697982043</v>
+        <v>0.1059313166367693</v>
       </c>
       <c r="T44">
-        <v>1.364770665085549</v>
+        <v>1.38871401008705</v>
       </c>
       <c r="U44">
         <v>0.2008</v>
       </c>
       <c r="V44">
-        <v>0.0821374861013652</v>
+        <v>0.08022731200598462</v>
       </c>
       <c r="W44">
-        <v>0.1843067927908459</v>
+        <v>0.1846903557491983</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -5293,7 +5293,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.37335220955166</v>
+        <v>0.3646696000272028</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5301,22 +5301,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1397977034551137</v>
+        <v>0.1413477034551138</v>
       </c>
       <c r="C45">
-        <v>-2285.122561320932</v>
+        <v>-3182.035243156162</v>
       </c>
       <c r="D45">
-        <v>20769.11343867907</v>
+        <v>20438.05275684383</v>
       </c>
       <c r="E45">
-        <v>17536.536</v>
+        <v>18102.388</v>
       </c>
       <c r="F45">
-        <v>24331.636</v>
+        <v>24897.488</v>
       </c>
       <c r="G45">
         <v>1277.4</v>
@@ -5337,37 +5337,37 @@
         <v>1781.7</v>
       </c>
       <c r="M45">
-        <v>4885.7925088</v>
+        <v>4999.4155904</v>
       </c>
       <c r="N45">
-        <v>-3104.0925088</v>
+        <v>-3217.7155904</v>
       </c>
       <c r="O45">
-        <v>-682.9003519360001</v>
+        <v>-707.897429888</v>
       </c>
       <c r="P45">
-        <v>-2421.192156864</v>
+        <v>-2509.818160512</v>
       </c>
       <c r="Q45">
-        <v>-1584.992156864</v>
+        <v>-1673.618160512</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1059313166367693</v>
+        <v>0.1070050901481401</v>
       </c>
       <c r="T45">
-        <v>1.38871401008705</v>
+        <v>1.41351247455289</v>
       </c>
       <c r="U45">
         <v>0.2008</v>
       </c>
       <c r="V45">
-        <v>0.08022731200598462</v>
+        <v>0.07840396400584862</v>
       </c>
       <c r="W45">
-        <v>0.1846903557491983</v>
+        <v>0.1850564840276256</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5375,7 +5375,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.3646696000272028</v>
+        <v>0.3563816545720391</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5383,22 +5383,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1413477034551138</v>
+        <v>0.1428977034551137</v>
       </c>
       <c r="C46">
-        <v>-3182.035243156162</v>
+        <v>-4068.559273747916</v>
       </c>
       <c r="D46">
-        <v>20438.05275684383</v>
+        <v>20117.38072625208</v>
       </c>
       <c r="E46">
-        <v>18102.388</v>
+        <v>18668.24</v>
       </c>
       <c r="F46">
-        <v>24897.488</v>
+        <v>25463.34</v>
       </c>
       <c r="G46">
         <v>1277.4</v>
@@ -5419,37 +5419,37 @@
         <v>1781.7</v>
       </c>
       <c r="M46">
-        <v>4999.4155904</v>
+        <v>5113.038672000001</v>
       </c>
       <c r="N46">
-        <v>-3217.7155904</v>
+        <v>-3331.338672000001</v>
       </c>
       <c r="O46">
-        <v>-707.897429888</v>
+        <v>-732.8945078400002</v>
       </c>
       <c r="P46">
-        <v>-2509.818160512</v>
+        <v>-2598.444164160001</v>
       </c>
       <c r="Q46">
-        <v>-1673.618160512</v>
+        <v>-1762.244164160001</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1070050901481401</v>
+        <v>0.1081179099690154</v>
       </c>
       <c r="T46">
-        <v>1.41351247455289</v>
+        <v>1.439212701362943</v>
       </c>
       <c r="U46">
         <v>0.2008</v>
       </c>
       <c r="V46">
-        <v>0.07840396400584862</v>
+        <v>0.07666165369460752</v>
       </c>
       <c r="W46">
-        <v>0.1850564840276256</v>
+        <v>0.1854063399381228</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5457,7 +5457,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.3563816545720391</v>
+        <v>0.348462062248216</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5465,22 +5465,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1428977034551137</v>
+        <v>0.1444477034551138</v>
       </c>
       <c r="C47">
-        <v>-4068.559273747916</v>
+        <v>-4945.176091612801</v>
       </c>
       <c r="D47">
-        <v>20117.38072625208</v>
+        <v>19806.6159083872</v>
       </c>
       <c r="E47">
-        <v>18668.24</v>
+        <v>19234.092</v>
       </c>
       <c r="F47">
-        <v>25463.34</v>
+        <v>26029.192</v>
       </c>
       <c r="G47">
         <v>1277.4</v>
@@ -5501,37 +5501,37 @@
         <v>1781.7</v>
       </c>
       <c r="M47">
-        <v>5113.038672000001</v>
+        <v>5226.6617536</v>
       </c>
       <c r="N47">
-        <v>-3331.338672000001</v>
+        <v>-3444.961753600001</v>
       </c>
       <c r="O47">
-        <v>-732.8945078400002</v>
+        <v>-757.8915857920001</v>
       </c>
       <c r="P47">
-        <v>-2598.444164160001</v>
+        <v>-2687.070167808</v>
       </c>
       <c r="Q47">
-        <v>-1762.244164160001</v>
+        <v>-1850.870167808</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1081179099690154</v>
+        <v>0.109271945338812</v>
       </c>
       <c r="T47">
-        <v>1.439212701362943</v>
+        <v>1.46586478842522</v>
       </c>
       <c r="U47">
         <v>0.2008</v>
       </c>
       <c r="V47">
-        <v>0.07666165369460752</v>
+        <v>0.07499509600559433</v>
       </c>
       <c r="W47">
-        <v>0.1854063399381228</v>
+        <v>0.1857409847220767</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5539,7 +5539,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.348462062248216</v>
+        <v>0.3408868000254287</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5547,22 +5547,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1444477034551138</v>
+        <v>0.1459977034551138</v>
       </c>
       <c r="C48">
-        <v>-4945.176091612801</v>
+        <v>-5812.337839577784</v>
       </c>
       <c r="D48">
-        <v>19806.6159083872</v>
+        <v>19505.30616042222</v>
       </c>
       <c r="E48">
-        <v>19234.092</v>
+        <v>19799.944</v>
       </c>
       <c r="F48">
-        <v>26029.192</v>
+        <v>26595.044</v>
       </c>
       <c r="G48">
         <v>1277.4</v>
@@ -5583,37 +5583,37 @@
         <v>1781.7</v>
       </c>
       <c r="M48">
-        <v>5226.6617536</v>
+        <v>5340.2848352</v>
       </c>
       <c r="N48">
-        <v>-3444.961753600001</v>
+        <v>-3558.5848352</v>
       </c>
       <c r="O48">
-        <v>-757.8915857920001</v>
+        <v>-782.888663744</v>
       </c>
       <c r="P48">
-        <v>-2687.070167808</v>
+        <v>-2775.696171456</v>
       </c>
       <c r="Q48">
-        <v>-1850.870167808</v>
+        <v>-1939.496171456</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.109271945338812</v>
+        <v>0.1104695292131292</v>
       </c>
       <c r="T48">
-        <v>1.46586478842522</v>
+        <v>1.493522614621922</v>
       </c>
       <c r="U48">
         <v>0.2008</v>
       </c>
       <c r="V48">
-        <v>0.07499509600559433</v>
+        <v>0.07339945566504977</v>
       </c>
       <c r="W48">
-        <v>0.1857409847220767</v>
+        <v>0.186061389302458</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5621,7 +5621,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.3408868000254287</v>
+        <v>0.3336338893865898</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5629,22 +5629,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1459977034551138</v>
+        <v>0.1475477034551138</v>
       </c>
       <c r="C49">
-        <v>-5812.337839577784</v>
+        <v>-6670.46955970495</v>
       </c>
       <c r="D49">
-        <v>19505.30616042222</v>
+        <v>19213.02644029505</v>
       </c>
       <c r="E49">
-        <v>19799.944</v>
+        <v>20365.796</v>
       </c>
       <c r="F49">
-        <v>26595.044</v>
+        <v>27160.896</v>
       </c>
       <c r="G49">
         <v>1277.4</v>
@@ -5665,37 +5665,37 @@
         <v>1781.7</v>
       </c>
       <c r="M49">
-        <v>5340.2848352</v>
+        <v>5453.907916800001</v>
       </c>
       <c r="N49">
-        <v>-3558.5848352</v>
+        <v>-3672.207916800001</v>
       </c>
       <c r="O49">
-        <v>-782.888663744</v>
+        <v>-807.8857416960002</v>
       </c>
       <c r="P49">
-        <v>-2775.696171456</v>
+        <v>-2864.322175104001</v>
       </c>
       <c r="Q49">
-        <v>-1939.496171456</v>
+        <v>-2028.122175104001</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1104695292131292</v>
+        <v>0.1117131740056894</v>
       </c>
       <c r="T49">
-        <v>1.493522614621922</v>
+        <v>1.522244203364651</v>
       </c>
       <c r="U49">
         <v>0.2008</v>
       </c>
       <c r="V49">
-        <v>0.07339945566504977</v>
+        <v>0.07187030033869456</v>
       </c>
       <c r="W49">
-        <v>0.186061389302458</v>
+        <v>0.1863684436919901</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5703,7 +5703,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.3336338893865898</v>
+        <v>0.3266831833577025</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5711,22 +5711,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1475477034551138</v>
+        <v>0.1490977034551138</v>
       </c>
       <c r="C50">
-        <v>-6670.469559704947</v>
+        <v>-7519.971193788995</v>
       </c>
       <c r="D50">
-        <v>19213.02644029505</v>
+        <v>18929.376806211</v>
       </c>
       <c r="E50">
-        <v>20365.79599999999</v>
+        <v>20931.648</v>
       </c>
       <c r="F50">
-        <v>27160.896</v>
+        <v>27726.748</v>
       </c>
       <c r="G50">
         <v>1277.4</v>
@@ -5747,37 +5747,37 @@
         <v>1781.7</v>
       </c>
       <c r="M50">
-        <v>5453.9079168</v>
+        <v>5567.5309984</v>
       </c>
       <c r="N50">
-        <v>-3672.2079168</v>
+        <v>-3785.830998400001</v>
       </c>
       <c r="O50">
-        <v>-807.885741696</v>
+        <v>-832.8828196480001</v>
       </c>
       <c r="P50">
-        <v>-2864.322175104</v>
+        <v>-2952.948178752001</v>
       </c>
       <c r="Q50">
-        <v>-2028.122175104</v>
+        <v>-2116.748178752001</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1117131740056894</v>
+        <v>0.1130055891822715</v>
       </c>
       <c r="T50">
-        <v>1.522244203364651</v>
+        <v>1.55209212892082</v>
       </c>
       <c r="U50">
         <v>0.2008</v>
       </c>
       <c r="V50">
-        <v>0.07187030033869457</v>
+        <v>0.07040355951545589</v>
       </c>
       <c r="W50">
-        <v>0.1863684436919901</v>
+        <v>0.1866629652492965</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5785,7 +5785,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.3266831833577025</v>
+        <v>0.3200161796157086</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5793,22 +5793,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1490977034551138</v>
+        <v>0.1506477034551137</v>
       </c>
       <c r="C51">
-        <v>-7519.971193788995</v>
+        <v>-8361.219409227822</v>
       </c>
       <c r="D51">
-        <v>18929.376806211</v>
+        <v>18653.98059077217</v>
       </c>
       <c r="E51">
-        <v>20931.648</v>
+        <v>21497.5</v>
       </c>
       <c r="F51">
-        <v>27726.748</v>
+        <v>28292.6</v>
       </c>
       <c r="G51">
         <v>1277.4</v>
@@ -5829,37 +5829,37 @@
         <v>1781.7</v>
       </c>
       <c r="M51">
-        <v>5567.5309984</v>
+        <v>5681.15408</v>
       </c>
       <c r="N51">
-        <v>-3785.830998400001</v>
+        <v>-3899.45408</v>
       </c>
       <c r="O51">
-        <v>-832.8828196480001</v>
+        <v>-857.8798976</v>
       </c>
       <c r="P51">
-        <v>-2952.948178752001</v>
+        <v>-3041.574182400001</v>
       </c>
       <c r="Q51">
-        <v>-2116.748178752001</v>
+        <v>-2205.374182400001</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1130055891822715</v>
+        <v>0.114349700965917</v>
       </c>
       <c r="T51">
-        <v>1.55209212892082</v>
+        <v>1.583133971499237</v>
       </c>
       <c r="U51">
         <v>0.2008</v>
       </c>
       <c r="V51">
-        <v>0.07040355951545589</v>
+        <v>0.06899548832514679</v>
       </c>
       <c r="W51">
-        <v>0.1866629652492965</v>
+        <v>0.1869457059443105</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5867,7 +5867,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.3200161796157086</v>
+        <v>0.3136158560233944</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5875,22 +5875,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1506477034551137</v>
+        <v>0.1521977034551137</v>
       </c>
       <c r="C52">
-        <v>-8361.219409227822</v>
+        <v>-9194.56926779541</v>
       </c>
       <c r="D52">
-        <v>18653.98059077217</v>
+        <v>18386.48273220459</v>
       </c>
       <c r="E52">
-        <v>21497.5</v>
+        <v>22063.352</v>
       </c>
       <c r="F52">
-        <v>28292.6</v>
+        <v>28858.452</v>
       </c>
       <c r="G52">
         <v>1277.4</v>
@@ -5911,37 +5911,37 @@
         <v>1781.7</v>
       </c>
       <c r="M52">
-        <v>5681.15408</v>
+        <v>5794.7771616</v>
       </c>
       <c r="N52">
-        <v>-3899.45408</v>
+        <v>-4013.0771616</v>
       </c>
       <c r="O52">
-        <v>-857.8798976</v>
+        <v>-882.8769755520001</v>
       </c>
       <c r="P52">
-        <v>-3041.574182400001</v>
+        <v>-3130.200186048</v>
       </c>
       <c r="Q52">
-        <v>-2205.374182400001</v>
+        <v>-2294.000186048</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.114349700965917</v>
+        <v>0.1157486744550173</v>
       </c>
       <c r="T52">
-        <v>1.583133971499237</v>
+        <v>1.615442828060446</v>
       </c>
       <c r="U52">
         <v>0.2008</v>
       </c>
       <c r="V52">
-        <v>0.06899548832514679</v>
+        <v>0.067642635612889</v>
       </c>
       <c r="W52">
-        <v>0.1869457059443105</v>
+        <v>0.1872173587689319</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5949,7 +5949,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.3136158560233944</v>
+        <v>0.3074665255131318</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5957,22 +5957,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1521977034551137</v>
+        <v>0.1537477034551138</v>
       </c>
       <c r="C53">
-        <v>-9194.56926779541</v>
+        <v>-10020.35575286344</v>
       </c>
       <c r="D53">
-        <v>18386.48273220459</v>
+        <v>18126.54824713656</v>
       </c>
       <c r="E53">
-        <v>22063.352</v>
+        <v>22629.204</v>
       </c>
       <c r="F53">
-        <v>28858.452</v>
+        <v>29424.304</v>
       </c>
       <c r="G53">
         <v>1277.4</v>
@@ -5993,37 +5993,37 @@
         <v>1781.7</v>
       </c>
       <c r="M53">
-        <v>5794.7771616</v>
+        <v>5908.4002432</v>
       </c>
       <c r="N53">
-        <v>-4013.0771616</v>
+        <v>-4126.7002432</v>
       </c>
       <c r="O53">
-        <v>-882.8769755520001</v>
+        <v>-907.874053504</v>
       </c>
       <c r="P53">
-        <v>-3130.200186048</v>
+        <v>-3218.826189696</v>
       </c>
       <c r="Q53">
-        <v>-2294.000186048</v>
+        <v>-2382.626189696</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1157486744550173</v>
+        <v>0.1172059385061635</v>
       </c>
       <c r="T53">
-        <v>1.615442828060446</v>
+        <v>1.649097886978372</v>
       </c>
       <c r="U53">
         <v>0.2008</v>
       </c>
       <c r="V53">
-        <v>0.067642635612889</v>
+        <v>0.06634181569725653</v>
       </c>
       <c r="W53">
-        <v>0.1872173587689319</v>
+        <v>0.1874785634079909</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -6031,7 +6031,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.3074665255131318</v>
+        <v>0.3015537077148024</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -6039,22 +6039,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1537477034551138</v>
+        <v>0.1552977034551137</v>
       </c>
       <c r="C54">
-        <v>-10020.35575286344</v>
+        <v>-10838.89516888433</v>
       </c>
       <c r="D54">
-        <v>18126.54824713656</v>
+        <v>17873.86083111567</v>
       </c>
       <c r="E54">
-        <v>22629.204</v>
+        <v>23195.056</v>
       </c>
       <c r="F54">
-        <v>29424.304</v>
+        <v>29990.156</v>
       </c>
       <c r="G54">
         <v>1277.4</v>
@@ -6075,37 +6075,37 @@
         <v>1781.7</v>
       </c>
       <c r="M54">
-        <v>5908.4002432</v>
+        <v>6022.0233248</v>
       </c>
       <c r="N54">
-        <v>-4126.7002432</v>
+        <v>-4240.323324800001</v>
       </c>
       <c r="O54">
-        <v>-907.874053504</v>
+        <v>-932.8711314560002</v>
       </c>
       <c r="P54">
-        <v>-3218.826189696</v>
+        <v>-3307.452193344001</v>
       </c>
       <c r="Q54">
-        <v>-2382.626189696</v>
+        <v>-2471.252193344</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1172059385061635</v>
+        <v>0.1187252137935287</v>
       </c>
       <c r="T54">
-        <v>1.649097886978372</v>
+        <v>1.684185076063018</v>
       </c>
       <c r="U54">
         <v>0.2008</v>
       </c>
       <c r="V54">
-        <v>0.06634181569725653</v>
+        <v>0.06509008332561017</v>
       </c>
       <c r="W54">
-        <v>0.1874785634079909</v>
+        <v>0.1877299112682175</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -6113,7 +6113,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.3015537077148024</v>
+        <v>0.2958640151164098</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -6121,22 +6121,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1552977034551137</v>
+        <v>0.1568477034551137</v>
       </c>
       <c r="C55">
-        <v>-10838.89516888433</v>
+        <v>-11650.48642542943</v>
       </c>
       <c r="D55">
-        <v>17873.86083111567</v>
+        <v>17628.12157457057</v>
       </c>
       <c r="E55">
-        <v>23195.056</v>
+        <v>23760.908</v>
       </c>
       <c r="F55">
-        <v>29990.156</v>
+        <v>30556.008</v>
       </c>
       <c r="G55">
         <v>1277.4</v>
@@ -6157,37 +6157,37 @@
         <v>1781.7</v>
       </c>
       <c r="M55">
-        <v>6022.0233248</v>
+        <v>6135.6464064</v>
       </c>
       <c r="N55">
-        <v>-4240.323324800001</v>
+        <v>-4353.9464064</v>
       </c>
       <c r="O55">
-        <v>-932.8711314560002</v>
+        <v>-957.8682094080001</v>
       </c>
       <c r="P55">
-        <v>-3307.452193344001</v>
+        <v>-3396.078196992</v>
       </c>
       <c r="Q55">
-        <v>-2471.252193344</v>
+        <v>-2559.878196992</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1187252137935287</v>
+        <v>0.1203105445281706</v>
       </c>
       <c r="T55">
-        <v>1.684185076063018</v>
+        <v>1.720797795107866</v>
       </c>
       <c r="U55">
         <v>0.2008</v>
       </c>
       <c r="V55">
-        <v>0.06509008332561017</v>
+        <v>0.06388471141217295</v>
       </c>
       <c r="W55">
-        <v>0.1877299112682175</v>
+        <v>0.1879719499484357</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -6195,7 +6195,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.2958640151164098</v>
+        <v>0.2903850518735134</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -6203,22 +6203,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1568477034551137</v>
+        <v>0.1583977034551138</v>
       </c>
       <c r="C56">
-        <v>-11650.48642542943</v>
+        <v>-12455.41221674184</v>
       </c>
       <c r="D56">
-        <v>17628.12157457057</v>
+        <v>17389.04778325816</v>
       </c>
       <c r="E56">
-        <v>23760.908</v>
+        <v>24326.76</v>
       </c>
       <c r="F56">
-        <v>30556.008</v>
+        <v>31121.86</v>
       </c>
       <c r="G56">
         <v>1277.4</v>
@@ -6239,37 +6239,37 @@
         <v>1781.7</v>
       </c>
       <c r="M56">
-        <v>6135.6464064</v>
+        <v>6249.269488</v>
       </c>
       <c r="N56">
-        <v>-4353.9464064</v>
+        <v>-4467.569488</v>
       </c>
       <c r="O56">
-        <v>-957.8682094080001</v>
+        <v>-982.86528736</v>
       </c>
       <c r="P56">
-        <v>-3396.078196992</v>
+        <v>-3484.70420064</v>
       </c>
       <c r="Q56">
-        <v>-2559.878196992</v>
+        <v>-2648.50420064</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1203105445281706</v>
+        <v>0.1219663344065744</v>
       </c>
       <c r="T56">
-        <v>1.720797795107866</v>
+        <v>1.759037746110264</v>
       </c>
       <c r="U56">
         <v>0.2008</v>
       </c>
       <c r="V56">
-        <v>0.06388471141217295</v>
+        <v>0.06272317120467889</v>
       </c>
       <c r="W56">
-        <v>0.1879719499484357</v>
+        <v>0.1882051872221005</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -6277,7 +6277,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.2903850518735134</v>
+        <v>0.2851053236576313</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6285,22 +6285,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1583977034551138</v>
+        <v>0.1599477034551137</v>
       </c>
       <c r="C57">
-        <v>-12455.41221674184</v>
+        <v>-13253.94010659048</v>
       </c>
       <c r="D57">
-        <v>17389.04778325816</v>
+        <v>17156.37189340952</v>
       </c>
       <c r="E57">
-        <v>24326.76</v>
+        <v>24892.612</v>
       </c>
       <c r="F57">
-        <v>31121.86</v>
+        <v>31687.712</v>
       </c>
       <c r="G57">
         <v>1277.4</v>
@@ -6321,37 +6321,37 @@
         <v>1781.7</v>
       </c>
       <c r="M57">
-        <v>6249.269488</v>
+        <v>6362.892569600001</v>
       </c>
       <c r="N57">
-        <v>-4467.569488</v>
+        <v>-4581.192569600001</v>
       </c>
       <c r="O57">
-        <v>-982.86528736</v>
+        <v>-1007.862365312</v>
       </c>
       <c r="P57">
-        <v>-3484.70420064</v>
+        <v>-3573.330204288</v>
       </c>
       <c r="Q57">
-        <v>-2648.50420064</v>
+        <v>-2737.130204288001</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1219663344065744</v>
+        <v>0.1236973874612693</v>
       </c>
       <c r="T57">
-        <v>1.759037746110264</v>
+        <v>1.799015876703678</v>
       </c>
       <c r="U57">
         <v>0.2008</v>
       </c>
       <c r="V57">
-        <v>0.06272317120467889</v>
+        <v>0.06160311457602392</v>
       </c>
       <c r="W57">
-        <v>0.1882051872221005</v>
+        <v>0.1884300945931344</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6359,7 +6359,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.2851053236576313</v>
+        <v>0.280014157163745</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6367,22 +6367,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1599477034551137</v>
+        <v>0.1614977034551138</v>
       </c>
       <c r="C58">
-        <v>-13253.94010659048</v>
+        <v>-14046.3235271782</v>
       </c>
       <c r="D58">
-        <v>17156.37189340952</v>
+        <v>16929.8404728218</v>
       </c>
       <c r="E58">
-        <v>24892.612</v>
+        <v>25458.464</v>
       </c>
       <c r="F58">
-        <v>31687.712</v>
+        <v>32253.564</v>
       </c>
       <c r="G58">
         <v>1277.4</v>
@@ -6403,37 +6403,37 @@
         <v>1781.7</v>
       </c>
       <c r="M58">
-        <v>6362.892569600001</v>
+        <v>6476.5156512</v>
       </c>
       <c r="N58">
-        <v>-4581.192569600001</v>
+        <v>-4694.815651200001</v>
       </c>
       <c r="O58">
-        <v>-1007.862365312</v>
+        <v>-1032.859443264</v>
       </c>
       <c r="P58">
-        <v>-3573.330204288</v>
+        <v>-3661.956207936</v>
       </c>
       <c r="Q58">
-        <v>-2737.130204288001</v>
+        <v>-2825.756207936</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1236973874612693</v>
+        <v>0.1255089546115314</v>
       </c>
       <c r="T58">
-        <v>1.799015876703678</v>
+        <v>1.840853455231671</v>
       </c>
       <c r="U58">
         <v>0.2008</v>
       </c>
       <c r="V58">
-        <v>0.06160311457602392</v>
+        <v>0.06052235817995331</v>
       </c>
       <c r="W58">
-        <v>0.1884300945931344</v>
+        <v>0.1886471104774654</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6441,7 +6441,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.280014157163745</v>
+        <v>0.2751016280906968</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6449,22 +6449,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1614977034551138</v>
+        <v>0.1630477034551138</v>
       </c>
       <c r="C59">
-        <v>-14046.3235271782</v>
+        <v>-14832.80269994419</v>
       </c>
       <c r="D59">
-        <v>16929.8404728218</v>
+        <v>16709.21330005581</v>
       </c>
       <c r="E59">
-        <v>25458.464</v>
+        <v>26024.31600000001</v>
       </c>
       <c r="F59">
-        <v>32253.564</v>
+        <v>32819.416</v>
       </c>
       <c r="G59">
         <v>1277.4</v>
@@ -6485,37 +6485,37 @@
         <v>1781.7</v>
       </c>
       <c r="M59">
-        <v>6476.5156512</v>
+        <v>6590.138732800001</v>
       </c>
       <c r="N59">
-        <v>-4694.815651200001</v>
+        <v>-4808.438732800001</v>
       </c>
       <c r="O59">
-        <v>-1032.859443264</v>
+        <v>-1057.856521216</v>
       </c>
       <c r="P59">
-        <v>-3661.956207936</v>
+        <v>-3750.582211584001</v>
       </c>
       <c r="Q59">
-        <v>-2825.756207936</v>
+        <v>-2914.382211584001</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1255089546115314</v>
+        <v>0.1274067868641869</v>
       </c>
       <c r="T59">
-        <v>1.840853455231671</v>
+        <v>1.884683299403854</v>
       </c>
       <c r="U59">
         <v>0.2008</v>
       </c>
       <c r="V59">
-        <v>0.06052235817995331</v>
+        <v>0.05947886924581619</v>
       </c>
       <c r="W59">
-        <v>0.1886471104774654</v>
+        <v>0.1888566430554401</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6523,7 +6523,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.2751016280906968</v>
+        <v>0.2703584965718917</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6531,22 +6531,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1630477034551137</v>
+        <v>0.1645977034551137</v>
       </c>
       <c r="C60">
-        <v>-14832.80269994419</v>
+        <v>-15613.60548529397</v>
       </c>
       <c r="D60">
-        <v>16709.21330005581</v>
+        <v>16494.26251470602</v>
       </c>
       <c r="E60">
-        <v>26024.316</v>
+        <v>26590.168</v>
       </c>
       <c r="F60">
-        <v>32819.416</v>
+        <v>33385.268</v>
       </c>
       <c r="G60">
         <v>1277.4</v>
@@ -6567,37 +6567,37 @@
         <v>1781.7</v>
       </c>
       <c r="M60">
-        <v>6590.1387328</v>
+        <v>6703.7618144</v>
       </c>
       <c r="N60">
-        <v>-4808.4387328</v>
+        <v>-4922.0618144</v>
       </c>
       <c r="O60">
-        <v>-1057.856521216</v>
+        <v>-1082.853599168</v>
       </c>
       <c r="P60">
-        <v>-3750.582211584</v>
+        <v>-3839.208215232</v>
       </c>
       <c r="Q60">
-        <v>-2914.382211584</v>
+        <v>-3003.008215232</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1274067868641869</v>
+        <v>0.1293971962998987</v>
       </c>
       <c r="T60">
-        <v>1.884683299403853</v>
+        <v>1.930651184755167</v>
       </c>
       <c r="U60">
         <v>0.2008</v>
       </c>
       <c r="V60">
-        <v>0.05947886924581619</v>
+        <v>0.058470752817921</v>
       </c>
       <c r="W60">
-        <v>0.1888566430554401</v>
+        <v>0.1890590728341615</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6605,7 +6605,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.2703584965718917</v>
+        <v>0.2657761491723681</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6613,22 +6613,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1645977034551137</v>
+        <v>0.1661477034551138</v>
       </c>
       <c r="C61">
-        <v>-15613.60548529397</v>
+        <v>-16388.94816757583</v>
       </c>
       <c r="D61">
-        <v>16494.26251470602</v>
+        <v>16284.77183242417</v>
       </c>
       <c r="E61">
-        <v>26590.168</v>
+        <v>27156.02</v>
       </c>
       <c r="F61">
-        <v>33385.268</v>
+        <v>33951.12</v>
       </c>
       <c r="G61">
         <v>1277.4</v>
@@ -6649,37 +6649,37 @@
         <v>1781.7</v>
       </c>
       <c r="M61">
-        <v>6703.7618144</v>
+        <v>6817.384896</v>
       </c>
       <c r="N61">
-        <v>-4922.0618144</v>
+        <v>-5035.684896</v>
       </c>
       <c r="O61">
-        <v>-1082.853599168</v>
+        <v>-1107.85067712</v>
       </c>
       <c r="P61">
-        <v>-3839.208215232</v>
+        <v>-3927.83421888</v>
       </c>
       <c r="Q61">
-        <v>-3003.008215232</v>
+        <v>-3091.63421888</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1293971962998987</v>
+        <v>0.1314871262073962</v>
       </c>
       <c r="T61">
-        <v>1.930651184755167</v>
+        <v>1.978917464374046</v>
       </c>
       <c r="U61">
         <v>0.2008</v>
       </c>
       <c r="V61">
-        <v>0.058470752817921</v>
+        <v>0.05749624027095566</v>
       </c>
       <c r="W61">
-        <v>0.1890590728341615</v>
+        <v>0.1892547549535921</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6687,7 +6687,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.2657761491723681</v>
+        <v>0.2613465466861621</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6695,22 +6695,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1661477034551138</v>
+        <v>0.1676977034551138</v>
       </c>
       <c r="C62">
-        <v>-16388.94816757583</v>
+        <v>-17159.03618098831</v>
       </c>
       <c r="D62">
-        <v>16284.77183242417</v>
+        <v>16080.53581901169</v>
       </c>
       <c r="E62">
-        <v>27156.02</v>
+        <v>27721.872</v>
       </c>
       <c r="F62">
-        <v>33951.12</v>
+        <v>34516.97199999999</v>
       </c>
       <c r="G62">
         <v>1277.4</v>
@@ -6731,37 +6731,37 @@
         <v>1781.7</v>
       </c>
       <c r="M62">
-        <v>6817.384896</v>
+        <v>6931.007977599999</v>
       </c>
       <c r="N62">
-        <v>-5035.684896</v>
+        <v>-5149.3079776</v>
       </c>
       <c r="O62">
-        <v>-1107.85067712</v>
+        <v>-1132.847755072</v>
       </c>
       <c r="P62">
-        <v>-3927.83421888</v>
+        <v>-4016.460222528</v>
       </c>
       <c r="Q62">
-        <v>-3091.63421888</v>
+        <v>-3180.260222528</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1314871262073962</v>
+        <v>0.1336842320075859</v>
       </c>
       <c r="T62">
-        <v>1.978917464374046</v>
+        <v>2.029658937819535</v>
       </c>
       <c r="U62">
         <v>0.2008</v>
       </c>
       <c r="V62">
-        <v>0.05749624027095566</v>
+        <v>0.05655367895503836</v>
       </c>
       <c r="W62">
-        <v>0.1892547549535921</v>
+        <v>0.1894440212658283</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6769,7 +6769,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.2613465466861621</v>
+        <v>0.2570621770683561</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6777,22 +6777,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1676977034551138</v>
+        <v>0.1692477034551138</v>
       </c>
       <c r="C63">
-        <v>-17159.03618098831</v>
+        <v>-17924.06478154047</v>
       </c>
       <c r="D63">
-        <v>16080.53581901169</v>
+        <v>15881.35921845953</v>
       </c>
       <c r="E63">
-        <v>27721.872</v>
+        <v>28287.724</v>
       </c>
       <c r="F63">
-        <v>34516.97199999999</v>
+        <v>35082.824</v>
       </c>
       <c r="G63">
         <v>1277.4</v>
@@ -6813,37 +6813,37 @@
         <v>1781.7</v>
       </c>
       <c r="M63">
-        <v>6931.007977599999</v>
+        <v>7044.6310592</v>
       </c>
       <c r="N63">
-        <v>-5149.3079776</v>
+        <v>-5262.9310592</v>
       </c>
       <c r="O63">
-        <v>-1132.847755072</v>
+        <v>-1157.844833024</v>
       </c>
       <c r="P63">
-        <v>-4016.460222528</v>
+        <v>-4105.086226176</v>
       </c>
       <c r="Q63">
-        <v>-3180.260222528</v>
+        <v>-3268.886226176</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1336842320075859</v>
+        <v>0.1359969749551539</v>
       </c>
       <c r="T63">
-        <v>2.029658937819535</v>
+        <v>2.083071015130575</v>
       </c>
       <c r="U63">
         <v>0.2008</v>
       </c>
       <c r="V63">
-        <v>0.05655367895503836</v>
+        <v>0.05564152284286031</v>
       </c>
       <c r="W63">
-        <v>0.1894440212658283</v>
+        <v>0.1896271822131537</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6851,7 +6851,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.2570621770683561</v>
+        <v>0.2529160129220923</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6859,22 +6859,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1692477034551138</v>
+        <v>0.1707977034551137</v>
       </c>
       <c r="C64">
-        <v>-17924.06478154047</v>
+        <v>-18684.2196696848</v>
       </c>
       <c r="D64">
-        <v>15881.35921845953</v>
+        <v>15687.0563303152</v>
       </c>
       <c r="E64">
-        <v>28287.724</v>
+        <v>28853.576</v>
       </c>
       <c r="F64">
-        <v>35082.824</v>
+        <v>35648.676</v>
       </c>
       <c r="G64">
         <v>1277.4</v>
@@ -6895,37 +6895,37 @@
         <v>1781.7</v>
       </c>
       <c r="M64">
-        <v>7044.6310592</v>
+        <v>7158.2541408</v>
       </c>
       <c r="N64">
-        <v>-5262.9310592</v>
+        <v>-5376.5541408</v>
       </c>
       <c r="O64">
-        <v>-1157.844833024</v>
+        <v>-1182.841910976</v>
       </c>
       <c r="P64">
-        <v>-4105.086226176</v>
+        <v>-4193.712229824</v>
       </c>
       <c r="Q64">
-        <v>-3268.886226176</v>
+        <v>-3357.512229824</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1359969749551539</v>
+        <v>0.1384347310350229</v>
       </c>
       <c r="T64">
-        <v>2.083071015130575</v>
+        <v>2.139370231755726</v>
       </c>
       <c r="U64">
         <v>0.2008</v>
       </c>
       <c r="V64">
-        <v>0.05564152284286031</v>
+        <v>0.05475832406757682</v>
       </c>
       <c r="W64">
-        <v>0.1896271822131537</v>
+        <v>0.1898045285272306</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6933,7 +6933,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.2529160129220923</v>
+        <v>0.24890147303444</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6941,22 +6941,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1707977034551137</v>
+        <v>0.1723477034551137</v>
       </c>
       <c r="C65">
-        <v>-18684.2196696848</v>
+        <v>-19439.67756779652</v>
       </c>
       <c r="D65">
-        <v>15687.0563303152</v>
+        <v>15497.45043220348</v>
       </c>
       <c r="E65">
-        <v>28853.576</v>
+        <v>29419.428</v>
       </c>
       <c r="F65">
-        <v>35648.676</v>
+        <v>36214.528</v>
       </c>
       <c r="G65">
         <v>1277.4</v>
@@ -6977,37 +6977,37 @@
         <v>1781.7</v>
       </c>
       <c r="M65">
-        <v>7158.2541408</v>
+        <v>7271.877222399999</v>
       </c>
       <c r="N65">
-        <v>-5376.5541408</v>
+        <v>-5490.1772224</v>
       </c>
       <c r="O65">
-        <v>-1182.841910976</v>
+        <v>-1207.838988928</v>
       </c>
       <c r="P65">
-        <v>-4193.712229824</v>
+        <v>-4282.338233472</v>
       </c>
       <c r="Q65">
-        <v>-3357.512229824</v>
+        <v>-3446.138233472</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1384347310350229</v>
+        <v>0.141007918008218</v>
       </c>
       <c r="T65">
-        <v>2.139370231755726</v>
+        <v>2.198797182637829</v>
       </c>
       <c r="U65">
         <v>0.2008</v>
       </c>
       <c r="V65">
-        <v>0.05475832406757682</v>
+        <v>0.05390272525402093</v>
       </c>
       <c r="W65">
-        <v>0.1898045285272306</v>
+        <v>0.1899763327689926</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -7015,7 +7015,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.24890147303444</v>
+        <v>0.2450123875182769</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -7023,22 +7023,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1723477034551137</v>
+        <v>0.1738977034551137</v>
       </c>
       <c r="C66">
-        <v>-19439.67756779652</v>
+        <v>-20190.60675627373</v>
       </c>
       <c r="D66">
-        <v>15497.45043220348</v>
+        <v>15312.37324372627</v>
       </c>
       <c r="E66">
-        <v>29419.428</v>
+        <v>29985.28</v>
       </c>
       <c r="F66">
-        <v>36214.528</v>
+        <v>36780.38</v>
       </c>
       <c r="G66">
         <v>1277.4</v>
@@ -7059,37 +7059,37 @@
         <v>1781.7</v>
       </c>
       <c r="M66">
-        <v>7271.877222399999</v>
+        <v>7385.500304</v>
       </c>
       <c r="N66">
-        <v>-5490.1772224</v>
+        <v>-5603.800304</v>
       </c>
       <c r="O66">
-        <v>-1207.838988928</v>
+        <v>-1232.83606688</v>
       </c>
       <c r="P66">
-        <v>-4282.338233472</v>
+        <v>-4370.964237120001</v>
       </c>
       <c r="Q66">
-        <v>-3446.138233472</v>
+        <v>-3534.764237120001</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.141007918008218</v>
+        <v>0.1437281442370242</v>
       </c>
       <c r="T66">
-        <v>2.198797182637829</v>
+        <v>2.261619959284624</v>
       </c>
       <c r="U66">
         <v>0.2008</v>
       </c>
       <c r="V66">
-        <v>0.05390272525402093</v>
+        <v>0.05307345255780522</v>
       </c>
       <c r="W66">
-        <v>0.1899763327689926</v>
+        <v>0.1901428507263927</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -7097,7 +7097,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.2450123875182769</v>
+        <v>0.2412429661718418</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -7105,22 +7105,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1738977034551137</v>
+        <v>0.1754477034551138</v>
       </c>
       <c r="C67">
-        <v>-20190.60675627373</v>
+        <v>-20937.16757167703</v>
       </c>
       <c r="D67">
-        <v>15312.37324372627</v>
+        <v>15131.66442832297</v>
       </c>
       <c r="E67">
-        <v>29985.28</v>
+        <v>30551.132</v>
       </c>
       <c r="F67">
-        <v>36780.38</v>
+        <v>37346.232</v>
       </c>
       <c r="G67">
         <v>1277.4</v>
@@ -7141,37 +7141,37 @@
         <v>1781.7</v>
       </c>
       <c r="M67">
-        <v>7385.500304</v>
+        <v>7499.1233856</v>
       </c>
       <c r="N67">
-        <v>-5603.800304</v>
+        <v>-5717.4233856</v>
       </c>
       <c r="O67">
-        <v>-1232.83606688</v>
+        <v>-1257.833144832</v>
       </c>
       <c r="P67">
-        <v>-4370.964237120001</v>
+        <v>-4459.590240768001</v>
       </c>
       <c r="Q67">
-        <v>-3534.764237120001</v>
+        <v>-3623.390240768001</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1437281442370242</v>
+        <v>0.1466083837734073</v>
       </c>
       <c r="T67">
-        <v>2.261619959284624</v>
+        <v>2.328138193381231</v>
       </c>
       <c r="U67">
         <v>0.2008</v>
       </c>
       <c r="V67">
-        <v>0.05307345255780522</v>
+        <v>0.05226930933723242</v>
       </c>
       <c r="W67">
-        <v>0.1901428507263927</v>
+        <v>0.1903043226850837</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -7179,7 +7179,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.2412429661718418</v>
+        <v>0.2375877697146928</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -7187,22 +7187,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1754477034551138</v>
+        <v>0.1769977034551137</v>
       </c>
       <c r="C68">
-        <v>-20937.16757167703</v>
+        <v>-21679.51287000763</v>
       </c>
       <c r="D68">
-        <v>15131.66442832297</v>
+        <v>14955.17112999238</v>
       </c>
       <c r="E68">
-        <v>30551.132</v>
+        <v>31116.984</v>
       </c>
       <c r="F68">
-        <v>37346.232</v>
+        <v>37912.084</v>
       </c>
       <c r="G68">
         <v>1277.4</v>
@@ -7223,37 +7223,37 @@
         <v>1781.7</v>
       </c>
       <c r="M68">
-        <v>7499.1233856</v>
+        <v>7612.746467200001</v>
       </c>
       <c r="N68">
-        <v>-5717.4233856</v>
+        <v>-5831.046467200001</v>
       </c>
       <c r="O68">
-        <v>-1257.833144832</v>
+        <v>-1282.830222784</v>
       </c>
       <c r="P68">
-        <v>-4459.590240768001</v>
+        <v>-4548.216244416</v>
       </c>
       <c r="Q68">
-        <v>-3623.390240768001</v>
+        <v>-3712.016244416001</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1466083837734073</v>
+        <v>0.1496631832816924</v>
       </c>
       <c r="T68">
-        <v>2.328138193381231</v>
+        <v>2.398687835604905</v>
       </c>
       <c r="U68">
         <v>0.2008</v>
       </c>
       <c r="V68">
-        <v>0.05226930933723242</v>
+        <v>0.05148917039190058</v>
       </c>
       <c r="W68">
-        <v>0.1903043226850837</v>
+        <v>0.1904609745853064</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -7261,7 +7261,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.2375877697146928</v>
+        <v>0.234041683599548</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7269,22 +7269,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1769977034551137</v>
+        <v>0.1785477034551138</v>
       </c>
       <c r="C69">
-        <v>-21679.51287000763</v>
+        <v>-22417.78845793782</v>
       </c>
       <c r="D69">
-        <v>14955.17112999238</v>
+        <v>14782.74754206218</v>
       </c>
       <c r="E69">
-        <v>31116.984</v>
+        <v>31682.836</v>
       </c>
       <c r="F69">
-        <v>37912.084</v>
+        <v>38477.936</v>
       </c>
       <c r="G69">
         <v>1277.4</v>
@@ -7305,37 +7305,37 @@
         <v>1781.7</v>
       </c>
       <c r="M69">
-        <v>7612.746467200001</v>
+        <v>7726.3695488</v>
       </c>
       <c r="N69">
-        <v>-5831.046467200001</v>
+        <v>-5944.6695488</v>
       </c>
       <c r="O69">
-        <v>-1282.830222784</v>
+        <v>-1307.827300736</v>
       </c>
       <c r="P69">
-        <v>-4548.216244416</v>
+        <v>-4636.842248064</v>
       </c>
       <c r="Q69">
-        <v>-3712.016244416001</v>
+        <v>-3800.642248064</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1496631832816924</v>
+        <v>0.1529089077592453</v>
       </c>
       <c r="T69">
-        <v>2.398687835604905</v>
+        <v>2.473646830467558</v>
       </c>
       <c r="U69">
         <v>0.2008</v>
       </c>
       <c r="V69">
-        <v>0.05148917039190058</v>
+        <v>0.05073197670966675</v>
       </c>
       <c r="W69">
-        <v>0.1904609745853064</v>
+        <v>0.1906130190766989</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -7343,7 +7343,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.234041683599548</v>
+        <v>0.2305998941348488</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7351,22 +7351,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1785477034551138</v>
+        <v>0.1800977034551137</v>
       </c>
       <c r="C70">
-        <v>-22417.78845793782</v>
+        <v>-23152.13349455049</v>
       </c>
       <c r="D70">
-        <v>14782.74754206218</v>
+        <v>14614.25450544951</v>
       </c>
       <c r="E70">
-        <v>31682.836</v>
+        <v>32248.688</v>
       </c>
       <c r="F70">
-        <v>38477.936</v>
+        <v>39043.788</v>
       </c>
       <c r="G70">
         <v>1277.4</v>
@@ -7387,37 +7387,37 @@
         <v>1781.7</v>
       </c>
       <c r="M70">
-        <v>7726.3695488</v>
+        <v>7839.9926304</v>
       </c>
       <c r="N70">
-        <v>-5944.6695488</v>
+        <v>-6058.2926304</v>
       </c>
       <c r="O70">
-        <v>-1307.827300736</v>
+        <v>-1332.824378688</v>
       </c>
       <c r="P70">
-        <v>-4636.842248064</v>
+        <v>-4725.468251712</v>
       </c>
       <c r="Q70">
-        <v>-3800.642248064</v>
+        <v>-3889.268251712</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1529089077592453</v>
+        <v>0.1563640338159951</v>
       </c>
       <c r="T70">
-        <v>2.473646830467558</v>
+        <v>2.553441889514899</v>
       </c>
       <c r="U70">
         <v>0.2008</v>
       </c>
       <c r="V70">
-        <v>0.05073197670966675</v>
+        <v>0.04999673067039621</v>
       </c>
       <c r="W70">
-        <v>0.1906130190766989</v>
+        <v>0.1907606564813844</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7425,7 +7425,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.2305998941348488</v>
+        <v>0.2272578666836191</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7433,22 +7433,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1800977034551137</v>
+        <v>0.1816477034551138</v>
       </c>
       <c r="C71">
-        <v>-23152.13349455049</v>
+        <v>-23882.68086591425</v>
       </c>
       <c r="D71">
-        <v>14614.25450544951</v>
+        <v>14449.55913408575</v>
       </c>
       <c r="E71">
-        <v>32248.688</v>
+        <v>32814.54</v>
       </c>
       <c r="F71">
-        <v>39043.788</v>
+        <v>39609.64</v>
       </c>
       <c r="G71">
         <v>1277.4</v>
@@ -7469,37 +7469,37 @@
         <v>1781.7</v>
       </c>
       <c r="M71">
-        <v>7839.9926304</v>
+        <v>7953.615712</v>
       </c>
       <c r="N71">
-        <v>-6058.2926304</v>
+        <v>-6171.915712</v>
       </c>
       <c r="O71">
-        <v>-1332.824378688</v>
+        <v>-1357.82145664</v>
       </c>
       <c r="P71">
-        <v>-4725.468251712</v>
+        <v>-4814.09425536</v>
       </c>
       <c r="Q71">
-        <v>-3889.268251712</v>
+        <v>-3977.89425536</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1563640338159951</v>
+        <v>0.1600495016098616</v>
       </c>
       <c r="T71">
-        <v>2.553441889514899</v>
+        <v>2.638556619165395</v>
       </c>
       <c r="U71">
         <v>0.2008</v>
       </c>
       <c r="V71">
-        <v>0.04999673067039621</v>
+        <v>0.04928249166081913</v>
       </c>
       <c r="W71">
-        <v>0.1907606564813844</v>
+        <v>0.1909040756745075</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7507,7 +7507,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.2272578666836191</v>
+        <v>0.224011325730996</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7515,22 +7515,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1816477034551138</v>
+        <v>0.1831977034551138</v>
       </c>
       <c r="C72">
-        <v>-23882.68086591425</v>
+        <v>-24609.5575346131</v>
       </c>
       <c r="D72">
-        <v>14449.55913408575</v>
+        <v>14288.53446538691</v>
       </c>
       <c r="E72">
-        <v>32814.54</v>
+        <v>33380.39200000001</v>
       </c>
       <c r="F72">
-        <v>39609.64</v>
+        <v>40175.49200000001</v>
       </c>
       <c r="G72">
         <v>1277.4</v>
@@ -7551,37 +7551,37 @@
         <v>1781.7</v>
       </c>
       <c r="M72">
-        <v>7953.615712</v>
+        <v>8067.238793600001</v>
       </c>
       <c r="N72">
-        <v>-6171.915712</v>
+        <v>-6285.538793600002</v>
       </c>
       <c r="O72">
-        <v>-1357.82145664</v>
+        <v>-1382.818534592</v>
       </c>
       <c r="P72">
-        <v>-4814.09425536</v>
+        <v>-4902.720259008001</v>
       </c>
       <c r="Q72">
-        <v>-3977.89425536</v>
+        <v>-4066.520259008002</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1600495016098616</v>
+        <v>0.1639891395964086</v>
       </c>
       <c r="T72">
-        <v>2.638556619165395</v>
+        <v>2.729541330171099</v>
       </c>
       <c r="U72">
         <v>0.2008</v>
       </c>
       <c r="V72">
-        <v>0.04928249166081913</v>
+        <v>0.04858837205996251</v>
       </c>
       <c r="W72">
-        <v>0.1909040756745075</v>
+        <v>0.1910434548903595</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7589,7 +7589,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.224011325730996</v>
+        <v>0.2208562366361932</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7597,22 +7597,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1831977034551137</v>
+        <v>0.1847477034551137</v>
       </c>
       <c r="C73">
-        <v>-24609.55753461309</v>
+        <v>-25332.88486616298</v>
       </c>
       <c r="D73">
-        <v>14288.53446538691</v>
+        <v>14131.05913383702</v>
       </c>
       <c r="E73">
-        <v>33380.392</v>
+        <v>33946.244</v>
       </c>
       <c r="F73">
-        <v>40175.492</v>
+        <v>40741.344</v>
       </c>
       <c r="G73">
         <v>1277.4</v>
@@ -7633,37 +7633,37 @@
         <v>1781.7</v>
       </c>
       <c r="M73">
-        <v>8067.2387936</v>
+        <v>8180.861875199999</v>
       </c>
       <c r="N73">
-        <v>-6285.5387936</v>
+        <v>-6399.161875199999</v>
       </c>
       <c r="O73">
-        <v>-1382.818534592</v>
+        <v>-1407.815612544</v>
       </c>
       <c r="P73">
-        <v>-4902.720259008</v>
+        <v>-4991.346262655999</v>
       </c>
       <c r="Q73">
-        <v>-4066.520259008</v>
+        <v>-4155.146262656</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1639891395964085</v>
+        <v>0.1682101802962803</v>
       </c>
       <c r="T73">
-        <v>2.729541330171098</v>
+        <v>2.82702494910578</v>
       </c>
       <c r="U73">
         <v>0.2008</v>
       </c>
       <c r="V73">
-        <v>0.04858837205996253</v>
+        <v>0.04791353355912972</v>
       </c>
       <c r="W73">
-        <v>0.1910434548903595</v>
+        <v>0.1911789624613268</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7671,7 +7671,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.2208562366361932</v>
+        <v>0.2177887889051351</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7679,22 +7679,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1847477034551137</v>
+        <v>0.1862977034551138</v>
       </c>
       <c r="C74">
-        <v>-25332.88486616298</v>
+        <v>-26052.77893407879</v>
       </c>
       <c r="D74">
-        <v>14131.05913383702</v>
+        <v>13977.01706592121</v>
       </c>
       <c r="E74">
-        <v>33946.244</v>
+        <v>34512.096</v>
       </c>
       <c r="F74">
-        <v>40741.344</v>
+        <v>41307.196</v>
       </c>
       <c r="G74">
         <v>1277.4</v>
@@ -7715,37 +7715,37 @@
         <v>1781.7</v>
       </c>
       <c r="M74">
-        <v>8180.861875199999</v>
+        <v>8294.484956799999</v>
       </c>
       <c r="N74">
-        <v>-6399.161875199999</v>
+        <v>-6512.784956799999</v>
       </c>
       <c r="O74">
-        <v>-1407.815612544</v>
+        <v>-1432.812690496</v>
       </c>
       <c r="P74">
-        <v>-4991.346262655999</v>
+        <v>-5079.972266303999</v>
       </c>
       <c r="Q74">
-        <v>-4155.146262656</v>
+        <v>-4243.772266303999</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1682101802962803</v>
+        <v>0.172743890677624</v>
       </c>
       <c r="T74">
-        <v>2.82702494910578</v>
+        <v>2.931729576850439</v>
       </c>
       <c r="U74">
         <v>0.2008</v>
       </c>
       <c r="V74">
-        <v>0.04791353355912972</v>
+        <v>0.04725718378434712</v>
       </c>
       <c r="W74">
-        <v>0.1911789624613268</v>
+        <v>0.1913107574961031</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7753,7 +7753,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.2177887889051351</v>
+        <v>0.2148053808379414</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7761,22 +7761,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1862977034551138</v>
+        <v>0.1878477034551137</v>
       </c>
       <c r="C75">
-        <v>-26052.77893407879</v>
+        <v>-26769.3508052033</v>
       </c>
       <c r="D75">
-        <v>13977.01706592121</v>
+        <v>13826.29719479669</v>
       </c>
       <c r="E75">
-        <v>34512.096</v>
+        <v>35077.948</v>
       </c>
       <c r="F75">
-        <v>41307.196</v>
+        <v>41873.048</v>
       </c>
       <c r="G75">
         <v>1277.4</v>
@@ -7797,37 +7797,37 @@
         <v>1781.7</v>
       </c>
       <c r="M75">
-        <v>8294.484956799999</v>
+        <v>8408.1080384</v>
       </c>
       <c r="N75">
-        <v>-6512.784956799999</v>
+        <v>-6626.4080384</v>
       </c>
       <c r="O75">
-        <v>-1432.812690496</v>
+        <v>-1457.809768448</v>
       </c>
       <c r="P75">
-        <v>-5079.972266303999</v>
+        <v>-5168.598269952</v>
       </c>
       <c r="Q75">
-        <v>-4243.772266303999</v>
+        <v>-4332.398269952</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.172743890677624</v>
+        <v>0.1776263480113788</v>
       </c>
       <c r="T75">
-        <v>2.931729576850439</v>
+        <v>3.044488406729302</v>
       </c>
       <c r="U75">
         <v>0.2008</v>
       </c>
       <c r="V75">
-        <v>0.04725718378434712</v>
+        <v>0.04661857319266675</v>
       </c>
       <c r="W75">
-        <v>0.1913107574961031</v>
+        <v>0.1914389905029125</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7835,7 +7835,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.2148053808379414</v>
+        <v>0.2119026054212124</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7843,22 +7843,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1878477034551137</v>
+        <v>0.1893977034551138</v>
       </c>
       <c r="C76">
-        <v>-26769.3508052033</v>
+        <v>-27482.70680677235</v>
       </c>
       <c r="D76">
-        <v>13826.29719479669</v>
+        <v>13678.79319322764</v>
       </c>
       <c r="E76">
-        <v>35077.948</v>
+        <v>35643.8</v>
       </c>
       <c r="F76">
-        <v>41873.048</v>
+        <v>42438.89999999999</v>
       </c>
       <c r="G76">
         <v>1277.4</v>
@@ -7879,37 +7879,37 @@
         <v>1781.7</v>
       </c>
       <c r="M76">
-        <v>8408.1080384</v>
+        <v>8521.731119999999</v>
       </c>
       <c r="N76">
-        <v>-6626.4080384</v>
+        <v>-6740.031119999999</v>
       </c>
       <c r="O76">
-        <v>-1457.809768448</v>
+        <v>-1482.8068464</v>
       </c>
       <c r="P76">
-        <v>-5168.598269952</v>
+        <v>-5257.224273599999</v>
       </c>
       <c r="Q76">
-        <v>-4332.398269952</v>
+        <v>-4421.024273599999</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1776263480113788</v>
+        <v>0.1828994019318339</v>
       </c>
       <c r="T76">
-        <v>3.044488406729302</v>
+        <v>3.166267942998473</v>
       </c>
       <c r="U76">
         <v>0.2008</v>
       </c>
       <c r="V76">
-        <v>0.04661857319266675</v>
+        <v>0.04599699221676453</v>
       </c>
       <c r="W76">
-        <v>0.1914389905029125</v>
+        <v>0.1915638039628737</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7917,7 +7917,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.2119026054212124</v>
+        <v>0.2090772373489297</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7925,22 +7925,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1893977034551138</v>
+        <v>0.1909477034551137</v>
       </c>
       <c r="C77">
-        <v>-27482.70680677235</v>
+        <v>-28192.94877656535</v>
       </c>
       <c r="D77">
-        <v>13678.79319322764</v>
+        <v>13534.40322343465</v>
       </c>
       <c r="E77">
-        <v>35643.8</v>
+        <v>36209.652</v>
       </c>
       <c r="F77">
-        <v>42438.89999999999</v>
+        <v>43004.752</v>
       </c>
       <c r="G77">
         <v>1277.4</v>
@@ -7961,37 +7961,37 @@
         <v>1781.7</v>
       </c>
       <c r="M77">
-        <v>8521.731119999999</v>
+        <v>8635.354201600001</v>
       </c>
       <c r="N77">
-        <v>-6740.031119999999</v>
+        <v>-6853.654201600001</v>
       </c>
       <c r="O77">
-        <v>-1482.8068464</v>
+        <v>-1507.803924352</v>
       </c>
       <c r="P77">
-        <v>-5257.224273599999</v>
+        <v>-5345.850277248001</v>
       </c>
       <c r="Q77">
-        <v>-4421.024273599999</v>
+        <v>-4509.650277248001</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1828994019318339</v>
+        <v>0.188611877012327</v>
       </c>
       <c r="T77">
-        <v>3.166267942998473</v>
+        <v>3.298195773956744</v>
       </c>
       <c r="U77">
         <v>0.2008</v>
       </c>
       <c r="V77">
-        <v>0.04599699221676453</v>
+        <v>0.04539176863496498</v>
       </c>
       <c r="W77">
-        <v>0.1915638039628737</v>
+        <v>0.1916853328580991</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7999,7 +7999,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.2090772373489297</v>
+        <v>0.2063262210680227</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -8007,22 +8007,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1909477034551137</v>
+        <v>0.1924977034551137</v>
       </c>
       <c r="C78">
-        <v>-28192.94877656535</v>
+        <v>-28900.17429737826</v>
       </c>
       <c r="D78">
-        <v>13534.40322343465</v>
+        <v>13393.02970262174</v>
       </c>
       <c r="E78">
-        <v>36209.652</v>
+        <v>36775.504</v>
       </c>
       <c r="F78">
-        <v>43004.752</v>
+        <v>43570.604</v>
       </c>
       <c r="G78">
         <v>1277.4</v>
@@ -8043,37 +8043,37 @@
         <v>1781.7</v>
       </c>
       <c r="M78">
-        <v>8635.354201600001</v>
+        <v>8748.9772832</v>
       </c>
       <c r="N78">
-        <v>-6853.654201600001</v>
+        <v>-6967.2772832</v>
       </c>
       <c r="O78">
-        <v>-1507.803924352</v>
+        <v>-1532.801002304</v>
       </c>
       <c r="P78">
-        <v>-5345.850277248001</v>
+        <v>-5434.476280896</v>
       </c>
       <c r="Q78">
-        <v>-4509.650277248001</v>
+        <v>-4598.276280896001</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.188611877012327</v>
+        <v>0.1948210890563412</v>
       </c>
       <c r="T78">
-        <v>3.298195773956744</v>
+        <v>3.441595590215733</v>
       </c>
       <c r="U78">
         <v>0.2008</v>
       </c>
       <c r="V78">
-        <v>0.04539176863496498</v>
+        <v>0.04480226514619921</v>
       </c>
       <c r="W78">
-        <v>0.1916853328580991</v>
+        <v>0.1918037051586432</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -8081,7 +8081,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.2063262210680227</v>
+        <v>0.2036466597554509</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -8089,22 +8089,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1924977034551137</v>
+        <v>0.1940477034551137</v>
       </c>
       <c r="C79">
-        <v>-28900.17429737826</v>
+        <v>-29604.47691695334</v>
       </c>
       <c r="D79">
-        <v>13393.02970262174</v>
+        <v>13254.57908304666</v>
       </c>
       <c r="E79">
-        <v>36775.504</v>
+        <v>37341.356</v>
       </c>
       <c r="F79">
-        <v>43570.604</v>
+        <v>44136.456</v>
       </c>
       <c r="G79">
         <v>1277.4</v>
@@ -8125,37 +8125,37 @@
         <v>1781.7</v>
       </c>
       <c r="M79">
-        <v>8748.9772832</v>
+        <v>8862.600364800001</v>
       </c>
       <c r="N79">
-        <v>-6967.2772832</v>
+        <v>-7080.900364800001</v>
       </c>
       <c r="O79">
-        <v>-1532.801002304</v>
+        <v>-1557.798080256</v>
       </c>
       <c r="P79">
-        <v>-5434.476280896</v>
+        <v>-5523.102284544</v>
       </c>
       <c r="Q79">
-        <v>-4598.276280896001</v>
+        <v>-4686.902284544</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1948210890563412</v>
+        <v>0.2015947749225385</v>
       </c>
       <c r="T79">
-        <v>3.441595590215733</v>
+        <v>3.598031753407357</v>
       </c>
       <c r="U79">
         <v>0.2008</v>
       </c>
       <c r="V79">
-        <v>0.04480226514619921</v>
+        <v>0.04422787713150435</v>
       </c>
       <c r="W79">
-        <v>0.1918037051586432</v>
+        <v>0.1919190422719939</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -8163,7 +8163,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.2036466597554509</v>
+        <v>0.2010358051432015</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -8171,22 +8171,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1940477034551137</v>
+        <v>0.2234294797373575</v>
       </c>
       <c r="C80">
-        <v>-29604.47691695334</v>
+        <v>-32342.09240808849</v>
       </c>
       <c r="D80">
-        <v>13254.57908304666</v>
+        <v>11082.8155919115</v>
       </c>
       <c r="E80">
-        <v>37341.356</v>
+        <v>37907.208</v>
       </c>
       <c r="F80">
-        <v>44136.456</v>
+        <v>44702.308</v>
       </c>
       <c r="G80">
         <v>1277.4</v>
@@ -8207,45 +8207,45 @@
         <v>1781.7</v>
       </c>
       <c r="M80">
-        <v>8862.600364800001</v>
+        <v>10540.8042264</v>
       </c>
       <c r="N80">
-        <v>-7080.900364800001</v>
+        <v>-8759.104226399999</v>
       </c>
       <c r="O80">
-        <v>-1557.798080256</v>
+        <v>-1927.002929808</v>
       </c>
       <c r="P80">
-        <v>-5523.102284544</v>
+        <v>-6832.101296591999</v>
       </c>
       <c r="Q80">
-        <v>-4686.902284544</v>
+        <v>-5995.901296591999</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2015947749225385</v>
+        <v>0.2098791750723915</v>
       </c>
       <c r="T80">
-        <v>3.598031753407357</v>
+        <v>3.789357391972089</v>
       </c>
       <c r="U80">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.04422787713150435</v>
+        <v>0.03718634665638514</v>
       </c>
       <c r="W80">
-        <v>0.1919190422719939</v>
+        <v>0.2270314594584244</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y80">
-        <v>0.2010358051432015</v>
+        <v>0.1690288484381144</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8253,22 +8253,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2234294797373575</v>
+        <v>0.2253294797373575</v>
       </c>
       <c r="C81">
-        <v>-32342.09240808849</v>
+        <v>-33024.14139872145</v>
       </c>
       <c r="D81">
-        <v>11082.8155919115</v>
+        <v>10966.61860127855</v>
       </c>
       <c r="E81">
-        <v>37907.208</v>
+        <v>38473.06</v>
       </c>
       <c r="F81">
-        <v>44702.308</v>
+        <v>45268.16</v>
       </c>
       <c r="G81">
         <v>1277.4</v>
@@ -8289,37 +8289,37 @@
         <v>1781.7</v>
       </c>
       <c r="M81">
-        <v>10540.8042264</v>
+        <v>10674.232128</v>
       </c>
       <c r="N81">
-        <v>-8759.104226399999</v>
+        <v>-8892.532128000001</v>
       </c>
       <c r="O81">
-        <v>-1927.002929808</v>
+        <v>-1956.35706816</v>
       </c>
       <c r="P81">
-        <v>-6832.101296591999</v>
+        <v>-6936.17505984</v>
       </c>
       <c r="Q81">
-        <v>-5995.901296591999</v>
+        <v>-6099.975059840001</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2098791750723915</v>
+        <v>0.218083133826011</v>
       </c>
       <c r="T81">
-        <v>3.789357391972089</v>
+        <v>3.978825261570694</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.03718634665638514</v>
+        <v>0.03672151732318032</v>
       </c>
       <c r="W81">
-        <v>0.2270314594584244</v>
+        <v>0.2271410662151941</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8327,7 +8327,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.1690288484381144</v>
+        <v>0.1669159878326379</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8335,22 +8335,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2253294797373575</v>
+        <v>0.2272294797373575</v>
       </c>
       <c r="C82">
-        <v>-33024.14139872145</v>
+        <v>-33703.77915166132</v>
       </c>
       <c r="D82">
-        <v>10966.61860127855</v>
+        <v>10852.83284833868</v>
       </c>
       <c r="E82">
-        <v>38473.06</v>
+        <v>39038.912</v>
       </c>
       <c r="F82">
-        <v>45268.16</v>
+        <v>45834.012</v>
       </c>
       <c r="G82">
         <v>1277.4</v>
@@ -8371,37 +8371,37 @@
         <v>1781.7</v>
       </c>
       <c r="M82">
-        <v>10674.232128</v>
+        <v>10807.6600296</v>
       </c>
       <c r="N82">
-        <v>-8892.532128000001</v>
+        <v>-9025.960029600001</v>
       </c>
       <c r="O82">
-        <v>-1956.35706816</v>
+        <v>-1985.711206512</v>
       </c>
       <c r="P82">
-        <v>-6936.17505984</v>
+        <v>-7040.248823088001</v>
       </c>
       <c r="Q82">
-        <v>-6099.975059840001</v>
+        <v>-6204.048823088001</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.218083133826011</v>
+        <v>0.2271506671852748</v>
       </c>
       <c r="T82">
-        <v>3.978825261570694</v>
+        <v>4.188237117442837</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.03672151732318032</v>
+        <v>0.03626816525746204</v>
       </c>
       <c r="W82">
-        <v>0.2271410662151941</v>
+        <v>0.2272479666322905</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8409,7 +8409,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.1669159878326379</v>
+        <v>0.1648552966248276</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8417,22 +8417,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2272294797373575</v>
+        <v>0.2291294797373575</v>
       </c>
       <c r="C83">
-        <v>-33703.77915166132</v>
+        <v>-34381.0799506132</v>
       </c>
       <c r="D83">
-        <v>10852.83284833868</v>
+        <v>10741.38404938681</v>
       </c>
       <c r="E83">
-        <v>39038.912</v>
+        <v>39604.764</v>
       </c>
       <c r="F83">
-        <v>45834.012</v>
+        <v>46399.864</v>
       </c>
       <c r="G83">
         <v>1277.4</v>
@@ -8453,37 +8453,37 @@
         <v>1781.7</v>
       </c>
       <c r="M83">
-        <v>10807.6600296</v>
+        <v>10941.0879312</v>
       </c>
       <c r="N83">
-        <v>-9025.960029600001</v>
+        <v>-9159.387931200001</v>
       </c>
       <c r="O83">
-        <v>-1985.711206512</v>
+        <v>-2015.065344864</v>
       </c>
       <c r="P83">
-        <v>-7040.248823088001</v>
+        <v>-7144.322586336</v>
       </c>
       <c r="Q83">
-        <v>-6204.048823088001</v>
+        <v>-6308.122586336</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2271506671852748</v>
+        <v>0.2372257042511234</v>
       </c>
       <c r="T83">
-        <v>4.188237117442837</v>
+        <v>4.420916957300772</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.03626816525746204</v>
+        <v>0.03582587055920031</v>
       </c>
       <c r="W83">
-        <v>0.2272479666322905</v>
+        <v>0.2273522597221406</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8491,7 +8491,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.1648552966248276</v>
+        <v>0.1628448661781833</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8499,22 +8499,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2291294797373575</v>
+        <v>0.2310294797373575</v>
       </c>
       <c r="C84">
-        <v>-34381.0799506132</v>
+        <v>-35056.11505899137</v>
       </c>
       <c r="D84">
-        <v>10741.38404938681</v>
+        <v>10632.20094100863</v>
       </c>
       <c r="E84">
-        <v>39604.764</v>
+        <v>40170.616</v>
       </c>
       <c r="F84">
-        <v>46399.864</v>
+        <v>46965.716</v>
       </c>
       <c r="G84">
         <v>1277.4</v>
@@ -8535,37 +8535,37 @@
         <v>1781.7</v>
       </c>
       <c r="M84">
-        <v>10941.0879312</v>
+        <v>11074.5158328</v>
       </c>
       <c r="N84">
-        <v>-9159.387931200001</v>
+        <v>-9292.815832799999</v>
       </c>
       <c r="O84">
-        <v>-2015.065344864</v>
+        <v>-2044.419483216</v>
       </c>
       <c r="P84">
-        <v>-7144.322586336</v>
+        <v>-7248.396349583999</v>
       </c>
       <c r="Q84">
-        <v>-6308.122586336</v>
+        <v>-6412.196349583999</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2372257042511234</v>
+        <v>0.2484860397953071</v>
       </c>
       <c r="T84">
-        <v>4.420916957300772</v>
+        <v>4.680970895965523</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.03582587055920031</v>
+        <v>0.03539423356451116</v>
       </c>
       <c r="W84">
-        <v>0.2273522597221406</v>
+        <v>0.2274540397254883</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8573,7 +8573,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.1628448661781833</v>
+        <v>0.1608828798386871</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8581,22 +8581,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2310294797373575</v>
+        <v>0.2329294797373575</v>
       </c>
       <c r="C85">
-        <v>-35056.11505899137</v>
+        <v>-35728.95287187673</v>
       </c>
       <c r="D85">
-        <v>10632.20094100863</v>
+        <v>10525.21512812327</v>
       </c>
       <c r="E85">
-        <v>40170.616</v>
+        <v>40736.468</v>
       </c>
       <c r="F85">
-        <v>46965.716</v>
+        <v>47531.568</v>
       </c>
       <c r="G85">
         <v>1277.4</v>
@@ -8617,37 +8617,37 @@
         <v>1781.7</v>
       </c>
       <c r="M85">
-        <v>11074.5158328</v>
+        <v>11207.9437344</v>
       </c>
       <c r="N85">
-        <v>-9292.815832799999</v>
+        <v>-9426.243734399999</v>
       </c>
       <c r="O85">
-        <v>-2044.419483216</v>
+        <v>-2073.773621568</v>
       </c>
       <c r="P85">
-        <v>-7248.396349583999</v>
+        <v>-7352.470112831999</v>
       </c>
       <c r="Q85">
-        <v>-6412.196349583999</v>
+        <v>-6516.270112832</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2484860397953071</v>
+        <v>0.2611539172825139</v>
       </c>
       <c r="T85">
-        <v>4.680970895965523</v>
+        <v>4.973531576963369</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.03539423356451116</v>
+        <v>0.03497287364112412</v>
       </c>
       <c r="W85">
-        <v>0.2274540397254883</v>
+        <v>0.2275533963954229</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8655,7 +8655,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.1608828798386871</v>
+        <v>0.1589676074596552</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8663,22 +8663,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2329294797373574</v>
+        <v>0.2348294797373575</v>
       </c>
       <c r="C86">
-        <v>-35728.95287187673</v>
+        <v>-36399.65905889115</v>
       </c>
       <c r="D86">
-        <v>10525.21512812327</v>
+        <v>10420.36094110885</v>
       </c>
       <c r="E86">
-        <v>40736.468</v>
+        <v>41302.32</v>
       </c>
       <c r="F86">
-        <v>47531.568</v>
+        <v>48097.42</v>
       </c>
       <c r="G86">
         <v>1277.4</v>
@@ -8699,37 +8699,37 @@
         <v>1781.7</v>
       </c>
       <c r="M86">
-        <v>11207.9437344</v>
+        <v>11341.371636</v>
       </c>
       <c r="N86">
-        <v>-9426.243734399999</v>
+        <v>-9559.671635999999</v>
       </c>
       <c r="O86">
-        <v>-2073.773621568</v>
+        <v>-2103.12775992</v>
       </c>
       <c r="P86">
-        <v>-7352.470112831999</v>
+        <v>-7456.543876079999</v>
       </c>
       <c r="Q86">
-        <v>-6516.270112832</v>
+        <v>-6620.343876079999</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2611539172825137</v>
+        <v>0.275510845101348</v>
       </c>
       <c r="T86">
-        <v>4.973531576963365</v>
+        <v>5.305100348760924</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.03497287364112412</v>
+        <v>0.0345614280688756</v>
       </c>
       <c r="W86">
-        <v>0.2275533963954229</v>
+        <v>0.2276504152613591</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8737,7 +8737,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.1589676074596552</v>
+        <v>0.157097400313071</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8745,22 +8745,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2348294797373575</v>
+        <v>0.2367294797373575</v>
       </c>
       <c r="C87">
-        <v>-36399.65905889115</v>
+        <v>-37068.29669861609</v>
       </c>
       <c r="D87">
-        <v>10420.36094110885</v>
+        <v>10317.57530138391</v>
       </c>
       <c r="E87">
-        <v>41302.32</v>
+        <v>41868.172</v>
       </c>
       <c r="F87">
-        <v>48097.42</v>
+        <v>48663.272</v>
       </c>
       <c r="G87">
         <v>1277.4</v>
@@ -8781,37 +8781,37 @@
         <v>1781.7</v>
       </c>
       <c r="M87">
-        <v>11341.371636</v>
+        <v>11474.7995376</v>
       </c>
       <c r="N87">
-        <v>-9559.671635999999</v>
+        <v>-9693.099537599999</v>
       </c>
       <c r="O87">
-        <v>-2103.12775992</v>
+        <v>-2132.481898272</v>
       </c>
       <c r="P87">
-        <v>-7456.543876079999</v>
+        <v>-7560.617639327999</v>
       </c>
       <c r="Q87">
-        <v>-6620.343876079999</v>
+        <v>-6724.417639327999</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.275510845101348</v>
+        <v>0.2919187626085871</v>
       </c>
       <c r="T87">
-        <v>5.305100348760924</v>
+        <v>5.684036087958133</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.0345614280688756</v>
+        <v>0.03415955099830728</v>
       </c>
       <c r="W87">
-        <v>0.2276504152613591</v>
+        <v>0.2277451778745992</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8819,7 +8819,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.157097400313071</v>
+        <v>0.1552706863559422</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8827,22 +8827,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2367294797373575</v>
+        <v>0.2386294797373575</v>
       </c>
       <c r="C88">
-        <v>-37068.29669861609</v>
+        <v>-37734.92640513349</v>
       </c>
       <c r="D88">
-        <v>10317.57530138391</v>
+        <v>10216.7975948665</v>
       </c>
       <c r="E88">
-        <v>41868.172</v>
+        <v>42434.024</v>
       </c>
       <c r="F88">
-        <v>48663.272</v>
+        <v>49229.124</v>
       </c>
       <c r="G88">
         <v>1277.4</v>
@@ -8863,37 +8863,37 @@
         <v>1781.7</v>
       </c>
       <c r="M88">
-        <v>11474.7995376</v>
+        <v>11608.2274392</v>
       </c>
       <c r="N88">
-        <v>-9693.099537599999</v>
+        <v>-9826.527439199999</v>
       </c>
       <c r="O88">
-        <v>-2132.481898272</v>
+        <v>-2161.836036624</v>
       </c>
       <c r="P88">
-        <v>-7560.617639327999</v>
+        <v>-7664.691402576</v>
       </c>
       <c r="Q88">
-        <v>-6724.417639327999</v>
+        <v>-6828.491402576</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2919187626085871</v>
+        <v>0.31085097511694</v>
       </c>
       <c r="T88">
-        <v>5.684036087958133</v>
+        <v>6.121269633185682</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.03415955099830728</v>
+        <v>0.03376691248108536</v>
       </c>
       <c r="W88">
-        <v>0.2277451778745992</v>
+        <v>0.2278377620369601</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8901,7 +8901,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.1552706863559422</v>
+        <v>0.1534859658231154</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8909,22 +8909,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2386294797373575</v>
+        <v>0.2405294797373575</v>
       </c>
       <c r="C89">
-        <v>-37734.92640513349</v>
+        <v>-38399.60644722251</v>
       </c>
       <c r="D89">
-        <v>10216.7975948665</v>
+        <v>10117.96955277748</v>
       </c>
       <c r="E89">
-        <v>42434.024</v>
+        <v>42999.876</v>
       </c>
       <c r="F89">
-        <v>49229.124</v>
+        <v>49794.976</v>
       </c>
       <c r="G89">
         <v>1277.4</v>
@@ -8945,37 +8945,37 @@
         <v>1781.7</v>
       </c>
       <c r="M89">
-        <v>11608.2274392</v>
+        <v>11741.6553408</v>
       </c>
       <c r="N89">
-        <v>-9826.527439199999</v>
+        <v>-9959.955340799999</v>
       </c>
       <c r="O89">
-        <v>-2161.836036624</v>
+        <v>-2191.190174976</v>
       </c>
       <c r="P89">
-        <v>-7664.691402576</v>
+        <v>-7768.765165823999</v>
       </c>
       <c r="Q89">
-        <v>-6828.491402576</v>
+        <v>-6932.565165823999</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.31085097511694</v>
+        <v>0.3329385563766851</v>
       </c>
       <c r="T89">
-        <v>6.121269633185682</v>
+        <v>6.631375435951157</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.03376691248108536</v>
+        <v>0.03338319756652757</v>
       </c>
       <c r="W89">
-        <v>0.2278377620369601</v>
+        <v>0.2279282420138128</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8983,7 +8983,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.1534859658231154</v>
+        <v>0.1517418071205799</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8991,22 +8991,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2405294797373575</v>
+        <v>0.2424294797373575</v>
       </c>
       <c r="C90">
-        <v>-38399.60644722251</v>
+        <v>-39062.39286070444</v>
       </c>
       <c r="D90">
-        <v>10117.96955277748</v>
+        <v>10021.03513929556</v>
       </c>
       <c r="E90">
-        <v>42999.876</v>
+        <v>43565.728</v>
       </c>
       <c r="F90">
-        <v>49794.976</v>
+        <v>50360.828</v>
       </c>
       <c r="G90">
         <v>1277.4</v>
@@ -9027,37 +9027,37 @@
         <v>1781.7</v>
       </c>
       <c r="M90">
-        <v>11741.6553408</v>
+        <v>11875.0832424</v>
       </c>
       <c r="N90">
-        <v>-9959.955340799999</v>
+        <v>-10093.3832424</v>
       </c>
       <c r="O90">
-        <v>-2191.190174976</v>
+        <v>-2220.544313328</v>
       </c>
       <c r="P90">
-        <v>-7768.765165823999</v>
+        <v>-7872.838929071999</v>
       </c>
       <c r="Q90">
-        <v>-6932.565165823999</v>
+        <v>-7036.638929071999</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3329385563766851</v>
+        <v>0.3590420615018383</v>
       </c>
       <c r="T90">
-        <v>6.631375435951157</v>
+        <v>7.234227748310352</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.03338319756652757</v>
+        <v>0.0330081054590385</v>
       </c>
       <c r="W90">
-        <v>0.2279282420138128</v>
+        <v>0.2280166887327587</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -9065,7 +9065,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.1517418071205799</v>
+        <v>0.1500368429956296</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -9073,22 +9073,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2424294797373575</v>
+        <v>0.2443294797373575</v>
       </c>
       <c r="C91">
-        <v>-39062.39286070444</v>
+        <v>-39723.33955439102</v>
       </c>
       <c r="D91">
-        <v>10021.03513929556</v>
+        <v>9925.940445608976</v>
       </c>
       <c r="E91">
-        <v>43565.728</v>
+        <v>44131.58</v>
       </c>
       <c r="F91">
-        <v>50360.828</v>
+        <v>50926.68</v>
       </c>
       <c r="G91">
         <v>1277.4</v>
@@ -9109,37 +9109,37 @@
         <v>1781.7</v>
       </c>
       <c r="M91">
-        <v>11875.0832424</v>
+        <v>12008.511144</v>
       </c>
       <c r="N91">
-        <v>-10093.3832424</v>
+        <v>-10226.811144</v>
       </c>
       <c r="O91">
-        <v>-2220.544313328</v>
+        <v>-2249.89845168</v>
       </c>
       <c r="P91">
-        <v>-7872.838929071999</v>
+        <v>-7976.91269232</v>
       </c>
       <c r="Q91">
-        <v>-7036.638929071999</v>
+        <v>-7140.71269232</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3590420615018383</v>
+        <v>0.3903662676520221</v>
       </c>
       <c r="T91">
-        <v>7.234227748310352</v>
+        <v>7.957650523141388</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.0330081054590385</v>
+        <v>0.03264134873171584</v>
       </c>
       <c r="W91">
-        <v>0.2280166887327587</v>
+        <v>0.2281031699690614</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -9147,7 +9147,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.1500368429956296</v>
+        <v>0.1483697669623448</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -9155,22 +9155,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2443294797373575</v>
+        <v>0.2462294797373575</v>
       </c>
       <c r="C92">
-        <v>-39723.33955439102</v>
+        <v>-40382.49841005722</v>
       </c>
       <c r="D92">
-        <v>9925.940445608976</v>
+        <v>9832.633589942781</v>
       </c>
       <c r="E92">
-        <v>44131.58</v>
+        <v>44697.432</v>
       </c>
       <c r="F92">
-        <v>50926.68</v>
+        <v>51492.532</v>
       </c>
       <c r="G92">
         <v>1277.4</v>
@@ -9191,37 +9191,37 @@
         <v>1781.7</v>
       </c>
       <c r="M92">
-        <v>12008.511144</v>
+        <v>12141.9390456</v>
       </c>
       <c r="N92">
-        <v>-10226.811144</v>
+        <v>-10360.2390456</v>
       </c>
       <c r="O92">
-        <v>-2249.89845168</v>
+        <v>-2279.252590032</v>
       </c>
       <c r="P92">
-        <v>-7976.91269232</v>
+        <v>-8080.986455568</v>
       </c>
       <c r="Q92">
-        <v>-7140.71269232</v>
+        <v>-7244.786455568</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3903662676520221</v>
+        <v>0.4286514085022469</v>
       </c>
       <c r="T92">
-        <v>7.957650523141388</v>
+        <v>8.841833914601544</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.03264134873171584</v>
+        <v>0.03228265259180688</v>
       </c>
       <c r="W92">
-        <v>0.2281031699690614</v>
+        <v>0.228187750518852</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -9229,7 +9229,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.1483697669623448</v>
+        <v>0.1467393299627586</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9237,22 +9237,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2462294797373575</v>
+        <v>0.2481294797373575</v>
       </c>
       <c r="C93">
-        <v>-40382.49841005722</v>
+        <v>-41039.91937682766</v>
       </c>
       <c r="D93">
-        <v>9832.633589942781</v>
+        <v>9741.064623172339</v>
       </c>
       <c r="E93">
-        <v>44697.432</v>
+        <v>45263.284</v>
       </c>
       <c r="F93">
-        <v>51492.532</v>
+        <v>52058.384</v>
       </c>
       <c r="G93">
         <v>1277.4</v>
@@ -9273,37 +9273,37 @@
         <v>1781.7</v>
       </c>
       <c r="M93">
-        <v>12141.9390456</v>
+        <v>12275.3669472</v>
       </c>
       <c r="N93">
-        <v>-10360.2390456</v>
+        <v>-10493.6669472</v>
       </c>
       <c r="O93">
-        <v>-2279.252590032</v>
+        <v>-2308.606728384</v>
       </c>
       <c r="P93">
-        <v>-8080.986455568</v>
+        <v>-8185.060218815999</v>
       </c>
       <c r="Q93">
-        <v>-7244.786455568</v>
+        <v>-7348.860218815999</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4286514085022469</v>
+        <v>0.4765078345650278</v>
       </c>
       <c r="T93">
-        <v>8.841833914601544</v>
+        <v>9.94706315392674</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.03228265259180688</v>
+        <v>0.03193175419406985</v>
       </c>
       <c r="W93">
-        <v>0.228187750518852</v>
+        <v>0.2282704923610384</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9311,7 +9311,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.1467393299627586</v>
+        <v>0.1451443372457721</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9319,22 +9319,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2481294797373575</v>
+        <v>0.2500294797373575</v>
       </c>
       <c r="C94">
-        <v>-41039.91937682766</v>
+        <v>-41695.65056033793</v>
       </c>
       <c r="D94">
-        <v>9741.064623172339</v>
+        <v>9651.185439662062</v>
       </c>
       <c r="E94">
-        <v>45263.284</v>
+        <v>45829.136</v>
       </c>
       <c r="F94">
-        <v>52058.384</v>
+        <v>52624.236</v>
       </c>
       <c r="G94">
         <v>1277.4</v>
@@ -9355,37 +9355,37 @@
         <v>1781.7</v>
       </c>
       <c r="M94">
-        <v>12275.3669472</v>
+        <v>12408.7948488</v>
       </c>
       <c r="N94">
-        <v>-10493.6669472</v>
+        <v>-10627.0948488</v>
       </c>
       <c r="O94">
-        <v>-2308.606728384</v>
+        <v>-2337.960866736</v>
       </c>
       <c r="P94">
-        <v>-8185.060218815999</v>
+        <v>-8289.133982063999</v>
       </c>
       <c r="Q94">
-        <v>-7348.860218815999</v>
+        <v>-7452.933982063999</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4765078345650278</v>
+        <v>0.5380375252171746</v>
       </c>
       <c r="T94">
-        <v>9.94706315392674</v>
+        <v>11.36807217591628</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.03193175419406985</v>
+        <v>0.03158840199843469</v>
       </c>
       <c r="W94">
-        <v>0.2282704923610384</v>
+        <v>0.2283514548087691</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9393,7 +9393,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.1451443372457721</v>
+        <v>0.1435836454474304</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9401,22 +9401,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2500294797373575</v>
+        <v>0.2519294797373575</v>
       </c>
       <c r="C95">
-        <v>-41695.65056033793</v>
+        <v>-42349.73830700485</v>
       </c>
       <c r="D95">
-        <v>9651.185439662062</v>
+        <v>9562.949692995153</v>
       </c>
       <c r="E95">
-        <v>45829.136</v>
+        <v>46394.988</v>
       </c>
       <c r="F95">
-        <v>52624.236</v>
+        <v>53190.088</v>
       </c>
       <c r="G95">
         <v>1277.4</v>
@@ -9437,37 +9437,37 @@
         <v>1781.7</v>
       </c>
       <c r="M95">
-        <v>12408.7948488</v>
+        <v>12542.2227504</v>
       </c>
       <c r="N95">
-        <v>-10627.0948488</v>
+        <v>-10760.5227504</v>
       </c>
       <c r="O95">
-        <v>-2337.960866736</v>
+        <v>-2367.315005088</v>
       </c>
       <c r="P95">
-        <v>-8289.133982063999</v>
+        <v>-8393.207745312</v>
       </c>
       <c r="Q95">
-        <v>-7452.933982063999</v>
+        <v>-7557.007745312</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5380375252171746</v>
+        <v>0.6200771127533705</v>
       </c>
       <c r="T95">
-        <v>11.36807217591628</v>
+        <v>13.26275087190232</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.03158840199843469</v>
+        <v>0.03125235516866411</v>
       </c>
       <c r="W95">
-        <v>0.2283514548087691</v>
+        <v>0.228430694651229</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9475,7 +9475,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.1435836454474304</v>
+        <v>0.1420561598575641</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9483,22 +9483,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2519294797373575</v>
+        <v>0.2538294797373575</v>
       </c>
       <c r="C96">
-        <v>-42349.73830700485</v>
+        <v>-43002.22728371595</v>
       </c>
       <c r="D96">
-        <v>9562.949692995153</v>
+        <v>9476.312716284046</v>
       </c>
       <c r="E96">
-        <v>46394.988</v>
+        <v>46960.84</v>
       </c>
       <c r="F96">
-        <v>53190.088</v>
+        <v>53755.94</v>
       </c>
       <c r="G96">
         <v>1277.4</v>
@@ -9519,37 +9519,37 @@
         <v>1781.7</v>
       </c>
       <c r="M96">
-        <v>12542.2227504</v>
+        <v>12675.650652</v>
       </c>
       <c r="N96">
-        <v>-10760.5227504</v>
+        <v>-10893.950652</v>
       </c>
       <c r="O96">
-        <v>-2367.315005088</v>
+        <v>-2396.66914344</v>
       </c>
       <c r="P96">
-        <v>-8393.207745312</v>
+        <v>-8497.28150856</v>
       </c>
       <c r="Q96">
-        <v>-7557.007745312</v>
+        <v>-7661.08150856</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.6200771127533705</v>
+        <v>0.7349325353040449</v>
       </c>
       <c r="T96">
-        <v>13.26275087190232</v>
+        <v>15.91530104628279</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.03125235516866411</v>
+        <v>0.03092338300899396</v>
       </c>
       <c r="W96">
-        <v>0.228430694651229</v>
+        <v>0.2285082662864792</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9557,7 +9557,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.1420561598575641</v>
+        <v>0.1405608318590635</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9565,22 +9565,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2538294797373575</v>
+        <v>0.2557294797373575</v>
       </c>
       <c r="C97">
-        <v>-43002.22728371595</v>
+        <v>-43653.1605532262</v>
       </c>
       <c r="D97">
-        <v>9476.312716284046</v>
+        <v>9391.231446773802</v>
       </c>
       <c r="E97">
-        <v>46960.84</v>
+        <v>47526.692</v>
       </c>
       <c r="F97">
-        <v>53755.94</v>
+        <v>54321.792</v>
       </c>
       <c r="G97">
         <v>1277.4</v>
@@ -9601,37 +9601,37 @@
         <v>1781.7</v>
       </c>
       <c r="M97">
-        <v>12675.650652</v>
+        <v>12809.0785536</v>
       </c>
       <c r="N97">
-        <v>-10893.950652</v>
+        <v>-11027.3785536</v>
       </c>
       <c r="O97">
-        <v>-2396.66914344</v>
+        <v>-2426.023281792</v>
       </c>
       <c r="P97">
-        <v>-8497.28150856</v>
+        <v>-8601.355271807999</v>
       </c>
       <c r="Q97">
-        <v>-7661.08150856</v>
+        <v>-7765.155271807999</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.7349325353040449</v>
+        <v>0.9072156691300567</v>
       </c>
       <c r="T97">
-        <v>15.91530104628279</v>
+        <v>19.8941263078535</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.03092338300899396</v>
+        <v>0.03060126443598361</v>
       </c>
       <c r="W97">
-        <v>0.2285082662864792</v>
+        <v>0.2285842218459951</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9639,7 +9639,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.1405608318590635</v>
+        <v>0.1390966565271983</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9647,22 +9647,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2557294797373574</v>
+        <v>0.2576294797373574</v>
       </c>
       <c r="C98">
-        <v>-43653.16055322619</v>
+        <v>-44302.57964552917</v>
       </c>
       <c r="D98">
-        <v>9391.231446773802</v>
+        <v>9307.664354470819</v>
       </c>
       <c r="E98">
-        <v>47526.692</v>
+        <v>48092.54399999999</v>
       </c>
       <c r="F98">
-        <v>54321.79199999999</v>
+        <v>54887.64399999999</v>
       </c>
       <c r="G98">
         <v>1277.4</v>
@@ -9683,37 +9683,37 @@
         <v>1781.7</v>
       </c>
       <c r="M98">
-        <v>12809.0785536</v>
+        <v>12942.5064552</v>
       </c>
       <c r="N98">
-        <v>-11027.3785536</v>
+        <v>-11160.8064552</v>
       </c>
       <c r="O98">
-        <v>-2426.023281792</v>
+        <v>-2455.377420144</v>
       </c>
       <c r="P98">
-        <v>-8601.355271807999</v>
+        <v>-8705.429035055999</v>
       </c>
       <c r="Q98">
-        <v>-7765.155271807999</v>
+        <v>-7869.229035055999</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.9072156691300542</v>
+        <v>1.194354225506739</v>
       </c>
       <c r="T98">
-        <v>19.89412630785345</v>
+        <v>26.5255017438046</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.03060126443598361</v>
+        <v>0.03028578748303533</v>
       </c>
       <c r="W98">
-        <v>0.2285842218459951</v>
+        <v>0.2286586113115003</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9721,7 +9721,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.1390966565271983</v>
+        <v>0.1376626703774333</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9729,22 +9729,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2576294797373574</v>
+        <v>0.2595294797373575</v>
       </c>
       <c r="C99">
-        <v>-44302.57964552917</v>
+        <v>-44950.52462545138</v>
       </c>
       <c r="D99">
-        <v>9307.664354470819</v>
+        <v>9225.571374548621</v>
       </c>
       <c r="E99">
-        <v>48092.54399999999</v>
+        <v>48658.396</v>
       </c>
       <c r="F99">
-        <v>54887.64399999999</v>
+        <v>55453.496</v>
       </c>
       <c r="G99">
         <v>1277.4</v>
@@ -9765,37 +9765,37 @@
         <v>1781.7</v>
       </c>
       <c r="M99">
-        <v>12942.5064552</v>
+        <v>13075.9343568</v>
       </c>
       <c r="N99">
-        <v>-11160.8064552</v>
+        <v>-11294.2343568</v>
       </c>
       <c r="O99">
-        <v>-2455.377420144</v>
+        <v>-2484.731558496</v>
       </c>
       <c r="P99">
-        <v>-8705.429035055999</v>
+        <v>-8809.502798304</v>
       </c>
       <c r="Q99">
-        <v>-7869.229035055999</v>
+        <v>-7973.302798304</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.194354225506739</v>
+        <v>1.768631338260109</v>
       </c>
       <c r="T99">
-        <v>26.5255017438046</v>
+        <v>39.7882526157069</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.03028578748303533</v>
+        <v>0.02997674883524925</v>
       </c>
       <c r="W99">
-        <v>0.2286586113115003</v>
+        <v>0.2287314826246482</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9803,7 +9803,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.1376626703774333</v>
+        <v>0.136257949251133</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9811,22 +9811,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2595294797373575</v>
+        <v>0.2614294797373575</v>
       </c>
       <c r="C100">
-        <v>-44950.52462545138</v>
+        <v>-45597.03415670063</v>
       </c>
       <c r="D100">
-        <v>9225.571374548621</v>
+        <v>9144.913843299375</v>
       </c>
       <c r="E100">
-        <v>48658.396</v>
+        <v>49224.248</v>
       </c>
       <c r="F100">
-        <v>55453.496</v>
+        <v>56019.348</v>
       </c>
       <c r="G100">
         <v>1277.4</v>
@@ -9847,37 +9847,37 @@
         <v>1781.7</v>
       </c>
       <c r="M100">
-        <v>13075.9343568</v>
+        <v>13209.3622584</v>
       </c>
       <c r="N100">
-        <v>-11294.2343568</v>
+        <v>-11427.6622584</v>
       </c>
       <c r="O100">
-        <v>-2484.731558496</v>
+        <v>-2514.085696848</v>
       </c>
       <c r="P100">
-        <v>-8809.502798304</v>
+        <v>-8913.576561551999</v>
       </c>
       <c r="Q100">
-        <v>-7973.302798304</v>
+        <v>-8077.376561552</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.768631338260109</v>
+        <v>3.491462676520217</v>
       </c>
       <c r="T100">
-        <v>39.7882526157069</v>
+        <v>79.5765052314138</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.02997674883524925</v>
+        <v>0.02967395339246895</v>
       </c>
       <c r="W100">
-        <v>0.2287314826246482</v>
+        <v>0.2288028817900558</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9885,91 +9885,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.136257949251133</v>
+        <v>0.1348816063294044</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2614294797373575</v>
-      </c>
-      <c r="C101">
-        <v>-45597.03415670063</v>
-      </c>
-      <c r="D101">
-        <v>9144.913843299375</v>
-      </c>
-      <c r="E101">
-        <v>49224.248</v>
-      </c>
-      <c r="F101">
-        <v>56019.348</v>
-      </c>
-      <c r="G101">
-        <v>1277.4</v>
-      </c>
-      <c r="H101">
-        <v>49790.1</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>2617.9</v>
-      </c>
-      <c r="K101">
-        <v>836.2</v>
-      </c>
-      <c r="L101">
-        <v>1781.7</v>
-      </c>
-      <c r="M101">
-        <v>13209.3622584</v>
-      </c>
-      <c r="N101">
-        <v>-11427.6622584</v>
-      </c>
-      <c r="O101">
-        <v>-2514.085696848</v>
-      </c>
-      <c r="P101">
-        <v>-8913.576561551999</v>
-      </c>
-      <c r="Q101">
-        <v>-8077.376561552</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.491462676520217</v>
-      </c>
-      <c r="T101">
-        <v>79.5765052314138</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.02967395339246895</v>
-      </c>
-      <c r="W101">
-        <v>0.2288028817900558</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.1348816063294044</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
